--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -262,8 +262,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:N63" headerRowCount="1">
-  <autoFilter ref="A1:N63"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:N64" headerRowCount="1">
+  <autoFilter ref="A1:N64"/>
   <tableColumns count="14">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="분류"/>
@@ -652,15 +652,15 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A7)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A7)</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A7)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A7)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A7)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A7)</f>
         <v/>
       </c>
       <c r="E7" s="10">
@@ -679,15 +679,15 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A8)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A8)</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A8)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A8)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A8)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A8)</f>
         <v/>
       </c>
       <c r="E8" s="10">
@@ -702,19 +702,19 @@
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A9)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A9)</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A9)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A9)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A9)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A9)</f>
         <v/>
       </c>
       <c r="E9" s="10">
@@ -729,19 +729,19 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="B10" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A10)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A10)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A10)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A10)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A10)</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -756,19 +756,19 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="B11" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A11)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A11)</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A11)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A11)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A11)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A11)</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -783,19 +783,19 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="B12" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A12)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A12)</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A12)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A12)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A12)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A12)</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -814,15 +814,15 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A13)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A13)</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A13)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A13)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A13)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A13)</f>
         <v/>
       </c>
       <c r="E13" s="10">
@@ -841,15 +841,15 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A14)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A14)</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A14)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A14)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A14)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A14)</f>
         <v/>
       </c>
       <c r="E14" s="10">
@@ -868,15 +868,15 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A15)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A15)</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A15)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A15)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A15)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A15)</f>
         <v/>
       </c>
       <c r="E15" s="10">
@@ -895,15 +895,15 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A16)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A16)</f>
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A16)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A16)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A16)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A16)</f>
         <v/>
       </c>
       <c r="E16" s="10">
@@ -922,15 +922,15 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A17)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A17)</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A17)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A17)</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A17)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A17)</f>
         <v/>
       </c>
       <c r="E17" s="10">
@@ -949,15 +949,15 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A18)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A18)</f>
         <v/>
       </c>
       <c r="C18" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A18)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A18)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A18)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A18)</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -976,15 +976,15 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$63,A19)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$64,A19)</f>
         <v/>
       </c>
       <c r="C19" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$63,'부품리스트'!$B$2:$B$63,A19)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A19)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$63,'부품리스트'!$B$2:$B$63,A19)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A19)</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -1054,7 +1054,7 @@
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
-          <t>· 핀 번호 확인 대상 IC: LMR36006, PCAP04, TPS26611 (회로도 VERIFY 표시; DAC8760은 v0.7에서 데이터시트 핀 확정). TPS2660은 R22 RTN 연결 확인.</t>
+          <t>· 핀 번호 확인 대상 IC: 없음 — 전 IC 제조사 데이터시트로 핀 대조 완료 (회로도 v0.8, STM32는 KiCad 공식 심볼). TPS2660 RTN은 GND와 분리 (R22 삭제).</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1414,25 +1414,25 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C6 C10</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>2.2u 100V</t>
+          <t>22u 25V</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>C_1210_3225Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
@@ -1442,19 +1442,19 @@
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>GRM32ER72A225KA35L</t>
+          <t>GRM31CR61E226KE15L</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>MLCC 2.2 uF 100 V X7R 1210</t>
+          <t>MLCC 22 uF 25 V X5R 1206 (벅 출력, 2개 — 데이터시트 COUT 2 × 15 µF 실효)</t>
         </is>
       </c>
       <c r="J6" s="19" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
       <c r="L6" s="20">
         <f>D6*J6</f>
@@ -1481,20 +1481,20 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>C8 C14 C15 C20 C21 C23 C28 C29 C40 C44 C50 C54 C60</t>
+          <t>C7</t>
         </is>
       </c>
       <c r="D7" s="18" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>100n</t>
+          <t>2.2u 100V</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_1210_3225Metric</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
@@ -1504,19 +1504,19 @@
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>GRM188R71H104KA93D</t>
+          <t>GRM32ER72A225KA35L</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>MLCC 100 nF 50 V X7R 0603</t>
+          <t>MLCC 2.2 uF 100 V X7R 1210</t>
         </is>
       </c>
       <c r="J7" s="19" t="n">
-        <v>0.004</v>
+        <v>0.15</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="L7" s="20">
         <f>D7*J7</f>
@@ -1543,15 +1543,15 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>C9 C12 C24 C25 C26</t>
+          <t>C8 C14 C15 C20 C21 C23 C28 C29 C36 C40 C44 C50 C54 C60</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
-          <t>1u</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="F8" s="16" t="inlineStr">
@@ -1566,19 +1566,19 @@
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>GRM188R61E105KA12D</t>
+          <t>GRM188R71H104KA93D</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>MLCC 1 uF 25 V X5R 0603</t>
+          <t>MLCC 100 nF 50 V X7R 0603</t>
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.005</v>
+        <v>0.004</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="L8" s="20">
         <f>D8*J8</f>
@@ -1605,20 +1605,20 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>C10</t>
+          <t>C9 C12</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>22u 10V</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -1628,19 +1628,19 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR61A226ME44L</t>
+          <t>GRM188R61E105KA12D</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>MLCC 22 uF 10 V X5R 0805</t>
+          <t>MLCC 1 uF 25 V X5R 0603</t>
         </is>
       </c>
       <c r="J9" s="19" t="n">
-        <v>0.04</v>
+        <v>0.005</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>0.1</v>
+        <v>0.015</v>
       </c>
       <c r="L9" s="20">
         <f>D9*J9</f>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>C13</t>
+          <t>C11</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>10u</t>
+          <t>20p C0G</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -1690,19 +1690,19 @@
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR61E106KA73L</t>
+          <t>GRM1885C1H200JA01D</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>MLCC 10 uF 25 V X5R 0805</t>
+          <t>MLCC 20 pF 50 V C0G 0603 (벅 CFF)</t>
         </is>
       </c>
       <c r="J10" s="19" t="n">
-        <v>0.03</v>
+        <v>0.003</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>0.08</v>
+        <v>0.008</v>
       </c>
       <c r="L10" s="20">
         <f>D10*J10</f>
@@ -1729,15 +1729,15 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C13 C24</t>
         </is>
       </c>
       <c r="D11" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>4.7u</t>
+          <t>10u</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -1752,19 +1752,19 @@
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR61E475KA12L</t>
+          <t>GRM21BR61E106KA73L</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>MLCC 4.7 uF 25 V X5R 0805</t>
+          <t>MLCC 10 uF 25 V X5R 0805</t>
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="L11" s="20">
         <f>D11*J11</f>
@@ -1786,25 +1786,25 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C18 C25</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>220p C0G 1%</t>
+          <t>4.7u</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
@@ -1814,19 +1814,19 @@
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>GRM1885C1H221FA01D</t>
+          <t>GRM21BR61E475KA12L</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>MLCC 220 pF 50 V C0G ±1% 0603 (PCAP04 기준 C)</t>
+          <t>MLCC 4.7 uF 25 V X5R 0805</t>
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="L12" s="20">
         <f>D12*J12</f>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="D13" s="18" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>10n</t>
+          <t>220p C0G 1%</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -1876,19 +1876,19 @@
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>GRM188R71H103KA01D</t>
+          <t>GRM1885C1H221FA01D</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>MLCC 10 nF 50 V X7R 0603</t>
+          <t>MLCC 220 pF 50 V C0G ±1% 0603 (PCAP04 기준 C)</t>
         </is>
       </c>
       <c r="J13" s="19" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="L13" s="20">
         <f>D13*J13</f>
@@ -1910,20 +1910,20 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>C41 C51</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>1n 100V</t>
+          <t>10n</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -1938,16 +1938,16 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>GRM188R72A102KA01D</t>
+          <t>GRM188R71H103KA01D</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>MLCC 1 nF 100 V X7R 0603</t>
+          <t>MLCC 10 nF 50 V X7R 0603</t>
         </is>
       </c>
       <c r="J14" s="19" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="K14" s="19" t="n">
         <v>0.01</v>
@@ -1972,25 +1972,25 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>C42 C45 C52 C55</t>
+          <t>C41 C51</t>
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>100n 50V</t>
+          <t>1n 100V</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -2000,19 +2000,19 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR71H104KA01L</t>
+          <t>GRM188R72A102KA01D</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>MLCC 100 nF 50 V X7R 0805</t>
+          <t>MLCC 1 nF 100 V X7R 0603</t>
         </is>
       </c>
       <c r="J15" s="19" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K15" s="19" t="n">
         <v>0.01</v>
-      </c>
-      <c r="K15" s="19" t="n">
-        <v>0.03</v>
       </c>
       <c r="L15" s="20">
         <f>D15*J15</f>
@@ -2039,20 +2039,20 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>C43 C53</t>
+          <t>C42 C45 C52 C55</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>4.7u 50V</t>
+          <t>100n 50V</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>C_1210_3225Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -2062,19 +2062,19 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>GRM32ER71H475KA88L</t>
+          <t>GRM21BR71H104KA01L</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>MLCC 4.7 uF 50 V X7R 1210</t>
+          <t>MLCC 100 nF 50 V X7R 0805</t>
         </is>
       </c>
       <c r="J16" s="19" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="K16" s="19" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="L16" s="20">
         <f>D16*J16</f>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="D17" s="18" t="n">
@@ -2109,34 +2109,34 @@
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>SMDJ36CA</t>
+          <t>4.7u 50V</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>D_SMC</t>
+          <t>C_1210_3225Metric</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>Littelfuse</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>SMDJ36CA</t>
+          <t>GRM32ER71H475KA88L</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>TVS 3000 W 36 V 양방향 SMC (입력 1단)</t>
+          <t>MLCC 4.7 uF 50 V X7R 1210</t>
         </is>
       </c>
       <c r="J17" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K17" s="19" t="n">
         <v>0.25</v>
-      </c>
-      <c r="K17" s="19" t="n">
-        <v>0.6</v>
       </c>
       <c r="L17" s="20">
         <f>D17*J17</f>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>SMBJ33CA</t>
+          <t>SMDJ36CA</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>D_SMB</t>
+          <t>D_SMC</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -2186,19 +2186,19 @@
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>SMBJ33CA</t>
+          <t>SMDJ36CA</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
-          <t>TVS 600 W 33 V 양방향 SMB (입력 2단)</t>
+          <t>TVS 3000 W 36 V 양방향 SMC (입력 1단)</t>
         </is>
       </c>
       <c r="J18" s="19" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="L18" s="20">
         <f>D18*J18</f>
@@ -2225,20 +2225,20 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>D30 D40</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>SMAJ33CA</t>
+          <t>SMBJ33CA</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>D_SMA</t>
+          <t>D_SMB</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
@@ -2248,19 +2248,19 @@
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>SMAJ33CA</t>
+          <t>SMBJ33CA</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>TVS 400 W 33 V 양방향 SMA (아날로그 출력)</t>
+          <t>TVS 600 W 33 V 양방향 SMB (입력 2단)</t>
         </is>
       </c>
       <c r="J19" s="19" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="L19" s="20">
         <f>D19*J19</f>
@@ -2282,47 +2282,47 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>D30 D40</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>600R@100MHz</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>L_0603_1608Metric</t>
+          <t>Texas_DRB0008A</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>BLM18KG601SN1D</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>페라이트 비드 600 Ω@100 MHz 0603</t>
+          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장)</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="L20" s="20">
         <f>D20*J20</f>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>GDT1</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="D21" s="18" t="n">
@@ -2357,34 +2357,34 @@
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>GDT 230V</t>
+          <t>600R@100MHz</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>GDT_Bourns_2038</t>
+          <t>L_0603_1608Metric</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>2038-23-SM-RPLF</t>
+          <t>BLM18KG601SN1D</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>GDT 230 V SMD (회로 GND–외함)</t>
+          <t>페라이트 비드 600 Ω@100 MHz 0603</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="L21" s="20">
         <f>D21*J21</f>
@@ -2394,9 +2394,9 @@
         <f>D21*K21</f>
         <v/>
       </c>
-      <c r="N21" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>GDT1</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
@@ -2419,34 +2419,34 @@
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>GDT 230V</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
+          <t>GDT_Bourns_2038</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>2038-23-SM-RPLF</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
+          <t>GDT 230 V SMD (회로 GND–외함)</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L22" s="20">
         <f>D22*J22</f>
@@ -2456,9 +2456,9 @@
         <f>D22*K22</f>
         <v/>
       </c>
-      <c r="N22" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N22" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D23" s="18" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>TC2030-IDC-NL</t>
+          <t>SM08B-GHS-TB</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>(PCB 패드만)</t>
+          <t>SM08B-GHS-TB</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>SWD 기록용 패드 — 부품 실장 없음</t>
+          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L23" s="20">
         <f>D23*J23</f>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="N23" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
@@ -2543,34 +2543,34 @@
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>TC2030-IDC-NL</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>(PCB 패드만)</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
+          <t>SWD 기록용 패드 — 부품 실장 없음</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L24" s="20">
         <f>D24*J24</f>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="N24" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="D25" s="18" t="n">
@@ -2605,34 +2605,34 @@
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>Chassis contact</t>
+          <t>SM04B-SRSS-TB</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>Chassis_Spring_Contact</t>
+          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>SMD 스프링 접점 (Würth WE-SECF 계열 등)</t>
+          <t>SM04B-SRSS-TB</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>PCB 가장자리 → 하우징 내면 샤시 접촉 (구 M12 쉘 핀 대체)</t>
+          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="L25" s="20">
         <f>D25*J25</f>
@@ -2642,9 +2642,9 @@
         <f>D25*K25</f>
         <v/>
       </c>
-      <c r="N25" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
@@ -2667,34 +2667,34 @@
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>CMC 2x1mH 0.3A</t>
+          <t>Chassis contact</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>CMC_WE-SL</t>
+          <t>Chassis_Spring_Contact</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>Würth</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>WE-SL2 계열 (품번 확인)</t>
+          <t>SMD 스프링 접점 (Würth WE-SECF 계열 등)</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>공통모드 초크 2×1 mH, ≥0.3 A</t>
+          <t>PCB 가장자리 → 하우징 내면 샤시 접촉 (구 M12 쉘 핀 대체)</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="L26" s="20">
         <f>D26*J26</f>
@@ -2704,9 +2704,9 @@
         <f>D26*K26</f>
         <v/>
       </c>
-      <c r="N26" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N26" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
@@ -2716,12 +2716,12 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
@@ -2729,34 +2729,34 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>22uH</t>
+          <t>CMC 2x1mH 0.3A</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>L_4x4mm</t>
+          <t>CMC_WE-SL</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>Coilcraft</t>
+          <t>Würth</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>XGL4030-223ME (확인)</t>
+          <t>WE-SL2 계열 (품번 확인)</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 22 uH, 4×4 mm, Isat ≥ 0.8 A</t>
+          <t>공통모드 초크 2×1 mH, ≥0.3 A</t>
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L27" s="20">
         <f>D27*J27</f>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
@@ -2791,34 +2791,34 @@
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>4.7R 1W pulse</t>
+          <t>15uH</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>R_MELF_MMB-0207</t>
+          <t>L_4x4mm</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Coilcraft</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>MMB 0207 4.7 Ω (품번 확인)</t>
+          <t>XGL4030-153ME (확인)</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>MELF 펄스 저항 4.7 Ω 1 W (입력 직렬)</t>
+          <t>파워 인덕터 15 uH, 4×4 mm, Isat ≥ 0.8 A (LMR36006 5 V·1 MHz 권장값)</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="L28" s="20">
         <f>D28*J28</f>
@@ -2840,12 +2840,12 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
@@ -2853,34 +2853,34 @@
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>4.7R 1W pulse</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_MELF_MMB-0207</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-071ML</t>
+          <t>MMB 0207 4.7 Ω (품번 확인)</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>저항 1 MΩ 1% 0603</t>
+          <t>MELF 펄스 저항 4.7 Ω 1 W (입력 직렬)</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.002</v>
+        <v>0.1</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0.005</v>
+        <v>0.3</v>
       </c>
       <c r="L29" s="20">
         <f>D29*J29</f>
@@ -2890,9 +2890,9 @@
         <f>D29*K29</f>
         <v/>
       </c>
-      <c r="N29" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>866k 1%</t>
+          <t>1M</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-07866KL</t>
+          <t>RC0603FR-071ML</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
+          <t>저항 1 MΩ 1% 0603</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>97.6k 1%</t>
+          <t>866k 1%</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -2992,12 +2992,12 @@
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0797K6L</t>
+          <t>RC0603FR-07866KL</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP)</t>
+          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
         </is>
       </c>
       <c r="J31" s="19" t="n">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>36.5k 1%</t>
+          <t>97.6k 1%</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0736K5L</t>
+          <t>RC0603FR-0797K6L</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>저항 36.5 kΩ 1% 0603 (OVP)</t>
+          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP)</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
@@ -3101,7 +3101,7 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>R_ILIM *</t>
+          <t>41.2k 1%</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
@@ -3116,12 +3116,12 @@
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-07 (값 TBD)</t>
+          <t>RC0603FR-0741K2L</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>저항 1% 0603 — TPS2660 전류제한 150 mA 값 계산 필요</t>
+          <t>저항 41.2 kΩ 1% 0603 (OVP 29 V)</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
@@ -3138,9 +3138,9 @@
         <f>D33*K33</f>
         <v/>
       </c>
-      <c r="N33" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -3150,20 +3150,20 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>R7 R31 R41</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>80.6k 1%</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0710KL</t>
+          <t>RC0603FR-0780K6L</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>저항 10 kΩ 1% 0603</t>
+          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
@@ -3460,47 +3460,47 @@
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>R22</t>
+          <t>R30 R40</t>
         </is>
       </c>
       <c r="D39" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>0R RTN link*</t>
+          <t>10R pulse</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>RC0603JR-070RL</t>
+          <t>CRCW251210R0FKEGHP (확인)</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>0 Ω 링크 — TPS2660 RTN 연결 확인 후 실장 여부 결정</t>
+          <t>펄스 내성 저항 10 Ω 2512 (출력 직렬)</t>
         </is>
       </c>
       <c r="J39" s="19" t="n">
-        <v>0.002</v>
+        <v>0.05</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>0.005</v>
+        <v>0.15</v>
       </c>
       <c r="L39" s="20">
         <f>D39*J39</f>
@@ -3522,47 +3522,47 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>R30 R40</t>
+          <t>R31 R33 R41</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>10R pulse</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>CRCW251210R0FKEGHP (확인)</t>
+          <t>RC0603FR-0710KL</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>펄스 내성 저항 10 Ω 2512 (출력 직렬)</t>
+          <t>저항 10 kΩ 1% 0603</t>
         </is>
       </c>
       <c r="J40" s="19" t="n">
-        <v>0.05</v>
+        <v>0.002</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>0.15</v>
+        <v>0.005</v>
       </c>
       <c r="L40" s="20">
         <f>D40*J40</f>
@@ -3572,9 +3572,9 @@
         <f>D40*K40</f>
         <v/>
       </c>
-      <c r="N40" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -3646,20 +3646,20 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>R34 R44</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>10R</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-07100KL</t>
+          <t>RC0603FR-0710RL</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0603 (DAC 데이지 체인 풀다운)</t>
+          <t>저항 10 Ω 1% 0603 (DAC8760 AVDD 직렬, 데이터시트 10장)</t>
         </is>
       </c>
       <c r="J42" s="19" t="n">
@@ -3783,12 +3783,12 @@
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>LMR36006</t>
+          <t>LMR36006BRNXR</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>VQFN-HR-12_LMR36006</t>
+          <t>Texas_RNX0012A_VQFN-HR-12_2x3mm</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>LMR36006 (가변판 주문코드 확인)</t>
+          <t>LMR36006BRNXR</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>벅 60 V 0.6 A → 5 V</t>
+          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm</t>
         </is>
       </c>
       <c r="J44" s="19" t="n">
@@ -3820,9 +3820,9 @@
         <f>D44*K44</f>
         <v/>
       </c>
-      <c r="N44" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>QFN-24_PCAP04</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>TPS26611</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>TPS26611</t>
+          <t>Texas_DDF0008A_SOT-8_1.6x2.9mm_P0.65mm</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>TPS26611 (패키지·주문코드 확인)</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>4–20 mA 출력 오결선 보호</t>
+          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
         </is>
       </c>
       <c r="J50" s="19" t="n">
@@ -4192,9 +4192,9 @@
         <f>D50*K50</f>
         <v/>
       </c>
-      <c r="N50" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>기판</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -4341,34 +4341,34 @@
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>HMT500(260313A) (E-301)</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
+          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
         </is>
       </c>
       <c r="J53" s="19" t="n">
-        <v>0.8</v>
+        <v>0.08</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L53" s="20">
         <f>D53*J53</f>
@@ -4378,9 +4378,9 @@
         <f>D53*K53</f>
         <v/>
       </c>
-      <c r="N53" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -4390,12 +4390,12 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>기판</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
@@ -4413,24 +4413,24 @@
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>MK33-W mini (150138)</t>
+          <t>HMT500(260313A) (E-301)</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>정전용량 습도 소자 200 pF (센서 프로브 P-202에 실장)</t>
+          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
         </is>
       </c>
       <c r="J54" s="19" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L54" s="20">
         <f>D54*J54</f>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="N54" s="21" t="inlineStr">
         <is>
-          <t>사내 단가</t>
+          <t>추정</t>
         </is>
       </c>
     </row>
@@ -4480,19 +4480,19 @@
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>MiniSens Pt1000 F0.1</t>
+          <t>MK33-W mini (150138)</t>
         </is>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
-          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
+          <t>정전용량 습도 소자 200 pF (센서 프로브 P-202에 실장)</t>
         </is>
       </c>
       <c r="J55" s="19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L55" s="20">
         <f>D55*J55</f>
@@ -4504,7 +4504,7 @@
       </c>
       <c r="N55" s="21" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>사내 단가</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>P-204</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
@@ -4537,24 +4537,24 @@
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>M Connect</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>TBD (두텍 사용품)</t>
+          <t>MiniSens Pt1000 F0.1</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
+          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
         </is>
       </c>
       <c r="J56" s="19" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L56" s="20">
         <f>D56*J56</f>
@@ -4564,9 +4564,9 @@
         <f>D56*K56</f>
         <v/>
       </c>
-      <c r="N56" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="N56" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
         </is>
       </c>
     </row>
@@ -4576,12 +4576,12 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>P-204</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
@@ -4599,24 +4599,24 @@
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>M Connect</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>GHR-08V-S</t>
+          <t>TBD (두텍 사용품)</t>
         </is>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
+          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
         </is>
       </c>
       <c r="J57" s="19" t="n">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>0.15</v>
+        <v>10</v>
       </c>
       <c r="L57" s="20">
         <f>D57*J57</f>
@@ -4626,9 +4626,9 @@
         <f>D57*K57</f>
         <v/>
       </c>
-      <c r="N57" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N57" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
         </is>
       </c>
       <c r="D58" s="18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
@@ -4666,19 +4666,19 @@
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>SSHL-002T-P0.2</t>
+          <t>GHR-08V-S</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>GH 크림프 단자 AWG 30–26</t>
+          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
         </is>
       </c>
       <c r="J58" s="19" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="L58" s="20">
         <f>D58*J58</f>
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -4723,24 +4723,24 @@
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG28 전선</t>
+          <t>SSHL-002T-P0.2</t>
         </is>
       </c>
       <c r="I59" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+          <t>GH 크림프 단자 AWG 30–26</t>
         </is>
       </c>
       <c r="J59" s="19" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="L59" s="20">
         <f>D59*J59</f>
@@ -4750,9 +4750,9 @@
         <f>D59*K59</f>
         <v/>
       </c>
-      <c r="N59" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4767,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
@@ -4785,24 +4785,24 @@
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>SHR-04V-S</t>
+          <t>PTFE AWG28 전선</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
+          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
         </is>
       </c>
       <c r="J60" s="19" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="K60" s="19" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="L60" s="20">
         <f>D60*J60</f>
@@ -4812,9 +4812,9 @@
         <f>D60*K60</f>
         <v/>
       </c>
-      <c r="N60" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N60" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4833,7 @@
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
@@ -4852,19 +4852,19 @@
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>SSH-003T-P0.2-H</t>
+          <t>SHR-04V-S</t>
         </is>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
-          <t>SH 크림프 단자 AWG 32–28</t>
+          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
         </is>
       </c>
       <c r="J61" s="19" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="L61" s="20">
         <f>D61*J61</f>
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -4909,24 +4909,24 @@
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG30 전선</t>
+          <t>SSH-003T-P0.2-H</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+          <t>SH 크림프 단자 AWG 32–28</t>
         </is>
       </c>
       <c r="J62" s="19" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="L62" s="20">
         <f>D62*J62</f>
@@ -4936,9 +4936,9 @@
         <f>D62*K62</f>
         <v/>
       </c>
-      <c r="N62" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>조립</t>
+          <t>하네스</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="D63" s="18" t="n">
@@ -4971,24 +4971,24 @@
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>SMT 양면 실장</t>
+          <t>PTFE AWG30 전선</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
-          <t>1k 기준 조립비</t>
+          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
         </is>
       </c>
       <c r="J63" s="19" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="L63" s="20">
         <f>D63*J63</f>
@@ -5005,17 +5005,79 @@
       </c>
     </row>
     <row r="64">
-      <c r="I64" s="3" t="inlineStr">
+      <c r="A64" s="16" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>조립</t>
+        </is>
+      </c>
+      <c r="C64" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="17" t="inlineStr">
+        <is>
+          <t>SMT 양면 실장</t>
+        </is>
+      </c>
+      <c r="I64" s="17" t="inlineStr">
+        <is>
+          <t>1k 기준 조립비</t>
+        </is>
+      </c>
+      <c r="J64" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K64" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L64" s="20">
+        <f>D64*J64</f>
+        <v/>
+      </c>
+      <c r="M64" s="20">
+        <f>D64*K64</f>
+        <v/>
+      </c>
+      <c r="N64" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="I65" s="3" t="inlineStr">
         <is>
           <t>합계 (1대분)</t>
         </is>
       </c>
-      <c r="L64" s="23">
-        <f>SUM(L2:L63)</f>
-        <v/>
-      </c>
-      <c r="M64" s="23">
-        <f>SUM(M2:M63)</f>
+      <c r="L65" s="23">
+        <f>SUM(L2:L64)</f>
+        <v/>
+      </c>
+      <c r="M65" s="23">
+        <f>SUM(M2:M64)</f>
         <v/>
       </c>
     </row>

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -2300,7 +2300,7 @@
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>Texas_DRB0008A</t>
+          <t>Texas_DRB0008A_PadFloat</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>GDT 230V</t>
+          <t>2035-23-SM</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>GDT_Bourns_2038</t>
+          <t>GDT_Bourns_2035-xx-SM</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2038-23-SM-RPLF</t>
+          <t>2035-23-SM-RPLF</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>GDT 230 V SMD (회로 GND–외함)</t>
+          <t>2전극 SMD GDT 230 V, Ø5 × 4.4 mm (회로 GND–외함). ※ 이전 2038은 3전극이라 교체</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
@@ -2456,9 +2456,9 @@
         <f>D22*K22</f>
         <v/>
       </c>
-      <c r="N22" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2667,31 +2667,31 @@
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>Chassis contact</t>
+          <t>S1941-46R</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>Chassis_Spring_Contact</t>
+          <t>SpringContact_Harwin_S1941-46R</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>Harwin</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>SMD 스프링 접점 (Würth WE-SECF 계열 등)</t>
+          <t>S1941-46R</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>PCB 가장자리 → 하우징 내면 샤시 접촉 (구 M12 쉘 핀 대체)</t>
+          <t>SMT 스프링 접점, 자유 높이 7.25 mm — PCB 가장자리 → 하우징 Ø27 내면 (압축량은 조립 시뮬레이션으로 확인)</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="K26" s="19" t="n">
         <v>0.4</v>
@@ -2704,9 +2704,9 @@
         <f>D26*K26</f>
         <v/>
       </c>
-      <c r="N26" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2729,12 +2729,12 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>CMC 2x1mH 0.3A</t>
+          <t>CMC 1mH 0.8A</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>CMC_WE-SL</t>
+          <t>L_CommonMode_Wuerth_WE-SL2</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
@@ -2744,19 +2744,19 @@
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>WE-SL2 계열 (품번 확인)</t>
+          <t>744222</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>공통모드 초크 2×1 mH, ≥0.3 A</t>
+          <t>WE-SL2 공통모드 초크 2 × 1 mH, 0.8 A, 310 mΩ, 9.2 × 6 × 5 mm (권선 1–4, 2–3: 데이터시트로 확인)</t>
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="L27" s="20">
         <f>D27*J27</f>
@@ -2766,9 +2766,9 @@
         <f>D27*K27</f>
         <v/>
       </c>
-      <c r="N27" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>L_4x4mm</t>
+          <t>L_Coilcraft_XAL4030-XXX</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>XGL4030-153ME (확인)</t>
+          <t>XGL4030-153MEC</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 15 uH, 4×4 mm, Isat ≥ 0.8 A (LMR36006 5 V·1 MHz 권장값)</t>
+          <t>파워 인덕터 15 µH, 4 × 4 × 3.1 mm (XAL4030 풋프린트) — LMR36006 5 V·1 MHz 권장값</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L28" s="20">
         <f>D28*J28</f>
@@ -2828,9 +2828,9 @@
         <f>D28*K28</f>
         <v/>
       </c>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2868,12 +2868,12 @@
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>MMB 0207 4.7 Ω (품번 확인)</t>
+          <t>MMB02070C4708FB200</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>MELF 펄스 저항 4.7 Ω 1 W (입력 직렬)</t>
+          <t>MELF 0207 박막 4.7 Ω 1% 1 W, AEC-Q200 (입력 직렬, 1단·2단 서지 분담)</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
@@ -2890,9 +2890,9 @@
         <f>D29*K29</f>
         <v/>
       </c>
-      <c r="N29" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>4.02k 0.01% 5ppm</t>
+          <t>4.02k 0.02% 5ppm</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>Vishay / Susumu</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>0.01% 5 ppm 박막 (품번 확인)</t>
+          <t>PLTT0603Z4021 (0.02 %, 5 ppm/K, 주문 접미사 확인)</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>Pt1000 기준저항 4.02 kΩ 0.01% 5 ppm/K 0603</t>
+          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거)</t>
         </is>
       </c>
       <c r="J38" s="19" t="n">
@@ -3448,9 +3448,9 @@
         <f>D38*K38</f>
         <v/>
       </c>
-      <c r="N38" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>CRCW251210R0FKEGHP (확인)</t>
+          <t>CRCW251210R0FKEGHP</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>펄스 내성 저항 10 Ω 2512 (출력 직렬)</t>
+          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬)</t>
         </is>
       </c>
       <c r="J39" s="19" t="n">
@@ -3510,9 +3510,9 @@
         <f>D39*K39</f>
         <v/>
       </c>
-      <c r="N39" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N39" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.66x2.46mm_ThermalVias</t>
+          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>Texas_DDF0008A_SOT-8_1.6x2.9mm_P0.65mm</t>
+          <t>SOT-23-8</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -2667,34 +2667,34 @@
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>S1941-46R</t>
+          <t>CHASSIS wire</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>SpringContact_Harwin_S1941-46R</t>
+          <t>SolderWire_Chassis_D0.6mm</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>Harwin</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>S1941-46R</t>
+          <t>PCB 납땜 구멍 (부품 없음)</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>SMT 스프링 접점, 자유 높이 7.25 mm — PCB 가장자리 → 하우징 Ø27 내면 (압축량은 조립 시뮬레이션으로 확인)</t>
+          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L26" s="20">
         <f>D26*J26</f>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
     </row>

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -262,8 +262,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:N64" headerRowCount="1">
-  <autoFilter ref="A1:N64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:N69" headerRowCount="1">
+  <autoFilter ref="A1:N69"/>
   <tableColumns count="14">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="분류"/>
@@ -652,15 +652,15 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A7)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A7)</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A7)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A7)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A7)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A7)</f>
         <v/>
       </c>
       <c r="E7" s="10">
@@ -679,15 +679,15 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A8)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A8)</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A8)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A8)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A8)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A8)</f>
         <v/>
       </c>
       <c r="E8" s="10">
@@ -706,15 +706,15 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A9)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A9)</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A9)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A9)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A9)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A9)</f>
         <v/>
       </c>
       <c r="E9" s="10">
@@ -733,15 +733,15 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A10)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A10)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A10)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A10)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A10)</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -756,19 +756,19 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="B11" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A11)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A11)</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A11)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A11)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A11)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A11)</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -783,19 +783,19 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="B12" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A12)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A12)</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A12)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A12)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A12)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A12)</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -810,19 +810,19 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="B13" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A13)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A13)</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A13)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A13)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A13)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A13)</f>
         <v/>
       </c>
       <c r="E13" s="10">
@@ -841,15 +841,15 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A14)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A14)</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A14)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A14)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A14)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A14)</f>
         <v/>
       </c>
       <c r="E14" s="10">
@@ -868,15 +868,15 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A15)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A15)</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A15)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A15)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A15)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A15)</f>
         <v/>
       </c>
       <c r="E15" s="10">
@@ -895,15 +895,15 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A16)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A16)</f>
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A16)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A16)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A16)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A16)</f>
         <v/>
       </c>
       <c r="E16" s="10">
@@ -922,15 +922,15 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A17)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A17)</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A17)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A17)</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A17)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A17)</f>
         <v/>
       </c>
       <c r="E17" s="10">
@@ -949,15 +949,15 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A18)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A18)</f>
         <v/>
       </c>
       <c r="C18" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A18)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A18)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A18)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A18)</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -976,15 +976,15 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$64,A19)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$69,A19)</f>
         <v/>
       </c>
       <c r="C19" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$64,'부품리스트'!$B$2:$B$64,A19)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A19)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$64,'부품리스트'!$B$2:$B$64,A19)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A19)</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -1069,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1228,25 +1228,25 @@
       </c>
       <c r="B3" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2 C7</t>
         </is>
       </c>
       <c r="D3" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
-          <t>4.7n 2kV Y2</t>
+          <t>2.2u 100V</t>
         </is>
       </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
-          <t>C_1812_4532Metric</t>
+          <t>C_1210_3225Metric</t>
         </is>
       </c>
       <c r="G3" s="16" t="inlineStr">
@@ -1256,19 +1256,19 @@
       </c>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t>GA343QR7GF472KW01L</t>
+          <t>GRM32ER72A225KA35L</t>
         </is>
       </c>
       <c r="I3" s="17" t="inlineStr">
         <is>
-          <t>Safety cap 4.7 nF Y2 (250 VAC) 1812</t>
+          <t>MLCC 2.2 uF 100 V X7R 1210</t>
         </is>
       </c>
       <c r="J3" s="19" t="n">
         <v>0.15</v>
       </c>
       <c r="K3" s="19" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="L3" s="20">
         <f>D3*J3</f>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B4" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>C4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="D4" s="18" t="n">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>22n</t>
+          <t>4.7n 2kV Y2</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_1812_4532Metric</t>
         </is>
       </c>
       <c r="G4" s="16" t="inlineStr">
@@ -1318,19 +1318,19 @@
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>GRM188R71H223KA01D</t>
+          <t>GA343QR7GF472KW01L</t>
         </is>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>MLCC 22 nF 50 V X7R 0603</t>
+          <t>Safety cap 4.7 nF Y2 (250 VAC) 1812</t>
         </is>
       </c>
       <c r="J4" s="19" t="n">
-        <v>0.004</v>
+        <v>0.15</v>
       </c>
       <c r="K4" s="19" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="L4" s="20">
         <f>D4*J4</f>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="D5" s="18" t="n">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>10u 50V</t>
+          <t>22n</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>C_1210_3225Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
@@ -1380,19 +1380,19 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>GRM32ER71H106KA12L</t>
+          <t>GRM188R71H223KA01D</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>MLCC 10 uF 50 V X7R 1210</t>
+          <t>MLCC 22 nF 50 V X7R 0603</t>
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.15</v>
+        <v>0.004</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="L5" s="20">
         <f>D5*J5</f>
@@ -1414,25 +1414,25 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>C6 C10</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
-          <t>22u 25V</t>
+          <t>10u 50V</t>
         </is>
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>C_1206_3216Metric</t>
+          <t>C_1210_3225Metric</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
@@ -1442,19 +1442,19 @@
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>GRM31CR61E226KE15L</t>
+          <t>GRM32ER71H106KA12L</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>MLCC 22 uF 25 V X5R 1206 (벅 출력, 2개 — 데이터시트 COUT 2 × 15 µF 실효)</t>
+          <t>MLCC 10 uF 50 V X7R 1210</t>
         </is>
       </c>
       <c r="J6" s="19" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
       <c r="L6" s="20">
         <f>D6*J6</f>
@@ -1476,47 +1476,47 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>C7</t>
+          <t>C6 C10</t>
         </is>
       </c>
       <c r="D7" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>2.2u 100V</t>
+          <t>22u 25V</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>C_1210_3225Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>(X7R 1206)</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>GRM32ER72A225KA35L</t>
+          <t>품번 확인 필요 — X7R 22 µF 25 V 1206</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>MLCC 2.2 uF 100 V X7R 1210</t>
+          <t>MLCC 22 uF 25 V X7R 1206 (벅 출력 2개, LMR36006 X7R 요구, v0.9: X5R 금지)</t>
         </is>
       </c>
       <c r="J7" s="19" t="n">
         <v>0.15</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="L7" s="20">
         <f>D7*J7</f>
@@ -1526,9 +1526,9 @@
         <f>D7*K7</f>
         <v/>
       </c>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N7" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
@@ -1543,11 +1543,11 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>C8 C14 C15 C20 C21 C23 C28 C29 C36 C40 C44 C50 C54 C60</t>
+          <t>C8 C14 C15 C20 C21 C23 C28 C29 C30 C36 C40 C44 C46 C50 C53 C54 C56 C60</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
@@ -1605,11 +1605,11 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>C9 C12</t>
+          <t>C9 C12 C26</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
@@ -1628,19 +1628,19 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>GRM188R61E105KA12D</t>
+          <t>GRM188R71E105KA12D</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>MLCC 1 uF 25 V X5R 0603</t>
+          <t>MLCC 1 uF 25 V X7R 0603 (v0.9: X5R → X7R, 몰딩 후 85 °C 초과)</t>
         </is>
       </c>
       <c r="J9" s="19" t="n">
-        <v>0.005</v>
+        <v>0.006</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="L9" s="20">
         <f>D9*J9</f>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>C13 C24</t>
+          <t>C13 C25</t>
         </is>
       </c>
       <c r="D11" s="18" t="n">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
@@ -1752,19 +1752,19 @@
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR61E106KA73L</t>
+          <t>GRM31CR71E106KA12L</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>MLCC 10 uF 25 V X5R 0805</t>
+          <t>MLCC 10 uF 25 V X7R 1206 (v0.9: 0805 X5R → 1206 X7R, DC 바이어스 여유)</t>
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="L11" s="20">
         <f>D11*J11</f>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>C18 C25</t>
+          <t>C16 C17</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
@@ -1799,27 +1799,27 @@
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>4.7u</t>
+          <t>220n 100V</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>(X7R 0603)</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR61E475KA12L</t>
+          <t>품번 확인 필요 — X7R 220 nF 100 V 0603</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>MLCC 4.7 uF 25 V X5R 0805</t>
+          <t>MLCC 220 nF 100 V X7R 0603 (LMR36006 VIN–PGND 핀마다)</t>
         </is>
       </c>
       <c r="J12" s="19" t="n">
@@ -1836,9 +1836,9 @@
         <f>D12*K12</f>
         <v/>
       </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
@@ -1848,12 +1848,12 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="D13" s="18" t="n">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>220p C0G 1%</t>
+          <t>4.7u</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
@@ -1876,19 +1876,19 @@
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>GRM1885C1H221FA01D</t>
+          <t>GRM21BR71E475KA73L</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>MLCC 220 pF 50 V C0G ±1% 0603 (PCAP04 기준 C)</t>
+          <t>MLCC 4.7 uF 25 V X7R 0805 (품번 확인 필요)</t>
         </is>
       </c>
       <c r="J13" s="19" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="L13" s="20">
         <f>D13*J13</f>
@@ -1898,9 +1898,9 @@
         <f>D13*K13</f>
         <v/>
       </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N13" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
@@ -1910,12 +1910,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>10n</t>
+          <t>220p C0G 1%</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -1938,19 +1938,19 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>GRM188R71H103KA01D</t>
+          <t>GRM1885C1H221FA01D</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>MLCC 10 nF 50 V X7R 0603</t>
+          <t>MLCC 220 pF 50 V C0G ±1% 0603 (PCAP04 기준 C)</t>
         </is>
       </c>
       <c r="J14" s="19" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="L14" s="20">
         <f>D14*J14</f>
@@ -1972,25 +1972,25 @@
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>C41 C51</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="D15" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>1n 100V</t>
+          <t>22u 10V</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -2000,19 +2000,19 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>GRM188R72A102KA01D</t>
+          <t>GRM31CR71A226KE15L</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>MLCC 1 nF 100 V X7R 0603</t>
+          <t>MLCC 22 uF 10 V X7R 1206 (PCAP04 VDD33 ≥ 10 µF 실효, 품번 확인 필요)</t>
         </is>
       </c>
       <c r="J15" s="19" t="n">
-        <v>0.004</v>
+        <v>0.08</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="L15" s="20">
         <f>D15*J15</f>
@@ -2022,9 +2022,9 @@
         <f>D15*K15</f>
         <v/>
       </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N15" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
@@ -2034,25 +2034,25 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>C42 C45 C52 C55</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>100n 50V</t>
+          <t>10n C0G</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR71H104KA01L</t>
+          <t>GRM1885C1H103JA01D</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>MLCC 100 nF 50 V X7R 0805</t>
+          <t>MLCC 10 nF 50 V C0G 0603 (ADS1220 차동 필터)</t>
         </is>
       </c>
       <c r="J16" s="19" t="n">
@@ -2096,25 +2096,25 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C41 C51</t>
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>4.7u 50V</t>
+          <t>1n 100V</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>C_1210_3225Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
@@ -2124,19 +2124,19 @@
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>GRM32ER71H475KA88L</t>
+          <t>GRM188R72A102KA01D</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>MLCC 4.7 uF 50 V X7R 1210</t>
+          <t>MLCC 1 nF 100 V X7R 0603</t>
         </is>
       </c>
       <c r="J17" s="19" t="n">
-        <v>0.1</v>
+        <v>0.004</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="L17" s="20">
         <f>D17*J17</f>
@@ -2158,47 +2158,47 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C42 C45 C52 C55</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>SMDJ36CA</t>
+          <t>100n 50V</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>D_SMC</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>Littelfuse</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>SMDJ36CA</t>
+          <t>GRM21BR71H104KA01L</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
-          <t>TVS 3000 W 36 V 양방향 SMC (입력 1단)</t>
+          <t>MLCC 100 nF 50 V X7R 0805</t>
         </is>
       </c>
       <c r="J18" s="19" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="K18" s="19" t="n">
-        <v>0.6</v>
+        <v>0.03</v>
       </c>
       <c r="L18" s="20">
         <f>D18*J18</f>
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C43</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
@@ -2233,34 +2233,34 @@
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>SMBJ33CA</t>
+          <t>4.7u 50V</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>D_SMB</t>
+          <t>C_1210_3225Metric</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>Littelfuse</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>SMBJ33CA</t>
+          <t>GRM32ER71H475KA88L</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>TVS 600 W 33 V 양방향 SMB (입력 2단)</t>
+          <t>MLCC 4.7 uF 50 V X7R 1210 (소프트 터미네이션 권장 — 에폭시 응력)</t>
         </is>
       </c>
       <c r="J19" s="19" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L19" s="20">
         <f>D19*J19</f>
@@ -2287,39 +2287,39 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>D30 D40</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>TVS3301DRBR</t>
+          <t>SMDJ36CA</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>Texas_DRB0008A_PadFloat</t>
+          <t>D_SMC</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Littelfuse</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>TVS3301DRBR</t>
+          <t>SMDJ36CA</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장)</t>
+          <t>TVS 3000 W 36 V 양방향 SMC (입력 1단)</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="K20" s="19" t="n">
         <v>0.6</v>
@@ -2344,47 +2344,47 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>D2 D30 D40</t>
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>600R@100MHz</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>L_0603_1608Metric</t>
+          <t>Texas_DRB0008A_PadFloat</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>BLM18KG601SN1D</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>페라이트 비드 600 Ω@100 MHz 0603</t>
+          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장)</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="L21" s="20">
         <f>D21*J21</f>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>GDT1</t>
+          <t>D50</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
@@ -2419,34 +2419,34 @@
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>2035-23-SM</t>
+          <t>BZX84C27</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>GDT_Bourns_2035-xx-SM</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>Nexperia</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>2035-23-SM-RPLF</t>
+          <t>BZX84-C27,215</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>2전극 SMD GDT 230 V, Ø5 × 4.4 mm (회로 GND–외함). ※ 이전 2038은 3전극이라 교체</t>
+          <t>제너 27 V (25.1–28.9) SOT-23 — +Vs 이미터 폴로워 기준 (1 A, 2 NC, 3 K)</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="L22" s="20">
         <f>D22*J22</f>
@@ -2468,12 +2468,12 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="D23" s="18" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>600R@100MHz</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
+          <t>L_0603_1608Metric</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>BLM18KG601SN1D</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
+          <t>페라이트 비드 600 Ω@100 MHz 0603</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.8</v>
+        <v>0.03</v>
       </c>
       <c r="L23" s="20">
         <f>D23*J23</f>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>GDT1</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
@@ -2543,34 +2543,34 @@
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>TC2030-IDC-NL</t>
+          <t>2035-23-SM</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+          <t>GDT_Bourns_2035-xx-SM</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>(PCB 패드만)</t>
+          <t>2035-23-SM-RPLF</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>SWD 기록용 패드 — 부품 실장 없음</t>
+          <t>2전극 SMD GDT 230 V, Ø5 × 4.4 mm (회로 GND–외함). ※ 이전 2038은 3전극이라 교체</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="20">
         <f>D24*J24</f>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="N24" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D25" s="18" t="n">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>SM08B-GHS-TB</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
+          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
@@ -2620,19 +2620,19 @@
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>SM08B-GHS-TB</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
+          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L25" s="20">
         <f>D25*J25</f>
@@ -2654,12 +2654,12 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
@@ -2667,27 +2667,27 @@
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>CHASSIS wire</t>
+          <t>TC2030-IDC-NL</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>SolderWire_Chassis_D0.6mm</t>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>PCB 납땜 구멍 (부품 없음)</t>
+          <t>(PCB 패드만)</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
+          <t>SWD 기록용 패드 — 부품 실장 없음</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
@@ -2729,34 +2729,34 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>CMC 1mH 0.8A</t>
+          <t>SM04B-SRSS-TB</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>L_CommonMode_Wuerth_WE-SL2</t>
+          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>Würth</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>744222</t>
+          <t>SM04B-SRSS-TB</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>WE-SL2 공통모드 초크 2 × 1 mH, 0.8 A, 310 mΩ, 9.2 × 6 × 5 mm (권선 1–4, 2–3: 데이터시트로 확인)</t>
+          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="L27" s="20">
         <f>D27*J27</f>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
@@ -2791,34 +2791,34 @@
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>15uH</t>
+          <t>CHASSIS wire</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>L_Coilcraft_XAL4030-XXX</t>
+          <t>SolderWire_Chassis_D0.6mm</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>Coilcraft</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>XGL4030-153MEC</t>
+          <t>PCB 납땜 구멍 (부품 없음)</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 15 µH, 4 × 4 × 3.1 mm (XAL4030 풋프린트) — LMR36006 5 V·1 MHz 권장값</t>
+          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L28" s="20">
         <f>D28*J28</f>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
@@ -2853,34 +2853,34 @@
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>4.7R 1W pulse</t>
+          <t>CMC 1mH 0.8A</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>R_MELF_MMB-0207</t>
+          <t>L_CommonMode_Wuerth_WE-SL2</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Würth</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>MMB02070C4708FB200</t>
+          <t>744222</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>MELF 0207 박막 4.7 Ω 1% 1 W, AEC-Q200 (입력 직렬, 1단·2단 서지 분담)</t>
+          <t>WE-SL2 공통모드 초크 2 × 1 mH, 0.8 A, 310 mΩ, 9.2 × 6 × 5 mm (권선 1–4, 2–3: 데이터시트로 확인)</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="L29" s="20">
         <f>D29*J29</f>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
@@ -2915,34 +2915,34 @@
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>1M</t>
+          <t>15uH</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>L_Coilcraft_XAL4030-XXX</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Coilcraft</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-071ML</t>
+          <t>XGL4030-153MEC</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>저항 1 MΩ 1% 0603</t>
+          <t>파워 인덕터 15 µH, 4 × 4 × 3.1 mm (XAL4030 풋프린트) — LMR36006 5 V·1 MHz 권장값</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
-        <v>0.002</v>
+        <v>0.3</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>0.005</v>
+        <v>0.7</v>
       </c>
       <c r="L30" s="20">
         <f>D30*J30</f>
@@ -2964,12 +2964,12 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
@@ -2977,34 +2977,34 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>866k 1%</t>
+          <t>MMBTA06</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>onsemi / Nexperia</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-07866KL</t>
+          <t>MMBTA06LT1G</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
+          <t>NPN 80 V 0.5 A SOT-23 — TPS26611 +Vs 이미터 폴로워 (1 B, 2 E, 3 C)</t>
         </is>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="L31" s="20">
         <f>D31*J31</f>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
@@ -3039,34 +3039,34 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>97.6k 1%</t>
+          <t>4.7R 1W pulse</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_MELF_MMB-0207</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0797K6L</t>
+          <t>MMB02070C4708FB200</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP)</t>
+          <t>MELF 0207 박막 4.7 Ω 1% 1 W, AEC-Q200 (입력 직렬, 1단·2단 서지 분담)</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
-        <v>0.002</v>
+        <v>0.1</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>0.005</v>
+        <v>0.3</v>
       </c>
       <c r="L32" s="20">
         <f>D32*J32</f>
@@ -3078,7 +3078,7 @@
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -3088,12 +3088,12 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
@@ -3101,34 +3101,34 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>41.2k 1%</t>
+          <t>1M HV</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_1206_3216Metric</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>(HV 1206)</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0741K2L</t>
+          <t>품번 확인 필요 — 1 MΩ 1206 고전압 (사용 전압 ≥ 1 kV)</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>저항 41.2 kΩ 1% 0603 (OVP 29 V)</t>
+          <t>고전압 칩 저항 1 MΩ 1206, 사용 전압 ≥ 1 kV (GDT 방전 전 임펄스, v0.9: 일반 0603 → HV 1206)</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
-        <v>0.002</v>
+        <v>0.05</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>0.005</v>
+        <v>0.2</v>
       </c>
       <c r="L33" s="20">
         <f>D33*J33</f>
@@ -3138,9 +3138,9 @@
         <f>D33*K33</f>
         <v/>
       </c>
-      <c r="N33" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N33" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>80.6k 1%</t>
+          <t>866k 1%</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -3178,12 +3178,12 @@
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0780K6L</t>
+          <t>RC0603FR-07866KL</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
+          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="D35" s="18" t="n">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>100k 1%</t>
+          <t>97.6k 1%</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
@@ -3240,12 +3240,12 @@
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-07100KL</t>
+          <t>RC0603FR-0797K6L</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0603 (벅 FB)</t>
+          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP)</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>24.9k 1%</t>
+          <t>36.5k 1%</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0724K9L</t>
+          <t>RC0603FR-0736K5L</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>저항 24.9 kΩ 1% 0603 (벅 FB)</t>
+          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
         </is>
       </c>
       <c r="J36" s="19" t="n">
@@ -3336,20 +3336,20 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>R17 R18 R20</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="D37" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>80.6k 1%</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-071KL</t>
+          <t>RC0603FR-0780K6L</t>
         </is>
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>저항 1 kΩ 1% 0603</t>
+          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
         </is>
       </c>
       <c r="J37" s="19" t="n">
@@ -3398,20 +3398,20 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R8 R14</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>4.02k 0.02% 5ppm</t>
+          <t>100k 1%</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -3421,24 +3421,24 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>PLTT0603Z4021 (0.02 %, 5 ppm/K, 주문 접미사 확인)</t>
+          <t>RC0603FR-07100KL</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거)</t>
+          <t>저항 100 kΩ 1% 0603 (벅 FB, 전원 감시)</t>
         </is>
       </c>
       <c r="J38" s="19" t="n">
-        <v>1</v>
+        <v>0.002</v>
       </c>
       <c r="K38" s="19" t="n">
-        <v>4</v>
+        <v>0.005</v>
       </c>
       <c r="L38" s="20">
         <f>D38*J38</f>
@@ -3460,47 +3460,47 @@
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>R30 R40</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="D39" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>10R pulse</t>
+          <t>24.9k 1%</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>CRCW251210R0FKEGHP</t>
+          <t>RC0603FR-0724K9L</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬)</t>
+          <t>저항 24.9 kΩ 1% 0603 (벅 FB)</t>
         </is>
       </c>
       <c r="J39" s="19" t="n">
-        <v>0.05</v>
+        <v>0.002</v>
       </c>
       <c r="K39" s="19" t="n">
-        <v>0.15</v>
+        <v>0.005</v>
       </c>
       <c r="L39" s="20">
         <f>D39*J39</f>
@@ -3512,7 +3512,7 @@
       </c>
       <c r="N39" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -3527,11 +3527,11 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>R31 R33 R41</t>
+          <t>R10 R11 R33 R50 R60</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
@@ -3584,20 +3584,20 @@
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>R32 R42</t>
+          <t>R12 R13 R31 R41</t>
         </is>
       </c>
       <c r="D41" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>15k 0.1% 25ppm</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
@@ -3612,19 +3612,19 @@
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>RT0603BRD0715KL</t>
+          <t>RC0603FR-07100KL</t>
         </is>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
-          <t>저항 15 kΩ 0.1% 25 ppm/K 0603 (DAC8760 외부 ISET-R)</t>
+          <t>저항 100 kΩ 1% 0603</t>
         </is>
       </c>
       <c r="J41" s="19" t="n">
-        <v>0.02</v>
+        <v>0.002</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>0.06</v>
+        <v>0.005</v>
       </c>
       <c r="L41" s="20">
         <f>D41*J41</f>
@@ -3646,20 +3646,20 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>R34 R44</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>10R</t>
+          <t>10k 1%</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0710RL</t>
+          <t>RC0603FR-0710KL</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>저항 10 Ω 1% 0603 (DAC8760 AVDD 직렬, 데이터시트 10장)</t>
+          <t>저항 10 kΩ 1% 0603 (전원 감시 분압)</t>
         </is>
       </c>
       <c r="J42" s="19" t="n">
@@ -3708,47 +3708,47 @@
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R17 R18 R20</t>
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>RC0603FR-071KL</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
+          <t>저항 1 kΩ 1% 0603</t>
         </is>
       </c>
       <c r="J43" s="19" t="n">
-        <v>1.5</v>
+        <v>0.002</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>3</v>
+        <v>0.005</v>
       </c>
       <c r="L43" s="20">
         <f>D43*J43</f>
@@ -3760,7 +3760,7 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
@@ -3783,34 +3783,34 @@
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>LMR36006BRNXR</t>
+          <t>4.02k 0.02% 5ppm</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>Texas_RNX0012A_VQFN-HR-12_2x3mm</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>LMR36006BRNXR</t>
+          <t>PLTT0603Z4021 (0.02 %, 5 ppm/K, 주문 접미사 확인)</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm</t>
+          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거)</t>
         </is>
       </c>
       <c r="J44" s="19" t="n">
         <v>1</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>1.6</v>
+        <v>4</v>
       </c>
       <c r="L44" s="20">
         <f>D44*J44</f>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -3832,47 +3832,47 @@
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>R30 R40</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>10R pulse</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>CRCW251210R0FKEGHP</t>
         </is>
       </c>
       <c r="I45" s="17" t="inlineStr">
         <is>
-          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5</t>
+          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬)</t>
         </is>
       </c>
       <c r="J45" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="L45" s="20">
         <f>D45*J45</f>
@@ -3894,47 +3894,47 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>R32 R42</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>15k 0.1% 25ppm</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>LQFP-48_7x7mm_P0.5mm</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>RT0603BRD0715KL</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이)</t>
+          <t>저항 15 kΩ 0.1% 25 ppm/K 0603 (DAC8760 외부 ISET-R)</t>
         </is>
       </c>
       <c r="J46" s="19" t="n">
-        <v>1.5</v>
+        <v>0.02</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>2.5</v>
+        <v>0.06</v>
       </c>
       <c r="L46" s="20">
         <f>D46*J46</f>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="N46" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -3956,47 +3956,47 @@
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>R34 R44</t>
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>10R</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>ScioSense</t>
+          <t>Yageo</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>RC0603FR-0710RL</t>
         </is>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
-          <t>정전용량-디지털 변환기 QFN24</t>
+          <t>저항 10 Ω 1% 0603 (DAC8760 AVDD 직렬, 데이터시트 10장)</t>
         </is>
       </c>
       <c r="J47" s="19" t="n">
-        <v>6.5</v>
+        <v>0.002</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>7.1</v>
+        <v>0.005</v>
       </c>
       <c r="L47" s="20">
         <f>D47*J47</f>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -4018,12 +4018,12 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
         <is>
-          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
@@ -4046,19 +4046,19 @@
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
+          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
         </is>
       </c>
       <c r="J48" s="19" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="L48" s="20">
         <f>D48*J48</f>
@@ -4080,25 +4080,25 @@
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>U7 U8</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>DAC8760IPWP</t>
+          <t>LMR36006BRNXR</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
+          <t>Texas_RNX0012A_VQFN-HR-12_2x3mm</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
@@ -4108,19 +4108,19 @@
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>DAC8760IPWPR</t>
+          <t>LMR36006BRNXR</t>
         </is>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
+          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm</t>
         </is>
       </c>
       <c r="J49" s="19" t="n">
-        <v>7.8</v>
+        <v>1</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>12.4</v>
+        <v>1.6</v>
       </c>
       <c r="L49" s="20">
         <f>D49*J49</f>
@@ -4142,25 +4142,25 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>U9 U10</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-8</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
@@ -4170,19 +4170,19 @@
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
+          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5</t>
         </is>
       </c>
       <c r="J50" s="19" t="n">
-        <v>1.2</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="L50" s="20">
         <f>D50*J50</f>
@@ -4204,12 +4204,12 @@
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>MCU</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
@@ -4217,34 +4217,34 @@
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>THVD2450DR</t>
+          <t>STM32G0B1CCT3</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>LQFP-48_7x7mm_P0.5mm</t>
         </is>
       </c>
       <c r="G51" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>THVD2450DR</t>
+          <t>STM32G0B1CCT3</t>
         </is>
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
-          <t>RS-485 트랜시버, 버스 ±70 V 내성, SOIC-8</t>
+          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이)</t>
         </is>
       </c>
       <c r="J51" s="19" t="n">
         <v>1.5</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L51" s="20">
         <f>D51*J51</f>
@@ -4266,47 +4266,47 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>U12 U13</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="F52" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ScioSense</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
+          <t>정전용량-디지털 변환기 QFN24</t>
         </is>
       </c>
       <c r="J52" s="19" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>1.1</v>
+        <v>7.1</v>
       </c>
       <c r="L52" s="20">
         <f>D52*J52</f>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="N52" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -4328,12 +4328,12 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -4341,12 +4341,12 @@
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
+          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
@@ -4356,19 +4356,19 @@
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
+          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
         </is>
       </c>
       <c r="J53" s="19" t="n">
-        <v>0.08</v>
+        <v>1.9</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>0.2</v>
+        <v>3.5</v>
       </c>
       <c r="L53" s="20">
         <f>D53*J53</f>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="N53" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -4390,47 +4390,47 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>기판</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>U7 U8</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>DAC8760IPWP</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>HMT500(260313A) (E-301)</t>
+          <t>DAC8760IPWPR</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
+          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
         </is>
       </c>
       <c r="J54" s="19" t="n">
-        <v>0.8</v>
+        <v>7.8</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>2</v>
+        <v>12.4</v>
       </c>
       <c r="L54" s="20">
         <f>D54*J54</f>
@@ -4440,9 +4440,9 @@
         <f>D54*K54</f>
         <v/>
       </c>
-      <c r="N54" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -4452,47 +4452,47 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>U9 U10</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SOT-23-8</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>MK33-W mini (150138)</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
-          <t>정전용량 습도 소자 200 pF (센서 프로브 P-202에 실장)</t>
+          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
         </is>
       </c>
       <c r="J55" s="19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L55" s="20">
         <f>D55*J55</f>
@@ -4502,9 +4502,9 @@
         <f>D55*K55</f>
         <v/>
       </c>
-      <c r="N55" s="21" t="inlineStr">
-        <is>
-          <t>사내 단가</t>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -4514,12 +4514,12 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
@@ -4527,31 +4527,31 @@
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>THVD2410DR</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>MiniSens Pt1000 F0.1</t>
+          <t>THVD2410DR</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
+          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, SOIC-8 — THVD2450과 같은 핀 (v0.9)</t>
         </is>
       </c>
       <c r="J56" s="19" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="K56" s="19" t="n">
         <v>3</v>
@@ -4564,9 +4564,9 @@
         <f>D56*K56</f>
         <v/>
       </c>
-      <c r="N56" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
         </is>
       </c>
     </row>
@@ -4576,47 +4576,47 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>P-204</t>
+          <t>U12 U13</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>M Connect</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>TBD (두텍 사용품)</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
-          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
+          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
         </is>
       </c>
       <c r="J57" s="19" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>10</v>
+        <v>1.1</v>
       </c>
       <c r="L57" s="20">
         <f>D57*J57</f>
@@ -4626,9 +4626,9 @@
         <f>D57*K57</f>
         <v/>
       </c>
-      <c r="N57" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="N57" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -4638,12 +4638,12 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>GHR-08V-S</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
+          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
         </is>
       </c>
       <c r="J58" s="19" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="L58" s="20">
         <f>D58*J58</f>
@@ -4700,16 +4700,16 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>기판</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
@@ -4723,24 +4723,24 @@
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>SSHL-002T-P0.2</t>
+          <t>HMT500(260313A) (E-301)</t>
         </is>
       </c>
       <c r="I59" s="17" t="inlineStr">
         <is>
-          <t>GH 크림프 단자 AWG 30–26</t>
+          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
         </is>
       </c>
       <c r="J59" s="19" t="n">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="L59" s="20">
         <f>D59*J59</f>
@@ -4750,9 +4750,9 @@
         <f>D59*K59</f>
         <v/>
       </c>
-      <c r="N59" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N59" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
         </is>
       </c>
     </row>
@@ -4762,12 +4762,12 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
@@ -4785,24 +4785,24 @@
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG28 전선</t>
+          <t>MK33-W mini (150138)</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+          <t>정전용량 습도 소자 200 pF (센서 프로브 P-202에 실장)</t>
         </is>
       </c>
       <c r="J60" s="19" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K60" s="19" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L60" s="20">
         <f>D60*J60</f>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="N60" s="21" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>사내 단가</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
@@ -4847,24 +4847,24 @@
       </c>
       <c r="G61" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>SHR-04V-S</t>
+          <t>MiniSens Pt1000 F0.1</t>
         </is>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
+          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
         </is>
       </c>
       <c r="J61" s="19" t="n">
-        <v>0.04</v>
+        <v>0.5</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="L61" s="20">
         <f>D61*J61</f>
@@ -4874,9 +4874,9 @@
         <f>D61*K61</f>
         <v/>
       </c>
-      <c r="N61" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N61" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
         </is>
       </c>
     </row>
@@ -4886,16 +4886,16 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>P-204</t>
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
@@ -4909,24 +4909,24 @@
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>M Connect</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>SSH-003T-P0.2-H</t>
+          <t>TBD (두텍 사용품)</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>SH 크림프 단자 AWG 32–28</t>
+          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
         </is>
       </c>
       <c r="J62" s="19" t="n">
-        <v>0.03</v>
+        <v>2</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>0.06</v>
+        <v>10</v>
       </c>
       <c r="L62" s="20">
         <f>D62*J62</f>
@@ -4936,9 +4936,9 @@
         <f>D62*K62</f>
         <v/>
       </c>
-      <c r="N62" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N62" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="D63" s="18" t="n">
@@ -4971,24 +4971,24 @@
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG30 전선</t>
+          <t>GHR-08V-S</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
         </is>
       </c>
       <c r="J63" s="19" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="L63" s="20">
         <f>D63*J63</f>
@@ -4998,9 +4998,9 @@
         <f>D63*K63</f>
         <v/>
       </c>
-      <c r="N63" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
     </row>
@@ -5010,47 +5010,47 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>조립</t>
+          <t>하네스</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="D64" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D64" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="16" t="inlineStr">
+      <c r="F64" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F64" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>SMT 양면 실장</t>
+          <t>SSHL-002T-P0.2</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>1k 기준 조립비</t>
+          <t>GH 크림프 단자 AWG 30–26</t>
         </is>
       </c>
       <c r="J64" s="19" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="K64" s="19" t="n">
-        <v>4</v>
+        <v>0.06</v>
       </c>
       <c r="L64" s="20">
         <f>D64*J64</f>
@@ -5060,24 +5060,334 @@
         <f>D64*K64</f>
         <v/>
       </c>
-      <c r="N64" s="21" t="inlineStr">
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C65" s="17" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="D65" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H65" s="17" t="inlineStr">
+        <is>
+          <t>PTFE AWG28 전선</t>
+        </is>
+      </c>
+      <c r="I65" s="17" t="inlineStr">
+        <is>
+          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+        </is>
+      </c>
+      <c r="J65" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K65" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L65" s="20">
+        <f>D65*J65</f>
+        <v/>
+      </c>
+      <c r="M65" s="20">
+        <f>D65*K65</f>
+        <v/>
+      </c>
+      <c r="N65" s="21" t="inlineStr">
         <is>
           <t>추정</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="I65" s="3" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="H66" s="17" t="inlineStr">
+        <is>
+          <t>SHR-04V-S</t>
+        </is>
+      </c>
+      <c r="I66" s="17" t="inlineStr">
+        <is>
+          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
+        </is>
+      </c>
+      <c r="J66" s="19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K66" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L66" s="20">
+        <f>D66*J66</f>
+        <v/>
+      </c>
+      <c r="M66" s="20">
+        <f>D66*K66</f>
+        <v/>
+      </c>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C67" s="17" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="D67" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="H67" s="17" t="inlineStr">
+        <is>
+          <t>SSH-003T-P0.2-H</t>
+        </is>
+      </c>
+      <c r="I67" s="17" t="inlineStr">
+        <is>
+          <t>SH 크림프 단자 AWG 32–28</t>
+        </is>
+      </c>
+      <c r="J67" s="19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K67" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L67" s="20">
+        <f>D67*J67</f>
+        <v/>
+      </c>
+      <c r="M67" s="20">
+        <f>D67*K67</f>
+        <v/>
+      </c>
+      <c r="N67" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C68" s="17" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="D68" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H68" s="17" t="inlineStr">
+        <is>
+          <t>PTFE AWG30 전선</t>
+        </is>
+      </c>
+      <c r="I68" s="17" t="inlineStr">
+        <is>
+          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+        </is>
+      </c>
+      <c r="J68" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K68" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L68" s="20">
+        <f>D68*J68</f>
+        <v/>
+      </c>
+      <c r="M68" s="20">
+        <f>D68*K68</f>
+        <v/>
+      </c>
+      <c r="N68" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>조립</t>
+        </is>
+      </c>
+      <c r="C69" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F69" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" s="17" t="inlineStr">
+        <is>
+          <t>SMT 양면 실장</t>
+        </is>
+      </c>
+      <c r="I69" s="17" t="inlineStr">
+        <is>
+          <t>1k 기준 조립비</t>
+        </is>
+      </c>
+      <c r="J69" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K69" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L69" s="20">
+        <f>D69*J69</f>
+        <v/>
+      </c>
+      <c r="M69" s="20">
+        <f>D69*K69</f>
+        <v/>
+      </c>
+      <c r="N69" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="I70" s="3" t="inlineStr">
         <is>
           <t>합계 (1대분)</t>
         </is>
       </c>
-      <c r="L65" s="23">
-        <f>SUM(L2:L64)</f>
-        <v/>
-      </c>
-      <c r="M65" s="23">
-        <f>SUM(M2:M64)</f>
+      <c r="L70" s="23">
+        <f>SUM(L2:L69)</f>
+        <v/>
+      </c>
+      <c r="M70" s="23">
+        <f>SUM(M2:M69)</f>
         <v/>
       </c>
     </row>

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>220p C0G 1%</t>
+          <t>330p C0G 1%</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>GRM1885C1H221FA01D</t>
+          <t>GRM1885C1H331FA01D</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>MLCC 220 pF 50 V C0G ±1% 0603 (PCAP04 기준 C)</t>
+          <t>MLCC 330 pF 50 V C0G ±1% 0603 (PCAP04 기준 C, 센서 MK33-W 300 pF)</t>
         </is>
       </c>
       <c r="J14" s="19" t="n">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>MK33-W mini (150138)</t>
+          <t>MK33-W (300 pF, 품번 확인 필요)</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>정전용량 습도 소자 200 pF (센서 프로브 P-202에 실장)</t>
+          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
         </is>
       </c>
       <c r="J60" s="19" t="n">

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -262,9 +262,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:N69" headerRowCount="1">
-  <autoFilter ref="A1:N69"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P69" headerRowCount="1">
+  <autoFilter ref="A1:P69"/>
+  <tableColumns count="16">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="분류"/>
     <tableColumn id="3" name="참조번호"/>
@@ -279,6 +279,8 @@
     <tableColumn id="12" name="금액 하한 (USD)"/>
     <tableColumn id="13" name="금액 상한 (USD)"/>
     <tableColumn id="14" name="상태"/>
+    <tableColumn id="15" name="LCSC"/>
+    <tableColumn id="16" name="JLC 구분"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
 </table>
@@ -1069,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1086,6 +1088,8 @@
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1159,6 +1163,16 @@
           <t>상태</t>
         </is>
       </c>
+      <c r="O1" s="15" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="P1" s="15" t="inlineStr">
+        <is>
+          <t>JLC 구분</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="16" t="n">
@@ -1189,12 +1203,12 @@
       </c>
       <c r="G2" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H2" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR72A104KA35L</t>
+          <t>CL21B104KCFNNNE</t>
         </is>
       </c>
       <c r="I2" s="17" t="inlineStr">
@@ -1219,6 +1233,16 @@
       <c r="N2" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>C28233</t>
+        </is>
+      </c>
+      <c r="P2" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1283,6 +1307,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O3" s="16" t="inlineStr">
+        <is>
+          <t>C86054</t>
+        </is>
+      </c>
+      <c r="P3" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="n">
@@ -1303,7 +1337,7 @@
       </c>
       <c r="E4" s="16" t="inlineStr">
         <is>
-          <t>4.7n 2kV Y2</t>
+          <t>4.7n 2kV</t>
         </is>
       </c>
       <c r="F4" s="16" t="inlineStr">
@@ -1313,24 +1347,24 @@
       </c>
       <c r="G4" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t>GA343QR7GF472KW01L</t>
+          <t>CC1812KKX7RDBB472</t>
         </is>
       </c>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>Safety cap 4.7 nF Y2 (250 VAC) 1812</t>
+          <t>MLCC 4.7 nF 2 kV X7R 1812 (GND–외함. LCSC에 Y2 1812 없음 — DC 기기라 Y2 불필요)</t>
         </is>
       </c>
       <c r="J4" s="19" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="K4" s="19" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="L4" s="20">
         <f>D4*J4</f>
@@ -1342,7 +1376,17 @@
       </c>
       <c r="N4" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O4" s="16" t="inlineStr">
+        <is>
+          <t>C309511</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1419,12 @@
       </c>
       <c r="G5" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>GRM188R71H223KA01D</t>
+          <t>CL10B223KB8NNNC</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
@@ -1405,6 +1449,16 @@
       <c r="N5" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>C21122</t>
+        </is>
+      </c>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1469,6 +1523,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O6" s="16" t="inlineStr">
+        <is>
+          <t>C77102</t>
+        </is>
+      </c>
+      <c r="P6" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n">
@@ -1494,22 +1558,22 @@
       </c>
       <c r="F7" s="16" t="inlineStr">
         <is>
-          <t>C_1206_3216Metric</t>
+          <t>C_1210_3225Metric</t>
         </is>
       </c>
       <c r="G7" s="16" t="inlineStr">
         <is>
-          <t>(X7R 1206)</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H7" s="17" t="inlineStr">
         <is>
-          <t>품번 확인 필요 — X7R 22 µF 25 V 1206</t>
+          <t>GRM32ER71E226ME15L</t>
         </is>
       </c>
       <c r="I7" s="17" t="inlineStr">
         <is>
-          <t>MLCC 22 uF 25 V X7R 1206 (벅 출력 2개, LMR36006 X7R 요구, v0.9: X5R 금지)</t>
+          <t>MLCC 22 uF 25 V X7R 1210 (벅 출력 2개, LMR36006 X7R 요구. LCSC에 1206 X7R 없음 → 1210)</t>
         </is>
       </c>
       <c r="J7" s="19" t="n">
@@ -1526,9 +1590,19 @@
         <f>D7*K7</f>
         <v/>
       </c>
-      <c r="N7" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O7" s="16" t="inlineStr">
+        <is>
+          <t>C424136</t>
+        </is>
+      </c>
+      <c r="P7" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -1561,12 +1635,12 @@
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>GRM188R71H104KA93D</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
@@ -1591,6 +1665,16 @@
       <c r="N8" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O8" s="16" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
+      <c r="P8" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1717,7 @@
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>MLCC 1 uF 25 V X7R 0603 (v0.9: X5R → X7R, 몰딩 후 85 °C 초과)</t>
+          <t>MLCC 1 uF 25 V X7R 0603 (v0.9: X5R → X7R, 몰딩 후 85 °C 초과) [LCSC: Basic 1 µF(C15849)는 X5R이라 쓰지 않음]</t>
         </is>
       </c>
       <c r="J9" s="19" t="n">
@@ -1653,6 +1737,16 @@
       <c r="N9" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>C86020</t>
+        </is>
+      </c>
+      <c r="P9" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1779,12 @@
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>GRM1885C1H200JA01D</t>
+          <t>CL10C200JB8NNNC</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
@@ -1715,6 +1809,16 @@
       <c r="N10" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>C1648</t>
+        </is>
+      </c>
+      <c r="P10" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1779,6 +1883,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>C77093</t>
+        </is>
+      </c>
+      <c r="P11" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n">
@@ -1804,22 +1918,22 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>(X7R 0603)</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>품번 확인 필요 — X7R 220 nF 100 V 0603</t>
+          <t>CL21B224KCFSFNE</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>MLCC 220 nF 100 V X7R 0603 (LMR36006 VIN–PGND 핀마다)</t>
+          <t>MLCC 220 nF 100 V X7R 0805 (LMR36006 VIN–PGND 핀마다. LCSC에 0603 없음 → 0805)</t>
         </is>
       </c>
       <c r="J12" s="19" t="n">
@@ -1836,9 +1950,19 @@
         <f>D12*K12</f>
         <v/>
       </c>
-      <c r="N12" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>C307542</t>
+        </is>
+      </c>
+      <c r="P12" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -1903,6 +2027,16 @@
           <t>확인 필요</t>
         </is>
       </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>C162427</t>
+        </is>
+      </c>
+      <c r="P13" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n">
@@ -1933,17 +2067,17 @@
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>GRM1885C1H331FA01D</t>
+          <t>VJ0603A331GXACW1BC</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>MLCC 330 pF 50 V C0G ±1% 0603 (PCAP04 기준 C, 센서 MK33-W 300 pF)</t>
+          <t>MLCC 330 pF 50 V C0G ±1% 0603 (PCAP04 기준 C, 센서 MK33-W 300 pF) [LCSC: ±2 % (LCSC에 ±1 % 없음) — 기준 C 절대값은 교정으로 제거, C0G라 온도 안정]</t>
         </is>
       </c>
       <c r="J14" s="19" t="n">
@@ -1963,6 +2097,16 @@
       <c r="N14" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>C3898227</t>
+        </is>
+      </c>
+      <c r="P14" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2027,6 +2171,16 @@
           <t>확인 필요</t>
         </is>
       </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>C91604</t>
+        </is>
+      </c>
+      <c r="P15" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n">
@@ -2089,6 +2243,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O16" s="16" t="inlineStr">
+        <is>
+          <t>C85973</t>
+        </is>
+      </c>
+      <c r="P16" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="n">
@@ -2151,6 +2315,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O17" s="16" t="inlineStr">
+        <is>
+          <t>C97897</t>
+        </is>
+      </c>
+      <c r="P17" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="n">
@@ -2181,12 +2355,12 @@
       </c>
       <c r="G18" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR71H104KA01L</t>
+          <t>CC0805KRX7R9BB104</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
@@ -2211,6 +2385,16 @@
       <c r="N18" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O18" s="16" t="inlineStr">
+        <is>
+          <t>C49678</t>
+        </is>
+      </c>
+      <c r="P18" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -2275,6 +2459,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O19" s="16" t="inlineStr">
+        <is>
+          <t>C86052</t>
+        </is>
+      </c>
+      <c r="P19" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n">
@@ -2310,19 +2504,19 @@
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>SMDJ36CA</t>
+          <t>5.0SMDJ36CA</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>TVS 3000 W 36 V 양방향 SMC (입력 1단)</t>
+          <t>TVS 5000 W 36 V 양방향 SMC (입력 1단. LCSC — 같은 36 V·SMC, 3 kW → 5 kW)</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L20" s="20">
         <f>D20*J20</f>
@@ -2334,7 +2528,17 @@
       </c>
       <c r="N20" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O20" s="16" t="inlineStr">
+        <is>
+          <t>C141713</t>
+        </is>
+      </c>
+      <c r="P20" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2581,7 @@
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장)</t>
+          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: 재고 적음 (검색 시 약 88개)]</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
@@ -2397,6 +2601,16 @@
       <c r="N21" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>C2864392</t>
+        </is>
+      </c>
+      <c r="P21" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2461,6 +2675,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>C96229</t>
+        </is>
+      </c>
+      <c r="P22" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="n">
@@ -2501,7 +2725,7 @@
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>페라이트 비드 600 Ω@100 MHz 0603</t>
+          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
@@ -2521,6 +2745,16 @@
       <c r="N23" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>C85833</t>
+        </is>
+      </c>
+      <c r="P23" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2777,7 @@
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>2035-23-SM</t>
+          <t>2035-25-SM</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
@@ -2558,12 +2792,12 @@
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2035-23-SM-RPLF</t>
+          <t>2035-25-SM-RPLF</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>2전극 SMD GDT 230 V, Ø5 × 4.4 mm (회로 GND–외함). ※ 이전 2038은 3전극이라 교체</t>
+          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
@@ -2582,7 +2816,17 @@
       </c>
       <c r="N24" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O24" s="16" t="inlineStr">
+        <is>
+          <t>C3660127</t>
+        </is>
+      </c>
+      <c r="P24" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2864,7 @@
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>SM08B-GHS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
@@ -2645,6 +2889,16 @@
       <c r="N25" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>C265111</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2709,6 +2963,8 @@
           <t>확정</t>
         </is>
       </c>
+      <c r="O26" s="16" t="inlineStr"/>
+      <c r="P26" s="16" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n">
@@ -2744,7 +3000,7 @@
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>SM04B-SRSS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
@@ -2769,6 +3025,16 @@
       <c r="N27" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O27" s="16" t="inlineStr">
+        <is>
+          <t>C160404</t>
+        </is>
+      </c>
+      <c r="P27" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2833,6 +3099,8 @@
           <t>확정</t>
         </is>
       </c>
+      <c r="O28" s="16" t="inlineStr"/>
+      <c r="P28" s="16" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="n">
@@ -2863,24 +3131,24 @@
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>Würth</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>744222</t>
+          <t>SRF0905-102Y</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>WE-SL2 공통모드 초크 2 × 1 mH, 0.8 A, 310 mΩ, 9.2 × 6 × 5 mm (권선 1–4, 2–3: 데이터시트로 확인)</t>
+          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="L29" s="20">
         <f>D29*J29</f>
@@ -2890,9 +3158,19 @@
         <f>D29*K29</f>
         <v/>
       </c>
-      <c r="N29" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N29" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>C2651138</t>
+        </is>
+      </c>
+      <c r="P29" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2920,7 +3198,7 @@
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>L_Coilcraft_XAL4030-XXX</t>
+          <t>L_Coilcraft_XAL4040-XXX</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
@@ -2930,12 +3208,12 @@
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>XGL4030-153MEC</t>
+          <t>XGL4040-153MEC</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 15 µH, 4 × 4 × 3.1 mm (XAL4030 풋프린트) — LMR36006 5 V·1 MHz 권장값</t>
+          <t>파워 인덕터 15 µH 3.6 A, 4 × 4 × 4.0 mm (XAL4040 풋프린트. LCSC — 4030형은 LCSC에 없음)</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
@@ -2954,7 +3232,17 @@
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>C3911667</t>
+        </is>
+      </c>
+      <c r="P30" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2987,7 +3275,7 @@
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>onsemi / Nexperia</t>
+          <t>onsemi</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
@@ -3017,6 +3305,16 @@
       <c r="N31" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>C77760</t>
+        </is>
+      </c>
+      <c r="P31" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3342,7 @@
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>R_MELF_MMB-0207</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
@@ -3054,12 +3352,12 @@
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>MMB02070C4708FB200</t>
+          <t>CRCW25124R70FKEGHP</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>MELF 0207 박막 4.7 Ω 1% 1 W, AEC-Q200 (입력 직렬, 1단·2단 서지 분담)</t>
+          <t>CRCW-HP 2512 4.7 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (입력 직렬, 1단·2단 서지 분담). MELF → 2512 (결정 #34) [LCSC: 펄스 내성(HP)형은 LCSC에 없음. LCSC 일반형 CRCW25124R70FKEG C242563은 서지 에너지 확인 후에만]</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
@@ -3078,7 +3376,13 @@
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>글로벌 소싱</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr"/>
+      <c r="P32" s="16" t="inlineStr">
+        <is>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -3111,24 +3415,24 @@
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>(HV 1206)</t>
+          <t>ROHM</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>품번 확인 필요 — 1 MΩ 1206 고전압 (사용 전압 ≥ 1 kV)</t>
+          <t>KTR18EZPF1004</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>고전압 칩 저항 1 MΩ 1206, 사용 전압 ≥ 1 kV (GDT 방전 전 임펄스, v0.9: 일반 0603 → HV 1206)</t>
+          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
       <c r="L33" s="20">
         <f>D33*J33</f>
@@ -3138,9 +3442,19 @@
         <f>D33*K33</f>
         <v/>
       </c>
-      <c r="N33" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O33" s="16" t="inlineStr">
+        <is>
+          <t>C253347</t>
+        </is>
+      </c>
+      <c r="P33" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3173,12 +3487,12 @@
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-07866KL</t>
+          <t>RCS0603866KFKEA</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
@@ -3203,6 +3517,16 @@
       <c r="N34" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="inlineStr">
+        <is>
+          <t>C3954581</t>
+        </is>
+      </c>
+      <c r="P34" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3235,17 +3559,17 @@
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0797K6L</t>
+          <t>ERA-3AEB9762V</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP)</t>
+          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">
@@ -3265,6 +3589,16 @@
       <c r="N35" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O35" s="16" t="inlineStr">
+        <is>
+          <t>C2074558</t>
+        </is>
+      </c>
+      <c r="P35" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3631,12 @@
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>CAL-CHIP</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0736K5L</t>
+          <t>RM06F3652CT</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
@@ -3327,6 +3661,16 @@
       <c r="N36" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O36" s="16" t="inlineStr">
+        <is>
+          <t>C4027587</t>
+        </is>
+      </c>
+      <c r="P36" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3359,12 +3703,12 @@
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0780K6L</t>
+          <t>0603WAF8062T5E</t>
         </is>
       </c>
       <c r="I37" s="17" t="inlineStr">
@@ -3389,6 +3733,16 @@
       <c r="N37" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O37" s="16" t="inlineStr">
+        <is>
+          <t>C23249</t>
+        </is>
+      </c>
+      <c r="P37" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3421,12 +3775,12 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-07100KL</t>
+          <t>0603WAF1003T5E</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
@@ -3451,6 +3805,16 @@
       <c r="N38" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O38" s="16" t="inlineStr">
+        <is>
+          <t>C25803</t>
+        </is>
+      </c>
+      <c r="P38" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -3483,12 +3847,12 @@
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0724K9L</t>
+          <t>0603WAF2492T5E</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
@@ -3513,6 +3877,16 @@
       <c r="N39" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O39" s="16" t="inlineStr">
+        <is>
+          <t>C25962</t>
+        </is>
+      </c>
+      <c r="P39" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3545,12 +3919,12 @@
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0710KL</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
@@ -3575,6 +3949,16 @@
       <c r="N40" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O40" s="16" t="inlineStr">
+        <is>
+          <t>C25804</t>
+        </is>
+      </c>
+      <c r="P40" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -3607,12 +3991,12 @@
       </c>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-07100KL</t>
+          <t>0603WAF1003T5E</t>
         </is>
       </c>
       <c r="I41" s="17" t="inlineStr">
@@ -3637,6 +4021,16 @@
       <c r="N41" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>C25803</t>
+        </is>
+      </c>
+      <c r="P41" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -3669,12 +4063,12 @@
       </c>
       <c r="G42" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0710KL</t>
+          <t>0603WAF1002T5E</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
@@ -3699,6 +4093,16 @@
       <c r="N42" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="inlineStr">
+        <is>
+          <t>C25804</t>
+        </is>
+      </c>
+      <c r="P42" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -3731,12 +4135,12 @@
       </c>
       <c r="G43" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-071KL</t>
+          <t>0603WAF1001T5E</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
@@ -3761,6 +4165,16 @@
       <c r="N43" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>C21190</t>
+        </is>
+      </c>
+      <c r="P43" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -3798,12 +4212,12 @@
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>PLTT0603Z4021 (0.02 %, 5 ppm/K, 주문 접미사 확인)</t>
+          <t>PLTT0603Z4021</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거)</t>
+          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거) [LCSC: LCSC 최선 ERA-3AEB4021V C491130 (0.1 %·25 ppm)은 Pt1000 정확도 약 5배 나빠 쓰지 않음]</t>
         </is>
       </c>
       <c r="J44" s="19" t="n">
@@ -3823,6 +4237,12 @@
       <c r="N44" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="inlineStr"/>
+      <c r="P44" s="16" t="inlineStr">
+        <is>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -3865,7 +4285,7 @@
       </c>
       <c r="I45" s="17" t="inlineStr">
         <is>
-          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬)</t>
+          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬) [LCSC: LCSC 일반형 CRCW251210R0FKEG C844885는 서지 에너지 확인 후에만]</t>
         </is>
       </c>
       <c r="J45" s="19" t="n">
@@ -3884,7 +4304,13 @@
       </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>글로벌 소싱</t>
+        </is>
+      </c>
+      <c r="O45" s="16" t="inlineStr"/>
+      <c r="P45" s="16" t="inlineStr">
+        <is>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -3917,12 +4343,12 @@
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>RT0603BRD0715KL</t>
+          <t>ERA-3AEB153V</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
@@ -3947,6 +4373,16 @@
       <c r="N46" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O46" s="16" t="inlineStr">
+        <is>
+          <t>C473244</t>
+        </is>
+      </c>
+      <c r="P46" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3979,12 +4415,12 @@
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>Yageo</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>RC0603FR-0710RL</t>
+          <t>0603WAF100JT5E</t>
         </is>
       </c>
       <c r="I47" s="17" t="inlineStr">
@@ -4009,6 +4445,16 @@
       <c r="N47" s="16" t="inlineStr">
         <is>
           <t>제안</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>C22859</t>
+        </is>
+      </c>
+      <c r="P47" s="16" t="inlineStr">
+        <is>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4073,6 +4519,16 @@
           <t>확정</t>
         </is>
       </c>
+      <c r="O48" s="16" t="inlineStr">
+        <is>
+          <t>C544399</t>
+        </is>
+      </c>
+      <c r="P48" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="n">
@@ -4113,7 +4569,7 @@
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm</t>
+          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm [LCSC: LCSC에 없음 (차량용 LMR36006FSCQRNXRQ1 C2869760은 다른 품번·재고 16개)]</t>
         </is>
       </c>
       <c r="J49" s="19" t="n">
@@ -4133,6 +4589,12 @@
       <c r="N49" s="16" t="inlineStr">
         <is>
           <t>확정</t>
+        </is>
+      </c>
+      <c r="O49" s="16" t="inlineStr"/>
+      <c r="P49" s="16" t="inlineStr">
+        <is>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4637,7 @@
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5</t>
+          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
         </is>
       </c>
       <c r="J50" s="19" t="n">
@@ -4195,6 +4657,16 @@
       <c r="N50" s="16" t="inlineStr">
         <is>
           <t>확정</t>
+        </is>
+      </c>
+      <c r="O50" s="16" t="inlineStr">
+        <is>
+          <t>C2862740</t>
+        </is>
+      </c>
+      <c r="P50" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4237,7 +4709,7 @@
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
-          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이)</t>
+          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이) [LCSC: LCSC엔 85 °C 등급 CCT6 C5270241만 — 몰딩 내부 온도 때문에 125 °C 등급 유지]</t>
         </is>
       </c>
       <c r="J51" s="19" t="n">
@@ -4257,6 +4729,12 @@
       <c r="N51" s="16" t="inlineStr">
         <is>
           <t>확정</t>
+        </is>
+      </c>
+      <c r="O51" s="16" t="inlineStr"/>
+      <c r="P51" s="16" t="inlineStr">
+        <is>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -4321,6 +4799,16 @@
           <t>확정</t>
         </is>
       </c>
+      <c r="O52" s="16" t="inlineStr">
+        <is>
+          <t>C2829318</t>
+        </is>
+      </c>
+      <c r="P52" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="n">
@@ -4383,6 +4871,16 @@
           <t>확정</t>
         </is>
       </c>
+      <c r="O53" s="16" t="inlineStr">
+        <is>
+          <t>C48263</t>
+        </is>
+      </c>
+      <c r="P53" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="n">
@@ -4445,6 +4943,16 @@
           <t>확정</t>
         </is>
       </c>
+      <c r="O54" s="16" t="inlineStr">
+        <is>
+          <t>C55047</t>
+        </is>
+      </c>
+      <c r="P54" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="n">
@@ -4507,6 +5015,16 @@
           <t>확정</t>
         </is>
       </c>
+      <c r="O55" s="16" t="inlineStr">
+        <is>
+          <t>C3148140</t>
+        </is>
+      </c>
+      <c r="P55" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="n">
@@ -4569,6 +5087,16 @@
           <t>확정</t>
         </is>
       </c>
+      <c r="O56" s="16" t="inlineStr">
+        <is>
+          <t>C1849398</t>
+        </is>
+      </c>
+      <c r="P56" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="n">
@@ -4631,6 +5159,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O57" s="16" t="inlineStr">
+        <is>
+          <t>C221351</t>
+        </is>
+      </c>
+      <c r="P57" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="n">
@@ -4693,6 +5231,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O58" s="16" t="inlineStr">
+        <is>
+          <t>C91874</t>
+        </is>
+      </c>
+      <c r="P58" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="n">
@@ -4755,6 +5303,8 @@
           <t>추정</t>
         </is>
       </c>
+      <c r="O59" s="16" t="inlineStr"/>
+      <c r="P59" s="16" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="n">
@@ -4817,6 +5367,8 @@
           <t>사내 단가</t>
         </is>
       </c>
+      <c r="O60" s="16" t="inlineStr"/>
+      <c r="P60" s="16" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="n">
@@ -4879,6 +5431,8 @@
           <t>추정</t>
         </is>
       </c>
+      <c r="O61" s="16" t="inlineStr"/>
+      <c r="P61" s="16" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="n">
@@ -4941,6 +5495,8 @@
           <t>TBD</t>
         </is>
       </c>
+      <c r="O62" s="16" t="inlineStr"/>
+      <c r="P62" s="16" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="n">
@@ -5003,6 +5559,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O63" s="16" t="inlineStr">
+        <is>
+          <t>C485357</t>
+        </is>
+      </c>
+      <c r="P63" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="n">
@@ -5065,6 +5631,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O64" s="16" t="inlineStr">
+        <is>
+          <t>C189897</t>
+        </is>
+      </c>
+      <c r="P64" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="n">
@@ -5127,6 +5703,8 @@
           <t>추정</t>
         </is>
       </c>
+      <c r="O65" s="16" t="inlineStr"/>
+      <c r="P65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="n">
@@ -5189,6 +5767,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O66" s="16" t="inlineStr">
+        <is>
+          <t>C385125</t>
+        </is>
+      </c>
+      <c r="P66" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="n">
@@ -5251,6 +5839,16 @@
           <t>제안</t>
         </is>
       </c>
+      <c r="O67" s="16" t="inlineStr">
+        <is>
+          <t>C263995</t>
+        </is>
+      </c>
+      <c r="P67" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="n">
@@ -5313,6 +5911,8 @@
           <t>추정</t>
         </is>
       </c>
+      <c r="O68" s="16" t="inlineStr"/>
+      <c r="P68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="n">
@@ -5375,6 +5975,8 @@
           <t>추정</t>
         </is>
       </c>
+      <c r="O69" s="16" t="inlineStr"/>
+      <c r="P69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="I70" s="3" t="inlineStr">

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -262,8 +262,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P69" headerRowCount="1">
-  <autoFilter ref="A1:P69"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P71" headerRowCount="1">
+  <autoFilter ref="A1:P71"/>
   <tableColumns count="16">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="분류"/>
@@ -654,15 +654,15 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A7)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A7)</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A7)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A7)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A7)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A7)</f>
         <v/>
       </c>
       <c r="E7" s="10">
@@ -681,15 +681,15 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A8)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A8)</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A8)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A8)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A8)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A8)</f>
         <v/>
       </c>
       <c r="E8" s="10">
@@ -708,15 +708,15 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A9)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A9)</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A9)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A9)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A9)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A9)</f>
         <v/>
       </c>
       <c r="E9" s="10">
@@ -735,15 +735,15 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A10)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A10)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A10)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A10)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A10)</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -762,15 +762,15 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A11)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A11)</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A11)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A11)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A11)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A11)</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -789,15 +789,15 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A12)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A12)</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A12)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A12)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A12)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A12)</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -816,15 +816,15 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A13)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A13)</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A13)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A13)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A13)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A13)</f>
         <v/>
       </c>
       <c r="E13" s="10">
@@ -843,15 +843,15 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A14)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A14)</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A14)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A14)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A14)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A14)</f>
         <v/>
       </c>
       <c r="E14" s="10">
@@ -870,15 +870,15 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A15)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A15)</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A15)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A15)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A15)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A15)</f>
         <v/>
       </c>
       <c r="E15" s="10">
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A16)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A16)</f>
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A16)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A16)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A16)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A16)</f>
         <v/>
       </c>
       <c r="E16" s="10">
@@ -924,15 +924,15 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A17)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A17)</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A17)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A17)</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A17)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A17)</f>
         <v/>
       </c>
       <c r="E17" s="10">
@@ -951,15 +951,15 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A18)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A18)</f>
         <v/>
       </c>
       <c r="C18" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A18)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A18)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A18)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A18)</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -978,15 +978,15 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$69,A19)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$71,A19)</f>
         <v/>
       </c>
       <c r="C19" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$69,'부품리스트'!$B$2:$B$69,A19)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A19)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$69,'부품리스트'!$B$2:$B$69,A19)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A19)</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1257,11 +1257,11 @@
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>C2 C7</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D3" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="16" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F5" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G5" s="16" t="inlineStr">
@@ -1424,19 +1424,19 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>CL10B223KB8NNNC</t>
+          <t>CL05B223KO5NNNC</t>
         </is>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>MLCC 22 nF 50 V X7R 0603</t>
+          <t>MLCC 22 nF 16 V X7R 0402 (eFuse dV/dt, RTN 기준 저전압)</t>
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L5" s="20">
         <f>D5*J5</f>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="N5" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>C21122</t>
+          <t>C1532</t>
         </is>
       </c>
       <c r="P5" s="16" t="inlineStr">
@@ -1617,11 +1617,11 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>C8 C14 C15 C20 C21 C23 C28 C29 C30 C36 C40 C44 C46 C50 C53 C54 C56 C60</t>
+          <t>C8 C14 C15 C20 C21 C23 C28 C29 C30 C36 C40 C44 C50 C54 C60</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
@@ -1630,29 +1630,29 @@
       </c>
       <c r="F8" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t>CC0603KRX7R9BB104</t>
+          <t>CL05B104KO5NNNC</t>
         </is>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
-          <t>MLCC 100 nF 50 V X7R 0603</t>
+          <t>MLCC 100 nF 16 V X7R 0402 (3.3·5 V 디커플링 — 결정 #35 0402로 자리 확보)</t>
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L8" s="20">
         <f>D8*J8</f>
@@ -1664,12 +1664,12 @@
       </c>
       <c r="N8" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O8" s="16" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C1525</t>
         </is>
       </c>
       <c r="P8" s="16" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="F9" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G9" s="16" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="H9" s="17" t="inlineStr">
         <is>
-          <t>GRM188R71E105KA12D</t>
+          <t>GRM155Z71A105KE01D</t>
         </is>
       </c>
       <c r="I9" s="17" t="inlineStr">
         <is>
-          <t>MLCC 1 uF 25 V X7R 0603 (v0.9: X5R → X7R, 몰딩 후 85 °C 초과) [LCSC: Basic 1 µF(C15849)는 X5R이라 쓰지 않음]</t>
+          <t>MLCC 1 uF 10 V X7R 0402 (5 V 이하 넷: 벅 VCC, LDO 입·출력. LCSC 표기 X7R — 데이터시트 확인) [LCSC: X7R 1 µF 0402 16 V는 LCSC에서 못 찾음 → 10 V (5 V 이하 넷)]</t>
         </is>
       </c>
       <c r="J9" s="19" t="n">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="N9" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>C86020</t>
+          <t>C528974</t>
         </is>
       </c>
       <c r="P9" s="16" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -1784,19 +1784,19 @@
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>CL10C200JB8NNNC</t>
+          <t>CL05C200JB5NNNC</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>MLCC 20 pF 50 V C0G 0603 (벅 CFF)</t>
+          <t>MLCC 20 pF 50 V C0G 0402 (벅 CFF)</t>
         </is>
       </c>
       <c r="J10" s="19" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>0.008</v>
+        <v>0.005</v>
       </c>
       <c r="L10" s="20">
         <f>D10*J10</f>
@@ -1808,17 +1808,17 @@
       </c>
       <c r="N10" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O10" s="16" t="inlineStr">
         <is>
-          <t>C1648</t>
+          <t>C32950</t>
         </is>
       </c>
       <c r="P10" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2476,47 +2476,47 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C46 C53 C56</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>SMDJ36CA</t>
+          <t>100n/50V</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>D_SMC</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>Littelfuse</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>5.0SMDJ36CA</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>TVS 5000 W 36 V 양방향 SMC (입력 1단. LCSC — 같은 36 V·SMC, 3 kW → 5 kW)</t>
+          <t>MLCC 100 nF 50 V X7R 0603 (VS_CLAMP 약 24 V)</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
-        <v>0.3</v>
+        <v>0.004</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>0.7</v>
+        <v>0.01</v>
       </c>
       <c r="L20" s="20">
         <f>D20*J20</f>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>C141713</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="P20" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -2553,42 +2553,42 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>D2 D30 D40</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>TVS3301DRBR</t>
+          <t>SMDJ36CA</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>Texas_DRB0008A_PadFloat</t>
+          <t>D_SMC</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Littelfuse</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>TVS3301DRBR</t>
+          <t>5.0SMDJ36CA</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: 재고 적음 (검색 시 약 88개)]</t>
+          <t>TVS 5000 W 36 V 양방향 SMC (입력 1단. LCSC — 같은 36 V·SMC, 3 kW → 5 kW)</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L21" s="20">
         <f>D21*J21</f>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="N21" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O21" s="16" t="inlineStr">
         <is>
-          <t>C2864392</t>
+          <t>C141713</t>
         </is>
       </c>
       <c r="P21" s="16" t="inlineStr">
@@ -2620,47 +2620,47 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>D50</t>
+          <t>D2 D30 D40 D60 D61</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>BZX84C27</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>Texas_DRB0008A_PadFloat</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>Nexperia</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>BZX84-C27,215</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>제너 27 V (25.1–28.9) SOT-23 — +Vs 이미터 폴로워 기준 (1 A, 2 NC, 3 K)</t>
+          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: 재고 적음 (검색 시 약 88개) — v0.9 수량 5개 (D2, D30, D40, D60, D61)]</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="L22" s="20">
         <f>D22*J22</f>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="O22" s="16" t="inlineStr">
         <is>
-          <t>C96229</t>
+          <t>C2864392</t>
         </is>
       </c>
       <c r="P22" s="16" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D23" s="18" t="n">
@@ -2705,34 +2705,34 @@
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>600R@100MHz</t>
+          <t>PMEG10010ELR</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>L_0603_1608Metric</t>
+          <t>D_SOD-123F</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Nexperia</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>BLM18KG601SN1D</t>
+          <t>PMEG10010ELR-QX</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
+          <t>쇼트키 100 V 1 A 저누설 SOD-123W (SOD-123F 풋프린트) — eFuse 앞 직렬, 음(−) 서지·역극성 차단 (외부 검수 H01)</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="L23" s="20">
         <f>D23*J23</f>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="N23" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>C85833</t>
+          <t>C5361358</t>
         </is>
       </c>
       <c r="P23" s="16" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>GDT1</t>
+          <t>D50</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
@@ -2777,34 +2777,34 @@
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>2035-25-SM</t>
+          <t>BZX84C24</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>GDT_Bourns_2035-xx-SM</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>onsemi</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>2035-25-SM-RPLF</t>
+          <t>BZX84C24LT1G</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
+          <t>제너 24 V (22.8–25.6) SOT-23 — +Vs 이미터 폴로워 기준 (1 A, 2 NC, 3 K). 외부 검수 H04: 27 → 24 V (+Vs 권장 30 V 여유)</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="L24" s="20">
         <f>D24*J24</f>
@@ -2821,7 +2821,7 @@
       </c>
       <c r="O24" s="16" t="inlineStr">
         <is>
-          <t>C3660127</t>
+          <t>C43728</t>
         </is>
       </c>
       <c r="P24" s="16" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="D25" s="18" t="n">
@@ -2849,34 +2849,34 @@
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>600R@100MHz</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
+          <t>L_0603_1608Metric</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB(LF)(SN)</t>
+          <t>BLM18KG601SN1D</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
+          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>0.8</v>
+        <v>0.03</v>
       </c>
       <c r="L25" s="20">
         <f>D25*J25</f>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>C265111</t>
+          <t>C85833</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr">
@@ -2908,12 +2908,12 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>GDT1</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
@@ -2921,34 +2921,34 @@
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>TC2030-IDC-NL</t>
+          <t>2035-25-SM</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+          <t>GDT_Bourns_2035-xx-SM</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>(PCB 패드만)</t>
+          <t>2035-25-SM-RPLF</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>SWD 기록용 패드 — 부품 실장 없음</t>
+          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L26" s="20">
         <f>D26*J26</f>
@@ -2960,11 +2960,19 @@
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O26" s="16" t="inlineStr"/>
-      <c r="P26" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>C3660127</t>
+        </is>
+      </c>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n">
@@ -2977,7 +2985,7 @@
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
@@ -2985,12 +2993,12 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>SM08B-GHS-TB</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
+          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
@@ -3000,19 +3008,19 @@
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB(LF)(SN)</t>
+          <t>SM08B-GHS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
+          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L27" s="20">
         <f>D27*J27</f>
@@ -3029,7 +3037,7 @@
       </c>
       <c r="O27" s="16" t="inlineStr">
         <is>
-          <t>C160404</t>
+          <t>C265111</t>
         </is>
       </c>
       <c r="P27" s="16" t="inlineStr">
@@ -3044,12 +3052,12 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
@@ -3057,27 +3065,27 @@
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>CHASSIS wire</t>
+          <t>TC2030-IDC-NL</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>SolderWire_Chassis_D0.6mm</t>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>PCB 납땜 구멍 (부품 없음)</t>
+          <t>(PCB 패드만)</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
+          <t>SWD 기록용 패드 — 부품 실장 없음</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
@@ -3108,12 +3116,12 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
@@ -3121,34 +3129,34 @@
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>CMC 1mH 0.8A</t>
+          <t>SM04B-SRSS-TB</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>L_CommonMode_Wuerth_WE-SL2</t>
+          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>SRF0905-102Y</t>
+          <t>SM04B-SRSS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
+          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="L29" s="20">
         <f>D29*J29</f>
@@ -3158,14 +3166,14 @@
         <f>D29*K29</f>
         <v/>
       </c>
-      <c r="N29" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
       <c r="O29" s="16" t="inlineStr">
         <is>
-          <t>C2651138</t>
+          <t>C160404</t>
         </is>
       </c>
       <c r="P29" s="16" t="inlineStr">
@@ -3180,12 +3188,12 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
@@ -3193,34 +3201,34 @@
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>15uH</t>
+          <t>CHASSIS wire</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>L_Coilcraft_XAL4040-XXX</t>
+          <t>SolderWire_Chassis_D0.6mm</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>Coilcraft</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>XGL4040-153MEC</t>
+          <t>PCB 납땜 구멍 (부품 없음)</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 15 µH 3.6 A, 4 × 4 × 4.0 mm (XAL4040 풋프린트. LCSC — 4030형은 LCSC에 없음)</t>
+          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L30" s="20">
         <f>D30*J30</f>
@@ -3232,19 +3240,11 @@
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
-        </is>
-      </c>
-      <c r="O30" s="16" t="inlineStr">
-        <is>
-          <t>C3911667</t>
-        </is>
-      </c>
-      <c r="P30" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr"/>
+      <c r="P30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="n">
@@ -3252,12 +3252,12 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
@@ -3265,34 +3265,34 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>MMBTA06</t>
+          <t>CMC 1mH 0.8A</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>L_CommonMode_Wuerth_WE-SL2</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>onsemi</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>MMBTA06LT1G</t>
+          <t>SRF0905-102Y</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>NPN 80 V 0.5 A SOT-23 — TPS26611 +Vs 이미터 폴로워 (1 B, 2 E, 3 C)</t>
+          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
         </is>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>0.05</v>
+        <v>1.2</v>
       </c>
       <c r="L31" s="20">
         <f>D31*J31</f>
@@ -3302,14 +3302,14 @@
         <f>D31*K31</f>
         <v/>
       </c>
-      <c r="N31" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N31" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="O31" s="16" t="inlineStr">
         <is>
-          <t>C77760</t>
+          <t>C2651138</t>
         </is>
       </c>
       <c r="P31" s="16" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
@@ -3337,34 +3337,34 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>4.7R 1W pulse</t>
+          <t>15uH</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>L_Coilcraft_XAL4040-XXX</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Coilcraft</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>CRCW25124R70FKEGHP</t>
+          <t>XGL4040-153MEC</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>CRCW-HP 2512 4.7 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (입력 직렬, 1단·2단 서지 분담). MELF → 2512 (결정 #34) [LCSC: 펄스 내성(HP)형은 LCSC에 없음. LCSC 일반형 CRCW25124R70FKEG C242563은 서지 에너지 확인 후에만]</t>
+          <t>파워 인덕터 15 µH 3.6 A, 4 × 4 × 4.0 mm (XAL4040 풋프린트. LCSC — 4030형은 LCSC에 없음)</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="L32" s="20">
         <f>D32*J32</f>
@@ -3376,13 +3376,17 @@
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
-        </is>
-      </c>
-      <c r="O32" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>C3911667</t>
+        </is>
+      </c>
       <c r="P32" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3392,12 +3396,12 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
@@ -3405,34 +3409,34 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>1M HV</t>
+          <t>MMBTA06</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>R_1206_3216Metric</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>ROHM</t>
+          <t>onsemi</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>KTR18EZPF1004</t>
+          <t>MMBTA06LT1G</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
+          <t>NPN 80 V 0.5 A SOT-23 — TPS26611 +Vs 이미터 폴로워 (1 B, 2 E, 3 C)</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
         <v>0.02</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="L33" s="20">
         <f>D33*J33</f>
@@ -3444,12 +3448,12 @@
       </c>
       <c r="N33" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>C253347</t>
+          <t>C77760</t>
         </is>
       </c>
       <c r="P33" s="16" t="inlineStr">
@@ -3464,12 +3468,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
@@ -3477,12 +3481,12 @@
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>866k 1%</t>
+          <t>4.7R 1W pulse</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
@@ -3492,19 +3496,19 @@
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>RCS0603866KFKEA</t>
+          <t>CRCW25124R70FKEGHP</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
+          <t>CRCW-HP 2512 4.7 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (입력 직렬, 1단·2단 서지 분담). MELF → 2512 (결정 #34) [LCSC: 펄스 내성(HP)형은 LCSC에 없음. LCSC 일반형 CRCW25124R70FKEG C242563은 서지 에너지 확인 후에만]</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
-        <v>0.002</v>
+        <v>0.1</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>0.005</v>
+        <v>0.3</v>
       </c>
       <c r="L34" s="20">
         <f>D34*J34</f>
@@ -3516,17 +3520,13 @@
       </c>
       <c r="N34" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O34" s="16" t="inlineStr">
-        <is>
-          <t>C3954581</t>
-        </is>
-      </c>
+          <t>글로벌 소싱</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="inlineStr"/>
       <c r="P34" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D35" s="18" t="n">
@@ -3549,34 +3549,34 @@
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>97.6k 1%</t>
+          <t>1M HV</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_1206_3216Metric</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>ROHM</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>ERA-3AEB9762V</t>
+          <t>KTR18EZPF1004</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
+          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>0.005</v>
+        <v>0.06</v>
       </c>
       <c r="L35" s="20">
         <f>D35*J35</f>
@@ -3588,12 +3588,12 @@
       </c>
       <c r="N35" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O35" s="16" t="inlineStr">
         <is>
-          <t>C2074558</t>
+          <t>C253347</t>
         </is>
       </c>
       <c r="P35" s="16" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
@@ -3621,7 +3621,7 @@
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>36.5k 1%</t>
+          <t>866k 1%</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
@@ -3631,17 +3631,17 @@
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>CAL-CHIP</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>RM06F3652CT</t>
+          <t>RCS0603866KFKEA</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
+          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
         </is>
       </c>
       <c r="J36" s="19" t="n">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="O36" s="16" t="inlineStr">
         <is>
-          <t>C4027587</t>
+          <t>C3954581</t>
         </is>
       </c>
       <c r="P36" s="16" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="D37" s="18" t="n">
@@ -3693,7 +3693,7 @@
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
-          <t>80.6k 1%</t>
+          <t>97.6k 1%</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
@@ -3703,17 +3703,17 @@
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>0603WAF8062T5E</t>
+          <t>ERA-3AEB9762V</t>
         </is>
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
+          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
         </is>
       </c>
       <c r="J37" s="19" t="n">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>C23249</t>
+          <t>C2074558</t>
         </is>
       </c>
       <c r="P37" s="16" t="inlineStr">
@@ -3757,15 +3757,15 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>R8 R14</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>100k 1%</t>
+          <t>36.5k 1%</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>CAL-CHIP</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>0603WAF1003T5E</t>
+          <t>RM06F3652CT</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0603 (벅 FB, 전원 감시)</t>
+          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
         </is>
       </c>
       <c r="J38" s="19" t="n">
@@ -3809,12 +3809,12 @@
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>C25803</t>
+          <t>C4027587</t>
         </is>
       </c>
       <c r="P38" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="D39" s="18" t="n">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>24.9k 1%</t>
+          <t>80.6k 1%</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>0603WAF2492T5E</t>
+          <t>0603WAF8062T5E</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>저항 24.9 kΩ 1% 0603 (벅 FB)</t>
+          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
         </is>
       </c>
       <c r="J39" s="19" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>C25962</t>
+          <t>C23249</t>
         </is>
       </c>
       <c r="P39" s="16" t="inlineStr">
@@ -3896,25 +3896,25 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>R10 R11 R33 R50 R60</t>
+          <t>R8 R14</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>100k 1%</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G40" s="16" t="inlineStr">
@@ -3924,19 +3924,19 @@
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>0402WGF1003TCE</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>저항 10 kΩ 1% 0603</t>
+          <t>저항 100 kΩ 1% 0402 (벅 FB, 전원 감시)</t>
         </is>
       </c>
       <c r="J40" s="19" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="L40" s="20">
         <f>D40*J40</f>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>C25804</t>
+          <t>C25741</t>
         </is>
       </c>
       <c r="P40" s="16" t="inlineStr">
@@ -3968,20 +3968,20 @@
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>R12 R13 R31 R41</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="D41" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>24.9k 1%</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>0603WAF1003T5E</t>
+          <t>0603WAF2492T5E</t>
         </is>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0603</t>
+          <t>저항 24.9 kΩ 1% 0603 (벅 FB)</t>
         </is>
       </c>
       <c r="J41" s="19" t="n">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>C25803</t>
+          <t>C25962</t>
         </is>
       </c>
       <c r="P41" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4045,20 +4045,20 @@
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R10 R11 R33 R50 R60</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>10k 1%</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G42" s="16" t="inlineStr">
@@ -4068,19 +4068,19 @@
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>저항 10 kΩ 1% 0603 (전원 감시 분압)</t>
+          <t>저항 10 kΩ 1% 0402 (50 V)</t>
         </is>
       </c>
       <c r="J42" s="19" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="K42" s="19" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="L42" s="20">
         <f>D42*J42</f>
@@ -4092,12 +4092,12 @@
       </c>
       <c r="N42" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O42" s="16" t="inlineStr">
         <is>
-          <t>C25804</t>
+          <t>C25744</t>
         </is>
       </c>
       <c r="P42" s="16" t="inlineStr">
@@ -4117,20 +4117,20 @@
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>R17 R18 R20</t>
+          <t>R12 R13 R31 R41</t>
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
@@ -4140,19 +4140,19 @@
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>0603WAF1001T5E</t>
+          <t>0402WGF1003TCE</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>저항 1 kΩ 1% 0603</t>
+          <t>저항 100 kΩ 1% 0402 (50 V)</t>
         </is>
       </c>
       <c r="J43" s="19" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="L43" s="20">
         <f>D43*J43</f>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>C21190</t>
+          <t>C25741</t>
         </is>
       </c>
       <c r="P43" s="16" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
@@ -4197,34 +4197,34 @@
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>4.02k 0.02% 5ppm</t>
+          <t>10k 1%</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G44" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>PLTT0603Z4021</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거) [LCSC: LCSC 최선 ERA-3AEB4021V C491130 (0.1 %·25 ppm)은 Pt1000 정확도 약 5배 나빠 쓰지 않음]</t>
+          <t>저항 10 kΩ 1% 0402 (전원 감시 분압)</t>
         </is>
       </c>
       <c r="J44" s="19" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="K44" s="19" t="n">
-        <v>4</v>
+        <v>0.003</v>
       </c>
       <c r="L44" s="20">
         <f>D44*J44</f>
@@ -4236,13 +4236,17 @@
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O44" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O44" s="16" t="inlineStr">
+        <is>
+          <t>C25744</t>
+        </is>
+      </c>
       <c r="P44" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4252,47 +4256,47 @@
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>R30 R40</t>
+          <t>R17 R18 R20</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>10R pulse</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G45" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>CRCW251210R0FKEGHP</t>
+          <t>0402WGF1001TCE</t>
         </is>
       </c>
       <c r="I45" s="17" t="inlineStr">
         <is>
-          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬) [LCSC: LCSC 일반형 CRCW251210R0FKEG C844885는 서지 에너지 확인 후에만]</t>
+          <t>저항 1 kΩ 1% 0402</t>
         </is>
       </c>
       <c r="J45" s="19" t="n">
-        <v>0.05</v>
+        <v>0.001</v>
       </c>
       <c r="K45" s="19" t="n">
-        <v>0.15</v>
+        <v>0.003</v>
       </c>
       <c r="L45" s="20">
         <f>D45*J45</f>
@@ -4304,13 +4308,17 @@
       </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
-        </is>
-      </c>
-      <c r="O45" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O45" s="16" t="inlineStr">
+        <is>
+          <t>C11702</t>
+        </is>
+      </c>
       <c r="P45" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4320,20 +4328,20 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>R32 R42</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>15k 0.1% 25ppm</t>
+          <t>4.02k 0.02% 5ppm</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
@@ -4343,24 +4351,24 @@
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>ERA-3AEB153V</t>
+          <t>PLTT0603Z4021</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>저항 15 kΩ 0.1% 25 ppm/K 0603 (DAC8760 외부 ISET-R)</t>
+          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거) [LCSC: LCSC 최선 ERA-3AEB4021V C491130 (0.1 %·25 ppm)은 Pt1000 정확도 약 5배 나빠 쓰지 않음]</t>
         </is>
       </c>
       <c r="J46" s="19" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>0.06</v>
+        <v>4</v>
       </c>
       <c r="L46" s="20">
         <f>D46*J46</f>
@@ -4375,14 +4383,10 @@
           <t>제안</t>
         </is>
       </c>
-      <c r="O46" s="16" t="inlineStr">
-        <is>
-          <t>C473244</t>
-        </is>
-      </c>
+      <c r="O46" s="16" t="inlineStr"/>
       <c r="P46" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -4392,12 +4396,12 @@
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>R34 R44</t>
+          <t>R30 R40</t>
         </is>
       </c>
       <c r="D47" s="18" t="n">
@@ -4405,34 +4409,34 @@
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>10R</t>
+          <t>10R pulse</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>0603WAF100JT5E</t>
+          <t>CRCW251210R0FKEGHP</t>
         </is>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
-          <t>저항 10 Ω 1% 0603 (DAC8760 AVDD 직렬, 데이터시트 10장)</t>
+          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬) [LCSC: LCSC 일반형 CRCW251210R0FKEG C844885는 서지 에너지 확인 후에만]</t>
         </is>
       </c>
       <c r="J47" s="19" t="n">
-        <v>0.002</v>
+        <v>0.05</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>0.005</v>
+        <v>0.15</v>
       </c>
       <c r="L47" s="20">
         <f>D47*J47</f>
@@ -4444,17 +4448,13 @@
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O47" s="16" t="inlineStr">
-        <is>
-          <t>C22859</t>
-        </is>
-      </c>
+          <t>글로벌 소싱</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="inlineStr"/>
       <c r="P47" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -4464,47 +4464,47 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R32 R42</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>15k 0.1% 25ppm</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>ERA-3AEB153V</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
+          <t>저항 15 kΩ 0.1% 25 ppm/K 0603 (DAC8760 외부 ISET-R)</t>
         </is>
       </c>
       <c r="J48" s="19" t="n">
-        <v>1.5</v>
+        <v>0.02</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>3</v>
+        <v>0.06</v>
       </c>
       <c r="L48" s="20">
         <f>D48*J48</f>
@@ -4516,12 +4516,12 @@
       </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O48" s="16" t="inlineStr">
         <is>
-          <t>C544399</t>
+          <t>C473244</t>
         </is>
       </c>
       <c r="P48" s="16" t="inlineStr">
@@ -4536,47 +4536,47 @@
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>R34 R44</t>
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>LMR36006BRNXR</t>
+          <t>10R</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
         <is>
-          <t>Texas_RNX0012A_VQFN-HR-12_2x3mm</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>LMR36006BRNXR</t>
+          <t>0402WGF100JTCE</t>
         </is>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm [LCSC: LCSC에 없음 (차량용 LMR36006FSCQRNXRQ1 C2869760은 다른 품번·재고 16개)]</t>
+          <t>저항 10 Ω 1% 0402 (DAC8760 AVDD 직렬, 약 8 mW)</t>
         </is>
       </c>
       <c r="J49" s="19" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>1.6</v>
+        <v>0.003</v>
       </c>
       <c r="L49" s="20">
         <f>D49*J49</f>
@@ -4588,13 +4588,17 @@
       </c>
       <c r="N49" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O49" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>C25077</t>
+        </is>
+      </c>
       <c r="P49" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4613,7 @@
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
@@ -4617,12 +4621,12 @@
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
@@ -4632,19 +4636,19 @@
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
+          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
         </is>
       </c>
       <c r="J50" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="L50" s="20">
         <f>D50*J50</f>
@@ -4661,7 +4665,7 @@
       </c>
       <c r="O50" s="16" t="inlineStr">
         <is>
-          <t>C2862740</t>
+          <t>C544399</t>
         </is>
       </c>
       <c r="P50" s="16" t="inlineStr">
@@ -4676,12 +4680,12 @@
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
@@ -4689,34 +4693,34 @@
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>LMR36006BRNXR</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>LQFP-48_7x7mm_P0.5mm</t>
+          <t>Texas_RNX0012A_VQFN-HR-12_2x3mm</t>
         </is>
       </c>
       <c r="G51" s="16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>LMR36006BRNXR</t>
         </is>
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
-          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이) [LCSC: LCSC엔 85 °C 등급 CCT6 C5270241만 — 몰딩 내부 온도 때문에 125 °C 등급 유지]</t>
+          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm [LCSC: LCSC에 없음 (차량용 LMR36006FSCQRNXRQ1 C2869760은 다른 품번·재고 16개)]</t>
         </is>
       </c>
       <c r="J51" s="19" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="L51" s="20">
         <f>D51*J51</f>
@@ -4744,12 +4748,12 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
@@ -4757,34 +4761,34 @@
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="F52" s="16" t="inlineStr">
         <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>ScioSense</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>정전용량-디지털 변환기 QFN24</t>
+          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
         </is>
       </c>
       <c r="J52" s="19" t="n">
-        <v>6.5</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>7.1</v>
+        <v>0.3</v>
       </c>
       <c r="L52" s="20">
         <f>D52*J52</f>
@@ -4801,7 +4805,7 @@
       </c>
       <c r="O52" s="16" t="inlineStr">
         <is>
-          <t>C2829318</t>
+          <t>C2862740</t>
         </is>
       </c>
       <c r="P52" s="16" t="inlineStr">
@@ -4816,12 +4820,12 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>MCU</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -4829,34 +4833,34 @@
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>STM32G0B1CCT3</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>LQFP-48_7x7mm_P0.5mm</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>STM32G0B1CCT3</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
+          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이) [LCSC: LCSC엔 85 °C 등급 CCT6 C5270241만 — 몰딩 내부 온도 때문에 125 °C 등급 유지]</t>
         </is>
       </c>
       <c r="J53" s="19" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="L53" s="20">
         <f>D53*J53</f>
@@ -4871,14 +4875,10 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="O53" s="16" t="inlineStr">
-        <is>
-          <t>C48263</t>
-        </is>
-      </c>
+      <c r="O53" s="16" t="inlineStr"/>
       <c r="P53" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -4888,47 +4888,47 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>U7 U8</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>DAC8760IPWP</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ScioSense</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>DAC8760IPWPR</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
+          <t>정전용량-디지털 변환기 QFN24</t>
         </is>
       </c>
       <c r="J54" s="19" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>12.4</v>
+        <v>7.1</v>
       </c>
       <c r="L54" s="20">
         <f>D54*J54</f>
@@ -4945,7 +4945,7 @@
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
-          <t>C55047</t>
+          <t>C2829318</t>
         </is>
       </c>
       <c r="P54" s="16" t="inlineStr">
@@ -4960,25 +4960,25 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>U9 U10</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-8</t>
+          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
@@ -4988,19 +4988,19 @@
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
-          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
+          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
         </is>
       </c>
       <c r="J55" s="19" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="L55" s="20">
         <f>D55*J55</f>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="O55" s="16" t="inlineStr">
         <is>
-          <t>C3148140</t>
+          <t>C48263</t>
         </is>
       </c>
       <c r="P55" s="16" t="inlineStr">
@@ -5032,25 +5032,25 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U7 U8</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>THVD2410DR</t>
+          <t>DAC8760IPWP</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>SOIC-8_3.9x4.9mm_P1.27mm</t>
+          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
@@ -5060,19 +5060,19 @@
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>THVD2410DR</t>
+          <t>DAC8760IPWPR</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, SOIC-8 — THVD2450과 같은 핀 (v0.9)</t>
+          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
         </is>
       </c>
       <c r="J56" s="19" t="n">
-        <v>1.5</v>
+        <v>7.8</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>3</v>
+        <v>12.4</v>
       </c>
       <c r="L56" s="20">
         <f>D56*J56</f>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="O56" s="16" t="inlineStr">
         <is>
-          <t>C1849398</t>
+          <t>C55047</t>
         </is>
       </c>
       <c r="P56" s="16" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>U12 U13</t>
+          <t>U9 U10</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>SOT-23-8</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
@@ -5132,19 +5132,19 @@
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
-          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
+          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
         </is>
       </c>
       <c r="J57" s="19" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="L57" s="20">
         <f>D57*J57</f>
@@ -5156,12 +5156,12 @@
       </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="O57" s="16" t="inlineStr">
         <is>
-          <t>C221351</t>
+          <t>C3148140</t>
         </is>
       </c>
       <c r="P57" s="16" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>THVD2410DGKR</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
+          <t>VSSOP-8_3.0x3.0mm_P0.65mm</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
@@ -5204,19 +5204,19 @@
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>THVD2410DGKR</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
+          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, VSSOP-8 (SOIC와 같은 핀, 외부 검수 H02 TVS 자리 확보) — THVD2450과 같은 핀 (v0.9)</t>
         </is>
       </c>
       <c r="J58" s="19" t="n">
-        <v>0.08</v>
+        <v>1.5</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>0.2</v>
+        <v>3</v>
       </c>
       <c r="L58" s="20">
         <f>D58*J58</f>
@@ -5228,12 +5228,12 @@
       </c>
       <c r="N58" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
-          <t>C91874</t>
+          <t>C1858306</t>
         </is>
       </c>
       <c r="P58" s="16" t="inlineStr">
@@ -5248,47 +5248,47 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>기판</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>U12 U13</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>HMT500(260313A) (E-301)</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="I59" s="17" t="inlineStr">
         <is>
-          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
+          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
         </is>
       </c>
       <c r="J59" s="19" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="L59" s="20">
         <f>D59*J59</f>
@@ -5298,13 +5298,21 @@
         <f>D59*K59</f>
         <v/>
       </c>
-      <c r="N59" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O59" s="16" t="inlineStr"/>
-      <c r="P59" s="16" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O59" s="16" t="inlineStr">
+        <is>
+          <t>C221351</t>
+        </is>
+      </c>
+      <c r="P59" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="n">
@@ -5312,12 +5320,12 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
@@ -5325,34 +5333,34 @@
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>MK33-W (300 pF, 품번 확인 필요)</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
+          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
         </is>
       </c>
       <c r="J60" s="19" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="K60" s="19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L60" s="20">
         <f>D60*J60</f>
@@ -5362,13 +5370,21 @@
         <f>D60*K60</f>
         <v/>
       </c>
-      <c r="N60" s="21" t="inlineStr">
-        <is>
-          <t>사내 단가</t>
-        </is>
-      </c>
-      <c r="O60" s="16" t="inlineStr"/>
-      <c r="P60" s="16" t="inlineStr"/>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O60" s="16" t="inlineStr">
+        <is>
+          <t>C91874</t>
+        </is>
+      </c>
+      <c r="P60" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="n">
@@ -5376,12 +5392,12 @@
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>기판</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
@@ -5399,24 +5415,24 @@
       </c>
       <c r="G61" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>MiniSens Pt1000 F0.1</t>
+          <t>HMT500(260313A) (E-301)</t>
         </is>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
-          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
+          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
         </is>
       </c>
       <c r="J61" s="19" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L61" s="20">
         <f>D61*J61</f>
@@ -5440,12 +5456,12 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>P-204</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D62" s="18" t="n">
@@ -5463,24 +5479,24 @@
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>M Connect</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>TBD (두텍 사용품)</t>
+          <t>MK33-W (300 pF, 품번 확인 필요)</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
+          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
         </is>
       </c>
       <c r="J62" s="19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L62" s="20">
         <f>D62*J62</f>
@@ -5490,9 +5506,9 @@
         <f>D62*K62</f>
         <v/>
       </c>
-      <c r="N62" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="N62" s="21" t="inlineStr">
+        <is>
+          <t>사내 단가</t>
         </is>
       </c>
       <c r="O62" s="16" t="inlineStr"/>
@@ -5504,12 +5520,12 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D63" s="18" t="n">
@@ -5527,24 +5543,24 @@
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>GHR-08V-S</t>
+          <t>MiniSens Pt1000 F0.1</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
+          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
         </is>
       </c>
       <c r="J63" s="19" t="n">
-        <v>0.06</v>
+        <v>0.5</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>0.15</v>
+        <v>3</v>
       </c>
       <c r="L63" s="20">
         <f>D63*J63</f>
@@ -5554,21 +5570,13 @@
         <f>D63*K63</f>
         <v/>
       </c>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O63" s="16" t="inlineStr">
-        <is>
-          <t>C485357</t>
-        </is>
-      </c>
-      <c r="P63" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N63" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O63" s="16" t="inlineStr"/>
+      <c r="P63" s="16" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="n">
@@ -5576,16 +5584,16 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>P-204</t>
         </is>
       </c>
       <c r="D64" s="18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
@@ -5599,24 +5607,24 @@
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>M Connect</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>SSHL-002T-P0.2</t>
+          <t>TBD (두텍 사용품)</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>GH 크림프 단자 AWG 30–26</t>
+          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
         </is>
       </c>
       <c r="J64" s="19" t="n">
-        <v>0.03</v>
+        <v>2</v>
       </c>
       <c r="K64" s="19" t="n">
-        <v>0.06</v>
+        <v>10</v>
       </c>
       <c r="L64" s="20">
         <f>D64*J64</f>
@@ -5626,21 +5634,13 @@
         <f>D64*K64</f>
         <v/>
       </c>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O64" s="16" t="inlineStr">
-        <is>
-          <t>C189897</t>
-        </is>
-      </c>
-      <c r="P64" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N64" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="O64" s="16" t="inlineStr"/>
+      <c r="P64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="n">
@@ -5671,24 +5671,24 @@
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG28 전선</t>
+          <t>GHR-08V-S</t>
         </is>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
         </is>
       </c>
       <c r="J65" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K65" s="19" t="n">
         <v>0.15</v>
-      </c>
-      <c r="K65" s="19" t="n">
-        <v>0.4</v>
       </c>
       <c r="L65" s="20">
         <f>D65*J65</f>
@@ -5698,13 +5698,21 @@
         <f>D65*K65</f>
         <v/>
       </c>
-      <c r="N65" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O65" s="16" t="inlineStr"/>
-      <c r="P65" s="16" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O65" s="16" t="inlineStr">
+        <is>
+          <t>C485357</t>
+        </is>
+      </c>
+      <c r="P65" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="n">
@@ -5717,11 +5725,11 @@
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="D66" s="18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5740,19 +5748,19 @@
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>SHR-04V-S</t>
+          <t>SSHL-002T-P0.2</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
+          <t>GH 크림프 단자 AWG 30–26</t>
         </is>
       </c>
       <c r="J66" s="19" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="K66" s="19" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="L66" s="20">
         <f>D66*J66</f>
@@ -5769,7 +5777,7 @@
       </c>
       <c r="O66" s="16" t="inlineStr">
         <is>
-          <t>C385125</t>
+          <t>C189897</t>
         </is>
       </c>
       <c r="P66" s="16" t="inlineStr">
@@ -5789,11 +5797,11 @@
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="D67" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E67" s="16" t="inlineStr">
         <is>
@@ -5807,24 +5815,24 @@
       </c>
       <c r="G67" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>SSH-003T-P0.2-H</t>
+          <t>PTFE AWG28 전선</t>
         </is>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
-          <t>SH 크림프 단자 AWG 32–28</t>
+          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
         </is>
       </c>
       <c r="J67" s="19" t="n">
-        <v>0.03</v>
+        <v>0.15</v>
       </c>
       <c r="K67" s="19" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="L67" s="20">
         <f>D67*J67</f>
@@ -5834,21 +5842,13 @@
         <f>D67*K67</f>
         <v/>
       </c>
-      <c r="N67" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O67" s="16" t="inlineStr">
-        <is>
-          <t>C263995</t>
-        </is>
-      </c>
-      <c r="P67" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N67" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O67" s="16" t="inlineStr"/>
+      <c r="P67" s="16" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="16" t="n">
@@ -5879,24 +5879,24 @@
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG30 전선</t>
+          <t>SHR-04V-S</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
         </is>
       </c>
       <c r="J68" s="19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K68" s="19" t="n">
         <v>0.1</v>
-      </c>
-      <c r="K68" s="19" t="n">
-        <v>0.3</v>
       </c>
       <c r="L68" s="20">
         <f>D68*J68</f>
@@ -5906,13 +5906,21 @@
         <f>D68*K68</f>
         <v/>
       </c>
-      <c r="N68" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O68" s="16" t="inlineStr"/>
-      <c r="P68" s="16" t="inlineStr"/>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O68" s="16" t="inlineStr">
+        <is>
+          <t>C385125</t>
+        </is>
+      </c>
+      <c r="P68" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="n">
@@ -5920,47 +5928,47 @@
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>조립</t>
+          <t>하네스</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" s="16" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D69" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" s="16" t="inlineStr">
+      <c r="F69" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G69" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>SMT 양면 실장</t>
+          <t>SSH-003T-P0.2-H</t>
         </is>
       </c>
       <c r="I69" s="17" t="inlineStr">
         <is>
-          <t>1k 기준 조립비</t>
+          <t>SH 크림프 단자 AWG 32–28</t>
         </is>
       </c>
       <c r="J69" s="19" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="K69" s="19" t="n">
-        <v>4</v>
+        <v>0.06</v>
       </c>
       <c r="L69" s="20">
         <f>D69*J69</f>
@@ -5970,26 +5978,162 @@
         <f>D69*K69</f>
         <v/>
       </c>
-      <c r="N69" s="21" t="inlineStr">
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O69" s="16" t="inlineStr">
+        <is>
+          <t>C263995</t>
+        </is>
+      </c>
+      <c r="P69" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C70" s="17" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="D70" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H70" s="17" t="inlineStr">
+        <is>
+          <t>PTFE AWG30 전선</t>
+        </is>
+      </c>
+      <c r="I70" s="17" t="inlineStr">
+        <is>
+          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+        </is>
+      </c>
+      <c r="J70" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K70" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L70" s="20">
+        <f>D70*J70</f>
+        <v/>
+      </c>
+      <c r="M70" s="20">
+        <f>D70*K70</f>
+        <v/>
+      </c>
+      <c r="N70" s="21" t="inlineStr">
         <is>
           <t>추정</t>
         </is>
       </c>
-      <c r="O69" s="16" t="inlineStr"/>
-      <c r="P69" s="16" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="I70" s="3" t="inlineStr">
+      <c r="O70" s="16" t="inlineStr"/>
+      <c r="P70" s="16" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>조립</t>
+        </is>
+      </c>
+      <c r="C71" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G71" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" s="17" t="inlineStr">
+        <is>
+          <t>SMT 양면 실장</t>
+        </is>
+      </c>
+      <c r="I71" s="17" t="inlineStr">
+        <is>
+          <t>1k 기준 조립비</t>
+        </is>
+      </c>
+      <c r="J71" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K71" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L71" s="20">
+        <f>D71*J71</f>
+        <v/>
+      </c>
+      <c r="M71" s="20">
+        <f>D71*K71</f>
+        <v/>
+      </c>
+      <c r="N71" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O71" s="16" t="inlineStr"/>
+      <c r="P71" s="16" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="I72" s="3" t="inlineStr">
         <is>
           <t>합계 (1대분)</t>
         </is>
       </c>
-      <c r="L70" s="23">
-        <f>SUM(L2:L69)</f>
-        <v/>
-      </c>
-      <c r="M70" s="23">
-        <f>SUM(M2:M69)</f>
+      <c r="L72" s="23">
+        <f>SUM(L2:L71)</f>
+        <v/>
+      </c>
+      <c r="M72" s="23">
+        <f>SUM(M2:M71)</f>
         <v/>
       </c>
     </row>

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -262,8 +262,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P71" headerRowCount="1">
-  <autoFilter ref="A1:P71"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P76" headerRowCount="1">
+  <autoFilter ref="A1:P76"/>
   <tableColumns count="16">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="분류"/>
@@ -654,15 +654,15 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A7)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A7)</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A7)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A7)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A7)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A7)</f>
         <v/>
       </c>
       <c r="E7" s="10">
@@ -681,15 +681,15 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A8)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A8)</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A8)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A8)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A8)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A8)</f>
         <v/>
       </c>
       <c r="E8" s="10">
@@ -708,15 +708,15 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A9)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A9)</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A9)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A9)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A9)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A9)</f>
         <v/>
       </c>
       <c r="E9" s="10">
@@ -735,15 +735,15 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A10)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A10)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A10)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A10)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A10)</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -762,15 +762,15 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A11)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A11)</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A11)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A11)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A11)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A11)</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -789,15 +789,15 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A12)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A12)</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A12)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A12)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A12)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A12)</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -816,15 +816,15 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A13)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A13)</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A13)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A13)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A13)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A13)</f>
         <v/>
       </c>
       <c r="E13" s="10">
@@ -843,15 +843,15 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A14)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A14)</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A14)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A14)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A14)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A14)</f>
         <v/>
       </c>
       <c r="E14" s="10">
@@ -870,15 +870,15 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A15)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A15)</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A15)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A15)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A15)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A15)</f>
         <v/>
       </c>
       <c r="E15" s="10">
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A16)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A16)</f>
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A16)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A16)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A16)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A16)</f>
         <v/>
       </c>
       <c r="E16" s="10">
@@ -924,15 +924,15 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A17)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A17)</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A17)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A17)</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A17)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A17)</f>
         <v/>
       </c>
       <c r="E17" s="10">
@@ -951,15 +951,15 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A18)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A18)</f>
         <v/>
       </c>
       <c r="C18" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A18)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A18)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A18)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A18)</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -978,15 +978,15 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$71,A19)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$76,A19)</f>
         <v/>
       </c>
       <c r="C19" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$71,'부품리스트'!$B$2:$B$71,A19)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A19)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$71,'부품리스트'!$B$2:$B$71,A19)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A19)</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1473,11 +1473,11 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>C5</t>
+          <t>C5 C64 C65</t>
         </is>
       </c>
       <c r="D6" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" s="16" t="inlineStr">
         <is>
@@ -1486,29 +1486,29 @@
       </c>
       <c r="F6" s="16" t="inlineStr">
         <is>
-          <t>C_1210_3225Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t>GRM32ER71H106KA12L</t>
+          <t>CL31B106KBHNNNE</t>
         </is>
       </c>
       <c r="I6" s="17" t="inlineStr">
         <is>
-          <t>MLCC 10 uF 50 V X7R 1210</t>
+          <t>MLCC 10 uF 50 V X7R 1206 (벅 입력 C5, VAO 출력 C64·C65)</t>
         </is>
       </c>
       <c r="J6" s="19" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="K6" s="19" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="L6" s="20">
         <f>D6*J6</f>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="N6" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O6" s="16" t="inlineStr">
         <is>
-          <t>C77102</t>
+          <t>C89632</t>
         </is>
       </c>
       <c r="P6" s="16" t="inlineStr">
@@ -1617,11 +1617,11 @@
       </c>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>C8 C14 C15 C20 C21 C23 C28 C29 C30 C36 C40 C44 C50 C54 C60</t>
+          <t>C8 C14 C15 C20 C21 C23 C28 C29 C30 C36 C40 C44 C50 C54 C60 C63</t>
         </is>
       </c>
       <c r="D8" s="18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="16" t="inlineStr">
         <is>
@@ -2404,47 +2404,47 @@
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>C43</t>
+          <t>C46 C56 C62</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>4.7u 50V</t>
+          <t>100n/50V</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>C_1210_3225Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>GRM32ER71H475KA88L</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>MLCC 4.7 uF 50 V X7R 1210 (소프트 터미네이션 권장 — 에폭시 응력)</t>
+          <t>MLCC 100 nF 50 V X7R 0603 (VS_CLAMP 약 24 V)</t>
         </is>
       </c>
       <c r="J19" s="19" t="n">
-        <v>0.1</v>
+        <v>0.004</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>0.25</v>
+        <v>0.01</v>
       </c>
       <c r="L19" s="20">
         <f>D19*J19</f>
@@ -2456,17 +2456,17 @@
       </c>
       <c r="N19" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>C86052</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -2481,42 +2481,42 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>C46 C53 C56</t>
+          <t>C47 C57</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>100n/50V</t>
+          <t>4.7n</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G20" s="16" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>CC0603KRX7R9BB104</t>
+          <t>CL05B472KB5NNNC</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>MLCC 100 nF 50 V X7R 0603 (VS_CLAMP 약 24 V)</t>
+          <t>MLCC 4.7 nF 50 V X7R 0402 (DAC VOUT–CMP 보상)</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="K20" s="19" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L20" s="20">
         <f>D20*J20</f>
@@ -2533,12 +2533,12 @@
       </c>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C84705</t>
         </is>
       </c>
       <c r="P20" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2548,47 +2548,47 @@
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>C48 C58</t>
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>SMDJ36CA</t>
+          <t>100p C0G</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>D_SMC</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>Littelfuse</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>5.0SMDJ36CA</t>
+          <t>CL05C101JB5NNNC</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>TVS 5000 W 36 V 양방향 SMC (입력 1단. LCSC — 같은 36 V·SMC, 3 kW → 5 kW)</t>
+          <t>MLCC 100 pF 50 V C0G 0402 (DAC CMP–GND)</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
-        <v>0.3</v>
+        <v>0.002</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>0.7</v>
+        <v>0.005</v>
       </c>
       <c r="L21" s="20">
         <f>D21*J21</f>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="O21" s="16" t="inlineStr">
         <is>
-          <t>C141713</t>
+          <t>C26409</t>
         </is>
       </c>
       <c r="P21" s="16" t="inlineStr">
@@ -2620,47 +2620,47 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>D2 D30 D40 D60 D61</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>TVS3301DRBR</t>
+          <t>2.2u 50V</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>Texas_DRB0008A_PadFloat</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>TVS3301DRBR</t>
+          <t>CL21B225KBFNNNE</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: 재고 적음 (검색 시 약 88개) — v0.9 수량 5개 (D2, D30, D40, D60, D61)]</t>
+          <t>MLCC 2.2 uF 50 V X7R 0805 (VAO 벅 입력) [LCSC: LCSC 번호는 JLC 화면에서 같은 품번 선택 (검색에서 C 번호 미확인)]</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>0.35</v>
+        <v>0.02</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>0.6</v>
+        <v>0.05</v>
       </c>
       <c r="L22" s="20">
         <f>D22*J22</f>
@@ -2672,14 +2672,10 @@
       </c>
       <c r="N22" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O22" s="16" t="inlineStr">
-        <is>
-          <t>C2864392</t>
-        </is>
-      </c>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O22" s="16" t="inlineStr"/>
       <c r="P22" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -2697,7 +2693,7 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D23" s="18" t="n">
@@ -2705,34 +2701,34 @@
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>PMEG10010ELR</t>
+          <t>SMDJ36CA</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>D_SOD-123F</t>
+          <t>D_SMC</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>Nexperia</t>
+          <t>Littelfuse</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>PMEG10010ELR-QX</t>
+          <t>5.0SMDJ36CA</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>쇼트키 100 V 1 A 저누설 SOD-123W (SOD-123F 풋프린트) — eFuse 앞 직렬, 음(−) 서지·역극성 차단 (외부 검수 H01)</t>
+          <t>TVS 5000 W 36 V 양방향 SMC (입력 1단. LCSC — 같은 36 V·SMC, 3 kW → 5 kW)</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.12</v>
+        <v>0.7</v>
       </c>
       <c r="L23" s="20">
         <f>D23*J23</f>
@@ -2749,7 +2745,7 @@
       </c>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>C5361358</t>
+          <t>C141713</t>
         </is>
       </c>
       <c r="P23" s="16" t="inlineStr">
@@ -2764,47 +2760,47 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>D50</t>
+          <t>D2 D30 D40 D60 D61</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>BZX84C24</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>Texas_DRB0008A_PadFloat</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>onsemi</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>BZX84C24LT1G</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>제너 24 V (22.8–25.6) SOT-23 — +Vs 이미터 폴로워 기준 (1 A, 2 NC, 3 K). 외부 검수 H04: 27 → 24 V (+Vs 권장 30 V 여유)</t>
+          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: 재고 적음 (검색 시 약 88개) — v0.9 수량 5개 (D2, D30, D40, D60, D61)]</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
-        <v>0.01</v>
+        <v>0.35</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>0.03</v>
+        <v>0.6</v>
       </c>
       <c r="L24" s="20">
         <f>D24*J24</f>
@@ -2816,12 +2812,12 @@
       </c>
       <c r="N24" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O24" s="16" t="inlineStr">
         <is>
-          <t>C43728</t>
+          <t>C2864392</t>
         </is>
       </c>
       <c r="P24" s="16" t="inlineStr">
@@ -2836,12 +2832,12 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D25" s="18" t="n">
@@ -2849,34 +2845,34 @@
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>600R@100MHz</t>
+          <t>PMEG10010ELR</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>L_0603_1608Metric</t>
+          <t>D_SOD-123F</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Nexperia</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>BLM18KG601SN1D</t>
+          <t>PMEG10010ELR-QX</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
+          <t>쇼트키 100 V 1 A 저누설 SOD-123W (SOD-123F 풋프린트) — eFuse 앞 직렬, 음(−) 서지·역극성 차단 (외부 검수 H01)</t>
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>0.03</v>
+        <v>0.12</v>
       </c>
       <c r="L25" s="20">
         <f>D25*J25</f>
@@ -2888,12 +2884,12 @@
       </c>
       <c r="N25" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>C85833</t>
+          <t>C5361358</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr">
@@ -2908,47 +2904,47 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>GDT1</t>
+          <t>D41 D51</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>2035-25-SM</t>
+          <t>BAS70-04</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>GDT_Bourns_2035-xx-SM</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>Nexperia</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>2035-25-SM-RPLF</t>
+          <t>BAS70-04,215</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
+          <t>쇼트키 2개 직렬 70 V SOT-23 — DAC 출력 클램프 (1 A, 2 K, 3 공통)</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.4</v>
+        <v>0.02</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>1</v>
+        <v>0.05</v>
       </c>
       <c r="L26" s="20">
         <f>D26*J26</f>
@@ -2965,7 +2961,7 @@
       </c>
       <c r="O26" s="16" t="inlineStr">
         <is>
-          <t>C3660127</t>
+          <t>C389351</t>
         </is>
       </c>
       <c r="P26" s="16" t="inlineStr">
@@ -2980,12 +2976,12 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
@@ -2993,34 +2989,34 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>600R@100MHz</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
+          <t>L_0603_1608Metric</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB(LF)(SN)</t>
+          <t>BLM18KG601SN1D</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
+          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.35</v>
+        <v>0.01</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>0.8</v>
+        <v>0.03</v>
       </c>
       <c r="L27" s="20">
         <f>D27*J27</f>
@@ -3037,7 +3033,7 @@
       </c>
       <c r="O27" s="16" t="inlineStr">
         <is>
-          <t>C265111</t>
+          <t>C85833</t>
         </is>
       </c>
       <c r="P27" s="16" t="inlineStr">
@@ -3052,12 +3048,12 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>GDT1</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
@@ -3065,34 +3061,34 @@
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>TC2030-IDC-NL</t>
+          <t>2035-25-SM</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+          <t>GDT_Bourns_2035-xx-SM</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>(PCB 패드만)</t>
+          <t>2035-25-SM-RPLF</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>SWD 기록용 패드 — 부품 실장 없음</t>
+          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="20">
         <f>D28*J28</f>
@@ -3104,11 +3100,19 @@
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O28" s="16" t="inlineStr"/>
-      <c r="P28" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O28" s="16" t="inlineStr">
+        <is>
+          <t>C3660127</t>
+        </is>
+      </c>
+      <c r="P28" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="n">
@@ -3121,7 +3125,7 @@
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
@@ -3129,12 +3133,12 @@
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>SM08B-GHS-TB</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
+          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
@@ -3144,19 +3148,19 @@
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB(LF)(SN)</t>
+          <t>SM08B-GHS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
+          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="L29" s="20">
         <f>D29*J29</f>
@@ -3173,7 +3177,7 @@
       </c>
       <c r="O29" s="16" t="inlineStr">
         <is>
-          <t>C160404</t>
+          <t>C265111</t>
         </is>
       </c>
       <c r="P29" s="16" t="inlineStr">
@@ -3188,12 +3192,12 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
@@ -3201,27 +3205,27 @@
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>CHASSIS wire</t>
+          <t>TC2030-IDC-NL</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>SolderWire_Chassis_D0.6mm</t>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>PCB 납땜 구멍 (부품 없음)</t>
+          <t>(PCB 패드만)</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
+          <t>SWD 기록용 패드 — 부품 실장 없음</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
@@ -3252,12 +3256,12 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
@@ -3265,34 +3269,34 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>CMC 1mH 0.8A</t>
+          <t>SM04B-SRSS-TB</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>L_CommonMode_Wuerth_WE-SL2</t>
+          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>SRF0905-102Y</t>
+          <t>SM04B-SRSS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
+          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="L31" s="20">
         <f>D31*J31</f>
@@ -3302,14 +3306,14 @@
         <f>D31*K31</f>
         <v/>
       </c>
-      <c r="N31" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
       <c r="O31" s="16" t="inlineStr">
         <is>
-          <t>C2651138</t>
+          <t>C160404</t>
         </is>
       </c>
       <c r="P31" s="16" t="inlineStr">
@@ -3324,12 +3328,12 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
@@ -3337,34 +3341,34 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>15uH</t>
+          <t>CHASSIS wire</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>L_Coilcraft_XAL4040-XXX</t>
+          <t>SolderWire_Chassis_D0.6mm</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>Coilcraft</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>XGL4040-153MEC</t>
+          <t>PCB 납땜 구멍 (부품 없음)</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 15 µH 3.6 A, 4 × 4 × 4.0 mm (XAL4040 풋프린트. LCSC — 4030형은 LCSC에 없음)</t>
+          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="L32" s="20">
         <f>D32*J32</f>
@@ -3376,19 +3380,11 @@
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
-        </is>
-      </c>
-      <c r="O32" s="16" t="inlineStr">
-        <is>
-          <t>C3911667</t>
-        </is>
-      </c>
-      <c r="P32" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr"/>
+      <c r="P32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="n">
@@ -3396,12 +3392,12 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
@@ -3409,34 +3405,34 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>MMBTA06</t>
+          <t>CMC 1mH 0.8A</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>L_CommonMode_Wuerth_WE-SL2</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>onsemi</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>MMBTA06LT1G</t>
+          <t>SRF0905-102Y</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>NPN 80 V 0.5 A SOT-23 — TPS26611 +Vs 이미터 폴로워 (1 B, 2 E, 3 C)</t>
+          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
-        <v>0.02</v>
+        <v>0.5</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>0.05</v>
+        <v>1.2</v>
       </c>
       <c r="L33" s="20">
         <f>D33*J33</f>
@@ -3446,14 +3442,14 @@
         <f>D33*K33</f>
         <v/>
       </c>
-      <c r="N33" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N33" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>C77760</t>
+          <t>C2651138</t>
         </is>
       </c>
       <c r="P33" s="16" t="inlineStr">
@@ -3468,12 +3464,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
@@ -3481,34 +3477,34 @@
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>4.7R 1W pulse</t>
+          <t>15uH</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>L_Coilcraft_XAL4040-XXX</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Coilcraft</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>CRCW25124R70FKEGHP</t>
+          <t>XGL4040-153MEC</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>CRCW-HP 2512 4.7 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (입력 직렬, 1단·2단 서지 분담). MELF → 2512 (결정 #34) [LCSC: 펄스 내성(HP)형은 LCSC에 없음. LCSC 일반형 CRCW25124R70FKEG C242563은 서지 에너지 확인 후에만]</t>
+          <t>파워 인덕터 15 µH 3.6 A, 4 × 4 × 4.0 mm (XAL4040 풋프린트. LCSC — 4030형은 LCSC에 없음)</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="L34" s="20">
         <f>D34*J34</f>
@@ -3520,13 +3516,17 @@
       </c>
       <c r="N34" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
-        </is>
-      </c>
-      <c r="O34" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O34" s="16" t="inlineStr">
+        <is>
+          <t>C3911667</t>
+        </is>
+      </c>
       <c r="P34" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="D35" s="18" t="n">
@@ -3549,34 +3549,34 @@
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>1M HV</t>
+          <t>22uH</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>R_1206_3216Metric</t>
+          <t>L_Taiyo-Yuden_NR-40xx</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>ROHM</t>
+          <t>(LCSC)</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>KTR18EZPF1004</t>
+          <t>SMNR4020-22UH</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
+          <t>파워 인덕터 22 µH ±20 % 1.05 A 455 mΩ 4 × 4 × 2 mm (NR-40xx 랜드) — VAO 벅 [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="K35" s="19" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="L35" s="20">
         <f>D35*J35</f>
@@ -3586,14 +3586,14 @@
         <f>D35*K35</f>
         <v/>
       </c>
-      <c r="N35" s="16" t="inlineStr">
-        <is>
-          <t>LCSC</t>
+      <c r="N35" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="O35" s="16" t="inlineStr">
         <is>
-          <t>C253347</t>
+          <t>C135264</t>
         </is>
       </c>
       <c r="P35" s="16" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>866k 1%</t>
+          <t>4.7R 1W pulse</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
@@ -3636,19 +3636,19 @@
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>RCS0603866KFKEA</t>
+          <t>CRCW25124R70FKEGHP</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
+          <t>CRCW-HP 2512 4.7 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (입력 직렬, 1단·2단 서지 분담). MELF → 2512 (결정 #34) [LCSC: 펄스 내성(HP)형은 LCSC에 없음. LCSC 일반형 CRCW25124R70FKEG C242563은 서지 에너지 확인 후에만]</t>
         </is>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0.002</v>
+        <v>0.1</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>0.005</v>
+        <v>0.3</v>
       </c>
       <c r="L36" s="20">
         <f>D36*J36</f>
@@ -3660,17 +3660,13 @@
       </c>
       <c r="N36" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O36" s="16" t="inlineStr">
-        <is>
-          <t>C3954581</t>
-        </is>
-      </c>
+          <t>글로벌 소싱</t>
+        </is>
+      </c>
+      <c r="O36" s="16" t="inlineStr"/>
       <c r="P36" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3676,12 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D37" s="18" t="n">
@@ -3693,34 +3689,34 @@
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
-          <t>97.6k 1%</t>
+          <t>1M HV</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_1206_3216Metric</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>ROHM</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>ERA-3AEB9762V</t>
+          <t>KTR18EZPF1004</t>
         </is>
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
+          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
         </is>
       </c>
       <c r="J37" s="19" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>0.005</v>
+        <v>0.06</v>
       </c>
       <c r="L37" s="20">
         <f>D37*J37</f>
@@ -3732,12 +3728,12 @@
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>C2074558</t>
+          <t>C253347</t>
         </is>
       </c>
       <c r="P37" s="16" t="inlineStr">
@@ -3757,7 +3753,7 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
@@ -3765,7 +3761,7 @@
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>36.5k 1%</t>
+          <t>866k 1%</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -3775,17 +3771,17 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>CAL-CHIP</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>RM06F3652CT</t>
+          <t>RCS0603866KFKEA</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
+          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
         </is>
       </c>
       <c r="J38" s="19" t="n">
@@ -3809,7 +3805,7 @@
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>C4027587</t>
+          <t>C3954581</t>
         </is>
       </c>
       <c r="P38" s="16" t="inlineStr">
@@ -3829,7 +3825,7 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="D39" s="18" t="n">
@@ -3837,7 +3833,7 @@
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>80.6k 1%</t>
+          <t>97.6k 1%</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -3847,17 +3843,17 @@
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>0603WAF8062T5E</t>
+          <t>ERA-3AEB9762V</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
+          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
         </is>
       </c>
       <c r="J39" s="19" t="n">
@@ -3881,7 +3877,7 @@
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>C23249</t>
+          <t>C2074558</t>
         </is>
       </c>
       <c r="P39" s="16" t="inlineStr">
@@ -3901,42 +3897,42 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>R8 R14</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>100k 1%</t>
+          <t>36.5k 1%</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>CAL-CHIP</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1003TCE</t>
+          <t>RM06F3652CT</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0402 (벅 FB, 전원 감시)</t>
+          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
         </is>
       </c>
       <c r="J40" s="19" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="K40" s="19" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="L40" s="20">
         <f>D40*J40</f>
@@ -3948,17 +3944,17 @@
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>C25741</t>
+          <t>C4027587</t>
         </is>
       </c>
       <c r="P40" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3973,7 +3969,7 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="D41" s="18" t="n">
@@ -3981,7 +3977,7 @@
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>24.9k 1%</t>
+          <t>80.6k 1%</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
@@ -3996,12 +3992,12 @@
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>0603WAF2492T5E</t>
+          <t>0603WAF8062T5E</t>
         </is>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
-          <t>저항 24.9 kΩ 1% 0603 (벅 FB)</t>
+          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
         </is>
       </c>
       <c r="J41" s="19" t="n">
@@ -4025,7 +4021,7 @@
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>C25962</t>
+          <t>C23249</t>
         </is>
       </c>
       <c r="P41" s="16" t="inlineStr">
@@ -4040,20 +4036,20 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>R10 R11 R33 R50 R60</t>
+          <t>R8 R14</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>100k 1%</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
@@ -4068,12 +4064,12 @@
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1002TCE</t>
+          <t>0402WGF1003TCE</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>저항 10 kΩ 1% 0402 (50 V)</t>
+          <t>저항 100 kΩ 1% 0402 (벅 FB, 전원 감시)</t>
         </is>
       </c>
       <c r="J42" s="19" t="n">
@@ -4097,7 +4093,7 @@
       </c>
       <c r="O42" s="16" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C25741</t>
         </is>
       </c>
       <c r="P42" s="16" t="inlineStr">
@@ -4112,25 +4108,25 @@
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>R12 R13 R31 R41</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>24.9k 1%</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
@@ -4140,19 +4136,19 @@
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1003TCE</t>
+          <t>0603WAF2492T5E</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0402 (50 V)</t>
+          <t>저항 24.9 kΩ 1% 0603 (벅 FB)</t>
         </is>
       </c>
       <c r="J43" s="19" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="L43" s="20">
         <f>D43*J43</f>
@@ -4164,17 +4160,17 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>C25741</t>
+          <t>C25962</t>
         </is>
       </c>
       <c r="P43" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4189,15 +4185,15 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R10 R11 R33 R60</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>10k 1%</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
@@ -4217,7 +4213,7 @@
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>저항 10 kΩ 1% 0402 (전원 감시 분압)</t>
+          <t>저항 10 kΩ 1% 0402 (50 V)</t>
         </is>
       </c>
       <c r="J44" s="19" t="n">
@@ -4261,15 +4257,15 @@
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>R17 R18 R20</t>
+          <t>R12 R13 R31 R41</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
@@ -4284,12 +4280,12 @@
       </c>
       <c r="H45" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1001TCE</t>
+          <t>0402WGF1003TCE</t>
         </is>
       </c>
       <c r="I45" s="17" t="inlineStr">
         <is>
-          <t>저항 1 kΩ 1% 0402</t>
+          <t>저항 100 kΩ 1% 0402 (50 V)</t>
         </is>
       </c>
       <c r="J45" s="19" t="n">
@@ -4313,7 +4309,7 @@
       </c>
       <c r="O45" s="16" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C25741</t>
         </is>
       </c>
       <c r="P45" s="16" t="inlineStr">
@@ -4328,12 +4324,12 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
@@ -4341,34 +4337,34 @@
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>4.02k 0.02% 5ppm</t>
+          <t>10k 1%</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G46" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>PLTT0603Z4021</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거) [LCSC: LCSC 최선 ERA-3AEB4021V C491130 (0.1 %·25 ppm)은 Pt1000 정확도 약 5배 나빠 쓰지 않음]</t>
+          <t>저항 10 kΩ 1% 0402 (전원 감시 분압)</t>
         </is>
       </c>
       <c r="J46" s="19" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="K46" s="19" t="n">
-        <v>4</v>
+        <v>0.003</v>
       </c>
       <c r="L46" s="20">
         <f>D46*J46</f>
@@ -4380,13 +4376,17 @@
       </c>
       <c r="N46" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O46" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O46" s="16" t="inlineStr">
+        <is>
+          <t>C25744</t>
+        </is>
+      </c>
       <c r="P46" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4396,47 +4396,47 @@
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>R30 R40</t>
+          <t>R17 R18 R20</t>
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>10R pulse</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G47" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>CRCW251210R0FKEGHP</t>
+          <t>0402WGF1001TCE</t>
         </is>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
-          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬) [LCSC: LCSC 일반형 CRCW251210R0FKEG C844885는 서지 에너지 확인 후에만]</t>
+          <t>저항 1 kΩ 1% 0402</t>
         </is>
       </c>
       <c r="J47" s="19" t="n">
-        <v>0.05</v>
+        <v>0.001</v>
       </c>
       <c r="K47" s="19" t="n">
-        <v>0.15</v>
+        <v>0.003</v>
       </c>
       <c r="L47" s="20">
         <f>D47*J47</f>
@@ -4448,13 +4448,17 @@
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
-        </is>
-      </c>
-      <c r="O47" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O47" s="16" t="inlineStr">
+        <is>
+          <t>C11702</t>
+        </is>
+      </c>
       <c r="P47" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4464,20 +4468,20 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>R32 R42</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>15k 0.1% 25ppm</t>
+          <t>4.02k 0.02% 5ppm</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
@@ -4487,24 +4491,24 @@
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>ERA-3AEB153V</t>
+          <t>PLTT0603Z4021</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>저항 15 kΩ 0.1% 25 ppm/K 0603 (DAC8760 외부 ISET-R)</t>
+          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거) [LCSC: LCSC 최선 ERA-3AEB4021V C491130 (0.1 %·25 ppm)은 Pt1000 정확도 약 5배 나빠 쓰지 않음]</t>
         </is>
       </c>
       <c r="J48" s="19" t="n">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>0.06</v>
+        <v>4</v>
       </c>
       <c r="L48" s="20">
         <f>D48*J48</f>
@@ -4519,14 +4523,10 @@
           <t>제안</t>
         </is>
       </c>
-      <c r="O48" s="16" t="inlineStr">
-        <is>
-          <t>C473244</t>
-        </is>
-      </c>
+      <c r="O48" s="16" t="inlineStr"/>
       <c r="P48" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -4536,12 +4536,12 @@
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>R34 R44</t>
+          <t>R30 R40</t>
         </is>
       </c>
       <c r="D49" s="18" t="n">
@@ -4549,34 +4549,34 @@
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>10R</t>
+          <t>10R pulse</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>0402WGF100JTCE</t>
+          <t>CRCW251210R0FKEGHP</t>
         </is>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>저항 10 Ω 1% 0402 (DAC8760 AVDD 직렬, 약 8 mW)</t>
+          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬) [LCSC: LCSC 일반형 CRCW251210R0FKEG C844885는 서지 에너지 확인 후에만]</t>
         </is>
       </c>
       <c r="J49" s="19" t="n">
-        <v>0.001</v>
+        <v>0.05</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>0.003</v>
+        <v>0.15</v>
       </c>
       <c r="L49" s="20">
         <f>D49*J49</f>
@@ -4588,17 +4588,13 @@
       </c>
       <c r="N49" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
-        </is>
-      </c>
-      <c r="O49" s="16" t="inlineStr">
-        <is>
-          <t>C25077</t>
-        </is>
-      </c>
+          <t>글로벌 소싱</t>
+        </is>
+      </c>
+      <c r="O49" s="16" t="inlineStr"/>
       <c r="P49" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -4608,47 +4604,47 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R32 R42</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>15k 0.1% 25ppm</t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>ERA-3AEB153V</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
+          <t>저항 15 kΩ 0.1% 25 ppm/K 0603 (DAC8760 외부 ISET-R)</t>
         </is>
       </c>
       <c r="J50" s="19" t="n">
-        <v>1.5</v>
+        <v>0.02</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>3</v>
+        <v>0.06</v>
       </c>
       <c r="L50" s="20">
         <f>D50*J50</f>
@@ -4660,12 +4656,12 @@
       </c>
       <c r="N50" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O50" s="16" t="inlineStr">
         <is>
-          <t>C544399</t>
+          <t>C473244</t>
         </is>
       </c>
       <c r="P50" s="16" t="inlineStr">
@@ -4680,47 +4676,47 @@
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>R34 R44</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>LMR36006BRNXR</t>
+          <t>10R</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>Texas_RNX0012A_VQFN-HR-12_2x3mm</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G51" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>LMR36006BRNXR</t>
+          <t>0402WGF100JTCE</t>
         </is>
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
-          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm [LCSC: LCSC에 없음 (차량용 LMR36006FSCQRNXRQ1 C2869760은 다른 품번·재고 16개)]</t>
+          <t>저항 10 Ω 1% 0402 (DAC8760 AVDD 직렬, 약 8 mW)</t>
         </is>
       </c>
       <c r="J51" s="19" t="n">
-        <v>1</v>
+        <v>0.001</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>1.6</v>
+        <v>0.003</v>
       </c>
       <c r="L51" s="20">
         <f>D51*J51</f>
@@ -4732,13 +4728,17 @@
       </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O51" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O51" s="16" t="inlineStr">
+        <is>
+          <t>C25077</t>
+        </is>
+      </c>
       <c r="P51" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4748,12 +4748,12 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>R51</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
@@ -4761,34 +4761,34 @@
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>422k 1%</t>
         </is>
       </c>
       <c r="F52" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>0402WGF4223TCE</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
+          <t>저항 422 kΩ 1% 0402 (VAO 분압 상단) [LCSC: LCSC 번호 미확인 — JLC 화면에서 422 kΩ 1 % 0402 선택]</t>
         </is>
       </c>
       <c r="J52" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.001</v>
       </c>
       <c r="K52" s="19" t="n">
-        <v>0.3</v>
+        <v>0.003</v>
       </c>
       <c r="L52" s="20">
         <f>D52*J52</f>
@@ -4798,16 +4798,12 @@
         <f>D52*K52</f>
         <v/>
       </c>
-      <c r="N52" s="16" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O52" s="16" t="inlineStr">
-        <is>
-          <t>C2862740</t>
-        </is>
-      </c>
+      <c r="N52" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="O52" s="16" t="inlineStr"/>
       <c r="P52" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -4820,12 +4816,12 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>R52</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -4833,34 +4829,34 @@
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>22.1k 1%</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>LQFP-48_7x7mm_P0.5mm</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>0402WGF2212TCE</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이) [LCSC: LCSC엔 85 °C 등급 CCT6 C5270241만 — 몰딩 내부 온도 때문에 125 °C 등급 유지]</t>
+          <t>저항 22.1 kΩ 1% 0402 (VAO 분압 하단) [LCSC: LCSC 번호 미확인 — JLC 화면에서 22.1 kΩ 1 % 0402 선택]</t>
         </is>
       </c>
       <c r="J53" s="19" t="n">
-        <v>1.5</v>
+        <v>0.001</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>2.5</v>
+        <v>0.003</v>
       </c>
       <c r="L53" s="20">
         <f>D53*J53</f>
@@ -4870,15 +4866,15 @@
         <f>D53*K53</f>
         <v/>
       </c>
-      <c r="N53" s="16" t="inlineStr">
-        <is>
-          <t>확정</t>
+      <c r="N53" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="O53" s="16" t="inlineStr"/>
       <c r="P53" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4888,12 +4884,12 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
@@ -4901,34 +4897,34 @@
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
+          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
         <is>
-          <t>ScioSense</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>정전용량-디지털 변환기 QFN24</t>
+          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
         </is>
       </c>
       <c r="J54" s="19" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>7.1</v>
+        <v>3</v>
       </c>
       <c r="L54" s="20">
         <f>D54*J54</f>
@@ -4945,7 +4941,7 @@
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
-          <t>C2829318</t>
+          <t>C544399</t>
         </is>
       </c>
       <c r="P54" s="16" t="inlineStr">
@@ -4960,12 +4956,12 @@
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
@@ -4973,12 +4969,12 @@
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>LMR36006BRNXR</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>Texas_RNX0012A_VQFN-HR-12_2x3mm</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
@@ -4988,19 +4984,19 @@
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>LMR36006BRNXR</t>
         </is>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
-          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
+          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm [LCSC: LCSC에 없음 (차량용 LMR36006FSCQRNXRQ1 C2869760은 다른 품번·재고 16개)]</t>
         </is>
       </c>
       <c r="J55" s="19" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>3.5</v>
+        <v>1.6</v>
       </c>
       <c r="L55" s="20">
         <f>D55*J55</f>
@@ -5015,14 +5011,10 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="O55" s="16" t="inlineStr">
-        <is>
-          <t>C48263</t>
-        </is>
-      </c>
+      <c r="O55" s="16" t="inlineStr"/>
       <c r="P55" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -5032,25 +5024,25 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>U7 U8</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>DAC8760IPWP</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
@@ -5060,19 +5052,19 @@
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>DAC8760IPWPR</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
+          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
         </is>
       </c>
       <c r="J56" s="19" t="n">
-        <v>7.8</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>12.4</v>
+        <v>0.3</v>
       </c>
       <c r="L56" s="20">
         <f>D56*J56</f>
@@ -5089,7 +5081,7 @@
       </c>
       <c r="O56" s="16" t="inlineStr">
         <is>
-          <t>C55047</t>
+          <t>C2862740</t>
         </is>
       </c>
       <c r="P56" s="16" t="inlineStr">
@@ -5104,44 +5096,44 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>MCU</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>U9 U10</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>STM32G0B1CCT3</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-8</t>
+          <t>LQFP-48_7x7mm_P0.5mm</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>STM32G0B1CCT3</t>
         </is>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
-          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
+          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이) [LCSC: LCSC엔 85 °C 등급 CCT6 C5270241만 — 몰딩 내부 온도 때문에 125 °C 등급 유지]</t>
         </is>
       </c>
       <c r="J57" s="19" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K57" s="19" t="n">
         <v>2.5</v>
@@ -5159,14 +5151,10 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="O57" s="16" t="inlineStr">
-        <is>
-          <t>C3148140</t>
-        </is>
-      </c>
+      <c r="O57" s="16" t="inlineStr"/>
       <c r="P57" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -5176,12 +5164,12 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
@@ -5189,34 +5177,34 @@
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>THVD2410DGKR</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>VSSOP-8_3.0x3.0mm_P0.65mm</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ScioSense</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>THVD2410DGKR</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, VSSOP-8 (SOIC와 같은 핀, 외부 검수 H02 TVS 자리 확보) — THVD2450과 같은 핀 (v0.9)</t>
+          <t>정전용량-디지털 변환기 QFN24</t>
         </is>
       </c>
       <c r="J58" s="19" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>3</v>
+        <v>7.1</v>
       </c>
       <c r="L58" s="20">
         <f>D58*J58</f>
@@ -5233,7 +5221,7 @@
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
-          <t>C1858306</t>
+          <t>C2829318</t>
         </is>
       </c>
       <c r="P58" s="16" t="inlineStr">
@@ -5248,25 +5236,25 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>U12 U13</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
@@ -5276,19 +5264,19 @@
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="I59" s="17" t="inlineStr">
         <is>
-          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
+          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
         </is>
       </c>
       <c r="J59" s="19" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="L59" s="20">
         <f>D59*J59</f>
@@ -5300,12 +5288,12 @@
       </c>
       <c r="N59" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="O59" s="16" t="inlineStr">
         <is>
-          <t>C221351</t>
+          <t>C48263</t>
         </is>
       </c>
       <c r="P59" s="16" t="inlineStr">
@@ -5325,20 +5313,20 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U7 U8</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>DAC8760IPWP</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
+          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
@@ -5348,19 +5336,19 @@
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>DAC8760IPWPR</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
+          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
         </is>
       </c>
       <c r="J60" s="19" t="n">
-        <v>0.08</v>
+        <v>7.8</v>
       </c>
       <c r="K60" s="19" t="n">
-        <v>0.2</v>
+        <v>12.4</v>
       </c>
       <c r="L60" s="20">
         <f>D60*J60</f>
@@ -5372,12 +5360,12 @@
       </c>
       <c r="N60" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="O60" s="16" t="inlineStr">
         <is>
-          <t>C91874</t>
+          <t>C55047</t>
         </is>
       </c>
       <c r="P60" s="16" t="inlineStr">
@@ -5392,47 +5380,47 @@
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>기판</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>U9 U10</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="F61" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SOT-23-8</t>
         </is>
       </c>
       <c r="G61" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>HMT500(260313A) (E-301)</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
-          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
+          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
         </is>
       </c>
       <c r="J61" s="19" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L61" s="20">
         <f>D61*J61</f>
@@ -5442,13 +5430,21 @@
         <f>D61*K61</f>
         <v/>
       </c>
-      <c r="N61" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O61" s="16" t="inlineStr"/>
-      <c r="P61" s="16" t="inlineStr"/>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O61" s="16" t="inlineStr">
+        <is>
+          <t>C3148140</t>
+        </is>
+      </c>
+      <c r="P61" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="n">
@@ -5456,12 +5452,12 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="D62" s="18" t="n">
@@ -5469,34 +5465,34 @@
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>THVD2410DGKR</t>
         </is>
       </c>
       <c r="F62" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>VSSOP-8_3.0x3.0mm_P0.65mm</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>MK33-W (300 pF, 품번 확인 필요)</t>
+          <t>THVD2410DGKR</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
+          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, VSSOP-8 (SOIC와 같은 핀, 외부 검수 H02 TVS 자리 확보) — THVD2450과 같은 핀 (v0.9)</t>
         </is>
       </c>
       <c r="J62" s="19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L62" s="20">
         <f>D62*J62</f>
@@ -5506,13 +5502,21 @@
         <f>D62*K62</f>
         <v/>
       </c>
-      <c r="N62" s="21" t="inlineStr">
-        <is>
-          <t>사내 단가</t>
-        </is>
-      </c>
-      <c r="O62" s="16" t="inlineStr"/>
-      <c r="P62" s="16" t="inlineStr"/>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O62" s="16" t="inlineStr">
+        <is>
+          <t>C1858306</t>
+        </is>
+      </c>
+      <c r="P62" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="n">
@@ -5520,47 +5524,47 @@
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>U12 U13</t>
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>MiniSens Pt1000 F0.1</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
-          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
+          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
         </is>
       </c>
       <c r="J63" s="19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="L63" s="20">
         <f>D63*J63</f>
@@ -5570,13 +5574,21 @@
         <f>D63*K63</f>
         <v/>
       </c>
-      <c r="N63" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O63" s="16" t="inlineStr"/>
-      <c r="P63" s="16" t="inlineStr"/>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O63" s="16" t="inlineStr">
+        <is>
+          <t>C221351</t>
+        </is>
+      </c>
+      <c r="P63" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="n">
@@ -5584,12 +5596,12 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>P-204</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="D64" s="18" t="n">
@@ -5597,34 +5609,34 @@
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>M Connect</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>TBD (두텍 사용품)</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
+          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
         </is>
       </c>
       <c r="J64" s="19" t="n">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="K64" s="19" t="n">
-        <v>10</v>
+        <v>0.2</v>
       </c>
       <c r="L64" s="20">
         <f>D64*J64</f>
@@ -5634,13 +5646,21 @@
         <f>D64*K64</f>
         <v/>
       </c>
-      <c r="N64" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="O64" s="16" t="inlineStr"/>
-      <c r="P64" s="16" t="inlineStr"/>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O64" s="16" t="inlineStr">
+        <is>
+          <t>C91874</t>
+        </is>
+      </c>
+      <c r="P64" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="n">
@@ -5648,12 +5668,12 @@
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>U15</t>
         </is>
       </c>
       <c r="D65" s="18" t="n">
@@ -5661,34 +5681,34 @@
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>LMR51606YFDBVR</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>GHR-08V-S</t>
+          <t>LMR51606YFDBVR</t>
         </is>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
+          <t>벅 4–65 V 0.6 A 1.1 MHz FPWM SOT-23-6 — AO 전원 VAO 16.1 V (결정 #37, IVS320 AO rev 1.0과 같음)</t>
         </is>
       </c>
       <c r="J65" s="19" t="n">
-        <v>0.06</v>
+        <v>0.6</v>
       </c>
       <c r="K65" s="19" t="n">
-        <v>0.15</v>
+        <v>1.2</v>
       </c>
       <c r="L65" s="20">
         <f>D65*J65</f>
@@ -5700,17 +5720,17 @@
       </c>
       <c r="N65" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
-          <t>C485357</t>
+          <t>C22439294</t>
         </is>
       </c>
       <c r="P65" s="16" t="inlineStr">
         <is>
-          <t>LCSC 주문</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -5720,16 +5740,16 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>기판</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D66" s="18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
@@ -5743,24 +5763,24 @@
       </c>
       <c r="G66" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>SSHL-002T-P0.2</t>
+          <t>HMT500(260313A) (E-301)</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>GH 크림프 단자 AWG 30–26</t>
+          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
         </is>
       </c>
       <c r="J66" s="19" t="n">
-        <v>0.03</v>
+        <v>0.8</v>
       </c>
       <c r="K66" s="19" t="n">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="L66" s="20">
         <f>D66*J66</f>
@@ -5770,21 +5790,13 @@
         <f>D66*K66</f>
         <v/>
       </c>
-      <c r="N66" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O66" s="16" t="inlineStr">
-        <is>
-          <t>C189897</t>
-        </is>
-      </c>
-      <c r="P66" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N66" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O66" s="16" t="inlineStr"/>
+      <c r="P66" s="16" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="16" t="n">
@@ -5792,12 +5804,12 @@
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D67" s="18" t="n">
@@ -5815,24 +5827,24 @@
       </c>
       <c r="G67" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG28 전선</t>
+          <t>MK33-W (300 pF, 품번 확인 필요)</t>
         </is>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
         </is>
       </c>
       <c r="J67" s="19" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="K67" s="19" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="L67" s="20">
         <f>D67*J67</f>
@@ -5844,7 +5856,7 @@
       </c>
       <c r="N67" s="21" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>사내 단가</t>
         </is>
       </c>
       <c r="O67" s="16" t="inlineStr"/>
@@ -5856,12 +5868,12 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D68" s="18" t="n">
@@ -5879,24 +5891,24 @@
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>SHR-04V-S</t>
+          <t>MiniSens Pt1000 F0.1</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
+          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
         </is>
       </c>
       <c r="J68" s="19" t="n">
-        <v>0.04</v>
+        <v>0.5</v>
       </c>
       <c r="K68" s="19" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="L68" s="20">
         <f>D68*J68</f>
@@ -5906,21 +5918,13 @@
         <f>D68*K68</f>
         <v/>
       </c>
-      <c r="N68" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O68" s="16" t="inlineStr">
-        <is>
-          <t>C385125</t>
-        </is>
-      </c>
-      <c r="P68" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N68" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O68" s="16" t="inlineStr"/>
+      <c r="P68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="n">
@@ -5928,16 +5932,16 @@
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>P-204</t>
         </is>
       </c>
       <c r="D69" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5951,24 +5955,24 @@
       </c>
       <c r="G69" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>M Connect</t>
         </is>
       </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>SSH-003T-P0.2-H</t>
+          <t>TBD (두텍 사용품)</t>
         </is>
       </c>
       <c r="I69" s="17" t="inlineStr">
         <is>
-          <t>SH 크림프 단자 AWG 32–28</t>
+          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
         </is>
       </c>
       <c r="J69" s="19" t="n">
-        <v>0.03</v>
+        <v>2</v>
       </c>
       <c r="K69" s="19" t="n">
-        <v>0.06</v>
+        <v>10</v>
       </c>
       <c r="L69" s="20">
         <f>D69*J69</f>
@@ -5978,21 +5982,13 @@
         <f>D69*K69</f>
         <v/>
       </c>
-      <c r="N69" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O69" s="16" t="inlineStr">
-        <is>
-          <t>C263995</t>
-        </is>
-      </c>
-      <c r="P69" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N69" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="O69" s="16" t="inlineStr"/>
+      <c r="P69" s="16" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="16" t="n">
@@ -6005,7 +6001,7 @@
       </c>
       <c r="C70" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="D70" s="18" t="n">
@@ -6023,24 +6019,24 @@
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG30 전선</t>
+          <t>GHR-08V-S</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
         </is>
       </c>
       <c r="J70" s="19" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="K70" s="19" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="L70" s="20">
         <f>D70*J70</f>
@@ -6050,13 +6046,21 @@
         <f>D70*K70</f>
         <v/>
       </c>
-      <c r="N70" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O70" s="16" t="inlineStr"/>
-      <c r="P70" s="16" t="inlineStr"/>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O70" s="16" t="inlineStr">
+        <is>
+          <t>C485357</t>
+        </is>
+      </c>
+      <c r="P70" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="n">
@@ -6064,47 +6068,47 @@
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>조립</t>
+          <t>하네스</t>
         </is>
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="n">
+        <v>8</v>
+      </c>
+      <c r="E71" s="16" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="D71" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" s="16" t="inlineStr">
+      <c r="F71" s="16" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F71" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="G71" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>SMT 양면 실장</t>
+          <t>SSHL-002T-P0.2</t>
         </is>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
-          <t>1k 기준 조립비</t>
+          <t>GH 크림프 단자 AWG 30–26</t>
         </is>
       </c>
       <c r="J71" s="19" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>4</v>
+        <v>0.06</v>
       </c>
       <c r="L71" s="20">
         <f>D71*J71</f>
@@ -6114,26 +6118,370 @@
         <f>D71*K71</f>
         <v/>
       </c>
-      <c r="N71" s="21" t="inlineStr">
+      <c r="N71" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O71" s="16" t="inlineStr">
+        <is>
+          <t>C189897</t>
+        </is>
+      </c>
+      <c r="P71" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C72" s="17" t="inlineStr">
+        <is>
+          <t>W-2</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F72" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H72" s="17" t="inlineStr">
+        <is>
+          <t>PTFE AWG28 전선</t>
+        </is>
+      </c>
+      <c r="I72" s="17" t="inlineStr">
+        <is>
+          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+        </is>
+      </c>
+      <c r="J72" s="19" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K72" s="19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L72" s="20">
+        <f>D72*J72</f>
+        <v/>
+      </c>
+      <c r="M72" s="20">
+        <f>D72*K72</f>
+        <v/>
+      </c>
+      <c r="N72" s="21" t="inlineStr">
         <is>
           <t>추정</t>
         </is>
       </c>
-      <c r="O71" s="16" t="inlineStr"/>
-      <c r="P71" s="16" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="I72" s="3" t="inlineStr">
+      <c r="O72" s="16" t="inlineStr"/>
+      <c r="P72" s="16" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C73" s="17" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F73" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" s="16" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="H73" s="17" t="inlineStr">
+        <is>
+          <t>SHR-04V-S</t>
+        </is>
+      </c>
+      <c r="I73" s="17" t="inlineStr">
+        <is>
+          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
+        </is>
+      </c>
+      <c r="J73" s="19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K73" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L73" s="20">
+        <f>D73*J73</f>
+        <v/>
+      </c>
+      <c r="M73" s="20">
+        <f>D73*K73</f>
+        <v/>
+      </c>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O73" s="16" t="inlineStr">
+        <is>
+          <t>C385125</t>
+        </is>
+      </c>
+      <c r="P73" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C74" s="17" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>SSH-003T-P0.2-H</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>SH 크림프 단자 AWG 32–28</t>
+        </is>
+      </c>
+      <c r="J74" s="19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="K74" s="19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L74" s="20">
+        <f>D74*J74</f>
+        <v/>
+      </c>
+      <c r="M74" s="20">
+        <f>D74*K74</f>
+        <v/>
+      </c>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O74" s="16" t="inlineStr">
+        <is>
+          <t>C263995</t>
+        </is>
+      </c>
+      <c r="P74" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>하네스</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>W-1</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
+        <is>
+          <t>PTFE AWG30 전선</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+        </is>
+      </c>
+      <c r="J75" s="19" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K75" s="19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L75" s="20">
+        <f>D75*J75</f>
+        <v/>
+      </c>
+      <c r="M75" s="20">
+        <f>D75*K75</f>
+        <v/>
+      </c>
+      <c r="N75" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O75" s="16" t="inlineStr"/>
+      <c r="P75" s="16" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="16" t="inlineStr">
+        <is>
+          <t>조립</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E76" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F76" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" s="17" t="inlineStr">
+        <is>
+          <t>SMT 양면 실장</t>
+        </is>
+      </c>
+      <c r="I76" s="17" t="inlineStr">
+        <is>
+          <t>1k 기준 조립비</t>
+        </is>
+      </c>
+      <c r="J76" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K76" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L76" s="20">
+        <f>D76*J76</f>
+        <v/>
+      </c>
+      <c r="M76" s="20">
+        <f>D76*K76</f>
+        <v/>
+      </c>
+      <c r="N76" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O76" s="16" t="inlineStr"/>
+      <c r="P76" s="16" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="I77" s="3" t="inlineStr">
         <is>
           <t>합계 (1대분)</t>
         </is>
       </c>
-      <c r="L72" s="23">
-        <f>SUM(L2:L71)</f>
-        <v/>
-      </c>
-      <c r="M72" s="23">
-        <f>SUM(M2:M71)</f>
+      <c r="L77" s="23">
+        <f>SUM(L2:L76)</f>
+        <v/>
+      </c>
+      <c r="M77" s="23">
+        <f>SUM(M2:M76)</f>
         <v/>
       </c>
     </row>

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -262,8 +262,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P76" headerRowCount="1">
-  <autoFilter ref="A1:P76"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P74" headerRowCount="1">
+  <autoFilter ref="A1:P74"/>
   <tableColumns count="16">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="분류"/>
@@ -654,15 +654,15 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A7)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A7)</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A7)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A7)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A7)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A7)</f>
         <v/>
       </c>
       <c r="E7" s="10">
@@ -681,15 +681,15 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A8)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A8)</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A8)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A8)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A8)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A8)</f>
         <v/>
       </c>
       <c r="E8" s="10">
@@ -708,15 +708,15 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A9)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A9)</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A9)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A9)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A9)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A9)</f>
         <v/>
       </c>
       <c r="E9" s="10">
@@ -735,15 +735,15 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A10)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A10)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A10)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A10)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A10)</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -762,15 +762,15 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A11)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A11)</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A11)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A11)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A11)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A11)</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -789,15 +789,15 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A12)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A12)</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A12)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A12)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A12)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A12)</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -816,15 +816,15 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A13)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A13)</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A13)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A13)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A13)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A13)</f>
         <v/>
       </c>
       <c r="E13" s="10">
@@ -843,15 +843,15 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A14)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A14)</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A14)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A14)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A14)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A14)</f>
         <v/>
       </c>
       <c r="E14" s="10">
@@ -870,15 +870,15 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A15)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A15)</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A15)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A15)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A15)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A15)</f>
         <v/>
       </c>
       <c r="E15" s="10">
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A16)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A16)</f>
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A16)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A16)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A16)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A16)</f>
         <v/>
       </c>
       <c r="E16" s="10">
@@ -924,15 +924,15 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A17)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A17)</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A17)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A17)</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A17)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A17)</f>
         <v/>
       </c>
       <c r="E17" s="10">
@@ -951,15 +951,15 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A18)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A18)</f>
         <v/>
       </c>
       <c r="C18" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A18)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A18)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A18)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A18)</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -978,15 +978,15 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$76,A19)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$74,A19)</f>
         <v/>
       </c>
       <c r="C19" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$76,'부품리스트'!$B$2:$B$76,A19)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A19)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$76,'부품리스트'!$B$2:$B$76,A19)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A19)</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P77"/>
+  <dimension ref="A1:P75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1545,11 +1545,11 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>C6 C10</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="D7" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
@@ -1689,11 +1689,11 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>C9 C12 C26</t>
+          <t>C12 C26</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
@@ -1756,47 +1756,47 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>C11</t>
+          <t>C13 C25</t>
         </is>
       </c>
       <c r="D10" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="16" t="inlineStr">
         <is>
-          <t>20p C0G</t>
+          <t>10u</t>
         </is>
       </c>
       <c r="F10" s="16" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H10" s="17" t="inlineStr">
         <is>
-          <t>CL05C200JB5NNNC</t>
+          <t>GRM31CR71E106KA12L</t>
         </is>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
-          <t>MLCC 20 pF 50 V C0G 0402 (벅 CFF)</t>
+          <t>MLCC 10 uF 25 V X7R 1206 (v0.9: 0805 X5R → 1206 X7R, DC 바이어스 여유)</t>
         </is>
       </c>
       <c r="J10" s="19" t="n">
-        <v>0.002</v>
+        <v>0.05</v>
       </c>
       <c r="K10" s="19" t="n">
-        <v>0.005</v>
+        <v>0.12</v>
       </c>
       <c r="L10" s="20">
         <f>D10*J10</f>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="N10" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O10" s="16" t="inlineStr">
         <is>
-          <t>C32950</t>
+          <t>C77093</t>
         </is>
       </c>
       <c r="P10" s="16" t="inlineStr">
@@ -1828,47 +1828,47 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>C13 C25</t>
+          <t>C16</t>
         </is>
       </c>
       <c r="D11" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>10u</t>
+          <t>220n 100V</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
         <is>
-          <t>C_1206_3216Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G11" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H11" s="17" t="inlineStr">
         <is>
-          <t>GRM31CR71E106KA12L</t>
+          <t>CL21B224KCFSFNE</t>
         </is>
       </c>
       <c r="I11" s="17" t="inlineStr">
         <is>
-          <t>MLCC 10 uF 25 V X7R 1206 (v0.9: 0805 X5R → 1206 X7R, DC 바이어스 여유)</t>
+          <t>MLCC 220 nF 100 V X7R 0805 (LMR36006 VIN–PGND 핀마다. LCSC에 0603 없음 → 0805)</t>
         </is>
       </c>
       <c r="J11" s="19" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="K11" s="19" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="L11" s="20">
         <f>D11*J11</f>
@@ -1880,12 +1880,12 @@
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>C77093</t>
+          <t>C307542</t>
         </is>
       </c>
       <c r="P11" s="16" t="inlineStr">
@@ -1900,20 +1900,20 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>C16 C17</t>
+          <t>C18</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>220n 100V</t>
+          <t>4.7u</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -1923,24 +1923,24 @@
       </c>
       <c r="G12" s="16" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t>CL21B224KCFSFNE</t>
+          <t>GRM21BR71E475KA73L</t>
         </is>
       </c>
       <c r="I12" s="17" t="inlineStr">
         <is>
-          <t>MLCC 220 nF 100 V X7R 0805 (LMR36006 VIN–PGND 핀마다. LCSC에 0603 없음 → 0805)</t>
+          <t>MLCC 4.7 uF 25 V X7R 0805 (품번 확인 필요)</t>
         </is>
       </c>
       <c r="J12" s="19" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="L12" s="20">
         <f>D12*J12</f>
@@ -1950,14 +1950,14 @@
         <f>D12*K12</f>
         <v/>
       </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>LCSC</t>
+      <c r="N12" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="O12" s="16" t="inlineStr">
         <is>
-          <t>C307542</t>
+          <t>C162427</t>
         </is>
       </c>
       <c r="P12" s="16" t="inlineStr">
@@ -1972,12 +1972,12 @@
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C13" s="17" t="inlineStr">
         <is>
-          <t>C18</t>
+          <t>C22</t>
         </is>
       </c>
       <c r="D13" s="18" t="n">
@@ -1985,34 +1985,34 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>4.7u</t>
+          <t>330p C0G 1%</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G13" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>GRM21BR71E475KA73L</t>
+          <t>VJ0603A331GXACW1BC</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>MLCC 4.7 uF 25 V X7R 0805 (품번 확인 필요)</t>
+          <t>MLCC 330 pF 50 V C0G ±1% 0603 (PCAP04 기준 C, 센서 MK33-W 300 pF) [LCSC: ±2 % (LCSC에 ±1 % 없음) — 기준 C 절대값은 교정으로 제거, C0G라 온도 안정]</t>
         </is>
       </c>
       <c r="J13" s="19" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="K13" s="19" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="L13" s="20">
         <f>D13*J13</f>
@@ -2022,14 +2022,14 @@
         <f>D13*K13</f>
         <v/>
       </c>
-      <c r="N13" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>C162427</t>
+          <t>C3898227</t>
         </is>
       </c>
       <c r="P13" s="16" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>C22</t>
+          <t>C24</t>
         </is>
       </c>
       <c r="D14" s="18" t="n">
@@ -2057,34 +2057,34 @@
       </c>
       <c r="E14" s="16" t="inlineStr">
         <is>
-          <t>330p C0G 1%</t>
+          <t>22u 10V</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_1206_3216Metric</t>
         </is>
       </c>
       <c r="G14" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H14" s="17" t="inlineStr">
         <is>
-          <t>VJ0603A331GXACW1BC</t>
+          <t>GRM31CR71A226KE15L</t>
         </is>
       </c>
       <c r="I14" s="17" t="inlineStr">
         <is>
-          <t>MLCC 330 pF 50 V C0G ±1% 0603 (PCAP04 기준 C, 센서 MK33-W 300 pF) [LCSC: ±2 % (LCSC에 ±1 % 없음) — 기준 C 절대값은 교정으로 제거, C0G라 온도 안정]</t>
+          <t>MLCC 22 uF 10 V X7R 1206 (PCAP04 VDD33 ≥ 10 µF 실효, 품번 확인 필요)</t>
         </is>
       </c>
       <c r="J14" s="19" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="K14" s="19" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="L14" s="20">
         <f>D14*J14</f>
@@ -2094,14 +2094,14 @@
         <f>D14*K14</f>
         <v/>
       </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
+      <c r="N14" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="O14" s="16" t="inlineStr">
         <is>
-          <t>C3898227</t>
+          <t>C91604</t>
         </is>
       </c>
       <c r="P14" s="16" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>C24</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="D15" s="18" t="n">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="E15" s="16" t="inlineStr">
         <is>
-          <t>22u 10V</t>
+          <t>10n C0G</t>
         </is>
       </c>
       <c r="F15" s="16" t="inlineStr">
         <is>
-          <t>C_1206_3216Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -2144,19 +2144,19 @@
       </c>
       <c r="H15" s="17" t="inlineStr">
         <is>
-          <t>GRM31CR71A226KE15L</t>
+          <t>GRM1885C1H103JA01D</t>
         </is>
       </c>
       <c r="I15" s="17" t="inlineStr">
         <is>
-          <t>MLCC 22 uF 10 V X7R 1206 (PCAP04 VDD33 ≥ 10 µF 실효, 품번 확인 필요)</t>
+          <t>MLCC 10 nF 50 V C0G 0603 (ADS1220 차동 필터)</t>
         </is>
       </c>
       <c r="J15" s="19" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="K15" s="19" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="L15" s="20">
         <f>D15*J15</f>
@@ -2166,14 +2166,14 @@
         <f>D15*K15</f>
         <v/>
       </c>
-      <c r="N15" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
         </is>
       </c>
       <c r="O15" s="16" t="inlineStr">
         <is>
-          <t>C91604</t>
+          <t>C85973</t>
         </is>
       </c>
       <c r="P15" s="16" t="inlineStr">
@@ -2188,20 +2188,20 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C41 C51</t>
         </is>
       </c>
       <c r="D16" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="16" t="inlineStr">
         <is>
-          <t>10n C0G</t>
+          <t>1n 100V</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
@@ -2216,19 +2216,19 @@
       </c>
       <c r="H16" s="17" t="inlineStr">
         <is>
-          <t>GRM1885C1H103JA01D</t>
+          <t>GRM188R72A102KA01D</t>
         </is>
       </c>
       <c r="I16" s="17" t="inlineStr">
         <is>
-          <t>MLCC 10 nF 50 V C0G 0603 (ADS1220 차동 필터)</t>
+          <t>MLCC 1 nF 100 V X7R 0603</t>
         </is>
       </c>
       <c r="J16" s="19" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K16" s="19" t="n">
         <v>0.01</v>
-      </c>
-      <c r="K16" s="19" t="n">
-        <v>0.03</v>
       </c>
       <c r="L16" s="20">
         <f>D16*J16</f>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="O16" s="16" t="inlineStr">
         <is>
-          <t>C85973</t>
+          <t>C97897</t>
         </is>
       </c>
       <c r="P16" s="16" t="inlineStr">
@@ -2260,47 +2260,47 @@
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>C41 C51</t>
+          <t>C42 C45 C52 C55</t>
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E17" s="16" t="inlineStr">
         <is>
-          <t>1n 100V</t>
+          <t>100n 50V</t>
         </is>
       </c>
       <c r="F17" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G17" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
         <is>
-          <t>GRM188R72A102KA01D</t>
+          <t>CC0805KRX7R9BB104</t>
         </is>
       </c>
       <c r="I17" s="17" t="inlineStr">
         <is>
-          <t>MLCC 1 nF 100 V X7R 0603</t>
+          <t>MLCC 100 nF 50 V X7R 0805</t>
         </is>
       </c>
       <c r="J17" s="19" t="n">
-        <v>0.004</v>
+        <v>0.01</v>
       </c>
       <c r="K17" s="19" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L17" s="20">
         <f>D17*J17</f>
@@ -2317,12 +2317,12 @@
       </c>
       <c r="O17" s="16" t="inlineStr">
         <is>
-          <t>C97897</t>
+          <t>C49678</t>
         </is>
       </c>
       <c r="P17" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -2332,25 +2332,25 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>C42 C45 C52 C55</t>
+          <t>C46 C56 C62</t>
         </is>
       </c>
       <c r="D18" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E18" s="16" t="inlineStr">
         <is>
-          <t>100n 50V</t>
+          <t>100n/50V</t>
         </is>
       </c>
       <c r="F18" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>C_0603_1608Metric</t>
         </is>
       </c>
       <c r="G18" s="16" t="inlineStr">
@@ -2360,19 +2360,19 @@
       </c>
       <c r="H18" s="17" t="inlineStr">
         <is>
-          <t>CC0805KRX7R9BB104</t>
+          <t>CC0603KRX7R9BB104</t>
         </is>
       </c>
       <c r="I18" s="17" t="inlineStr">
         <is>
-          <t>MLCC 100 nF 50 V X7R 0805</t>
+          <t>MLCC 100 nF 50 V X7R 0603 (VS_CLAMP 약 24 V)</t>
         </is>
       </c>
       <c r="J18" s="19" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="K18" s="19" t="n">
         <v>0.01</v>
-      </c>
-      <c r="K18" s="19" t="n">
-        <v>0.03</v>
       </c>
       <c r="L18" s="20">
         <f>D18*J18</f>
@@ -2384,12 +2384,12 @@
       </c>
       <c r="N18" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O18" s="16" t="inlineStr">
         <is>
-          <t>C49678</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="P18" s="16" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>C46 C56 C62</t>
+          <t>C47 C57</t>
         </is>
       </c>
       <c r="D19" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" s="16" t="inlineStr">
         <is>
-          <t>100n/50V</t>
+          <t>4.7n</t>
         </is>
       </c>
       <c r="F19" s="16" t="inlineStr">
         <is>
-          <t>C_0603_1608Metric</t>
+          <t>C_0402_1005Metric</t>
         </is>
       </c>
       <c r="G19" s="16" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>CC0603KRX7R9BB104</t>
+          <t>CL05B472KB5NNNC</t>
         </is>
       </c>
       <c r="I19" s="17" t="inlineStr">
         <is>
-          <t>MLCC 100 nF 50 V X7R 0603 (VS_CLAMP 약 24 V)</t>
+          <t>MLCC 4.7 nF 50 V X7R 0402 (DAC VOUT–CMP 보상)</t>
         </is>
       </c>
       <c r="J19" s="19" t="n">
-        <v>0.004</v>
+        <v>0.002</v>
       </c>
       <c r="K19" s="19" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="L19" s="20">
         <f>D19*J19</f>
@@ -2461,12 +2461,12 @@
       </c>
       <c r="O19" s="16" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C84705</t>
         </is>
       </c>
       <c r="P19" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>C47 C57</t>
+          <t>C48 C58</t>
         </is>
       </c>
       <c r="D20" s="18" t="n">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="E20" s="16" t="inlineStr">
         <is>
-          <t>4.7n</t>
+          <t>100p C0G</t>
         </is>
       </c>
       <c r="F20" s="16" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="H20" s="17" t="inlineStr">
         <is>
-          <t>CL05B472KB5NNNC</t>
+          <t>CL05C101JB5NNNC</t>
         </is>
       </c>
       <c r="I20" s="17" t="inlineStr">
         <is>
-          <t>MLCC 4.7 nF 50 V X7R 0402 (DAC VOUT–CMP 보상)</t>
+          <t>MLCC 100 pF 50 V C0G 0402 (DAC CMP–GND)</t>
         </is>
       </c>
       <c r="J20" s="19" t="n">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="O20" s="16" t="inlineStr">
         <is>
-          <t>C84705</t>
+          <t>C26409</t>
         </is>
       </c>
       <c r="P20" s="16" t="inlineStr">
@@ -2553,20 +2553,20 @@
       </c>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>C48 C58</t>
+          <t>C61</t>
         </is>
       </c>
       <c r="D21" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
-          <t>100p C0G</t>
+          <t>2.2u 50V</t>
         </is>
       </c>
       <c r="F21" s="16" t="inlineStr">
         <is>
-          <t>C_0402_1005Metric</t>
+          <t>C_0805_2012Metric</t>
         </is>
       </c>
       <c r="G21" s="16" t="inlineStr">
@@ -2576,19 +2576,19 @@
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>CL05C101JB5NNNC</t>
+          <t>CL21B225KBFNNNE</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>MLCC 100 pF 50 V C0G 0402 (DAC CMP–GND)</t>
+          <t>MLCC 2.2 uF 50 V X7R 0805 (VAO 벅 입력) [LCSC: LCSC 번호는 JLC 화면에서 같은 품번 선택 (검색에서 C 번호 미확인)]</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>0.005</v>
+        <v>0.05</v>
       </c>
       <c r="L21" s="20">
         <f>D21*J21</f>
@@ -2603,11 +2603,7 @@
           <t>LCSC</t>
         </is>
       </c>
-      <c r="O21" s="16" t="inlineStr">
-        <is>
-          <t>C26409</t>
-        </is>
-      </c>
+      <c r="O21" s="16" t="inlineStr"/>
       <c r="P21" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -2620,12 +2616,12 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>C61</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="D22" s="18" t="n">
@@ -2633,34 +2629,34 @@
       </c>
       <c r="E22" s="16" t="inlineStr">
         <is>
-          <t>2.2u 50V</t>
+          <t>SMDJ36CA</t>
         </is>
       </c>
       <c r="F22" s="16" t="inlineStr">
         <is>
-          <t>C_0805_2012Metric</t>
+          <t>D_SMC</t>
         </is>
       </c>
       <c r="G22" s="16" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Littelfuse</t>
         </is>
       </c>
       <c r="H22" s="17" t="inlineStr">
         <is>
-          <t>CL21B225KBFNNNE</t>
+          <t>5.0SMDJ36CA</t>
         </is>
       </c>
       <c r="I22" s="17" t="inlineStr">
         <is>
-          <t>MLCC 2.2 uF 50 V X7R 0805 (VAO 벅 입력) [LCSC: LCSC 번호는 JLC 화면에서 같은 품번 선택 (검색에서 C 번호 미확인)]</t>
+          <t>TVS 5000 W 36 V 양방향 SMC (입력 1단. LCSC — 같은 36 V·SMC, 3 kW → 5 kW)</t>
         </is>
       </c>
       <c r="J22" s="19" t="n">
-        <v>0.02</v>
+        <v>0.3</v>
       </c>
       <c r="K22" s="19" t="n">
-        <v>0.05</v>
+        <v>0.7</v>
       </c>
       <c r="L22" s="20">
         <f>D22*J22</f>
@@ -2675,7 +2671,11 @@
           <t>LCSC</t>
         </is>
       </c>
-      <c r="O22" s="16" t="inlineStr"/>
+      <c r="O22" s="16" t="inlineStr">
+        <is>
+          <t>C141713</t>
+        </is>
+      </c>
       <c r="P22" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -2693,42 +2693,42 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D2 D30 D40 D60 D61</t>
         </is>
       </c>
       <c r="D23" s="18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
-          <t>SMDJ36CA</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="F23" s="16" t="inlineStr">
         <is>
-          <t>D_SMC</t>
+          <t>Texas_DRB0008A_PadFloat</t>
         </is>
       </c>
       <c r="G23" s="16" t="inlineStr">
         <is>
-          <t>Littelfuse</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
         <is>
-          <t>5.0SMDJ36CA</t>
+          <t>TVS3301DRBR</t>
         </is>
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>TVS 5000 W 36 V 양방향 SMC (입력 1단. LCSC — 같은 36 V·SMC, 3 kW → 5 kW)</t>
+          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: 재고 적음 (검색 시 약 88개) — v0.9 수량 5개 (D2, D30, D40, D60, D61)]</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="K23" s="19" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L23" s="20">
         <f>D23*J23</f>
@@ -2740,12 +2740,12 @@
       </c>
       <c r="N23" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O23" s="16" t="inlineStr">
         <is>
-          <t>C141713</t>
+          <t>C2864392</t>
         </is>
       </c>
       <c r="P23" s="16" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>D2 D30 D40 D60 D61</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="D24" s="18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>TVS3301DRBR</t>
+          <t>PMEG10010ELR</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
         <is>
-          <t>Texas_DRB0008A_PadFloat</t>
+          <t>D_SOD-123F</t>
         </is>
       </c>
       <c r="G24" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Nexperia</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
         <is>
-          <t>TVS3301DRBR</t>
+          <t>PMEG10010ELR-QX</t>
         </is>
       </c>
       <c r="I24" s="17" t="inlineStr">
         <is>
-          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: 재고 적음 (검색 시 약 88개) — v0.9 수량 5개 (D2, D30, D40, D60, D61)]</t>
+          <t>쇼트키 100 V 1 A 저누설 SOD-123W (SOD-123F 풋프린트) — eFuse 앞 직렬, 음(−) 서지·역극성 차단 (외부 검수 H01)</t>
         </is>
       </c>
       <c r="J24" s="19" t="n">
-        <v>0.35</v>
+        <v>0.05</v>
       </c>
       <c r="K24" s="19" t="n">
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="L24" s="20">
         <f>D24*J24</f>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="N24" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O24" s="16" t="inlineStr">
         <is>
-          <t>C2864392</t>
+          <t>C5361358</t>
         </is>
       </c>
       <c r="P24" s="16" t="inlineStr">
@@ -2832,25 +2832,25 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D41 D51</t>
         </is>
       </c>
       <c r="D25" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>PMEG10010ELR</t>
+          <t>BAS70-04</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>D_SOD-123F</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
@@ -2860,19 +2860,19 @@
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>PMEG10010ELR-QX</t>
+          <t>BAS70-04,215</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>쇼트키 100 V 1 A 저누설 SOD-123W (SOD-123F 풋프린트) — eFuse 앞 직렬, 음(−) 서지·역극성 차단 (외부 검수 H01)</t>
+          <t>쇼트키 2개 직렬 70 V SOT-23 — DAC 출력 클램프 (1 A, 2 K, 3 공통)</t>
         </is>
       </c>
       <c r="J25" s="19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K25" s="19" t="n">
         <v>0.05</v>
-      </c>
-      <c r="K25" s="19" t="n">
-        <v>0.12</v>
       </c>
       <c r="L25" s="20">
         <f>D25*J25</f>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>C5361358</t>
+          <t>C389351</t>
         </is>
       </c>
       <c r="P25" s="16" t="inlineStr">
@@ -2904,47 +2904,47 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>D41 D51</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>BAS70-04</t>
+          <t>600R@100MHz</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>L_0603_1608Metric</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>Nexperia</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>BAS70-04,215</t>
+          <t>BLM18KG601SN1D</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>쇼트키 2개 직렬 70 V SOT-23 — DAC 출력 클램프 (1 A, 2 K, 3 공통)</t>
+          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="L26" s="20">
         <f>D26*J26</f>
@@ -2956,12 +2956,12 @@
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O26" s="16" t="inlineStr">
         <is>
-          <t>C389351</t>
+          <t>C85833</t>
         </is>
       </c>
       <c r="P26" s="16" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>GDT1</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
@@ -2989,34 +2989,34 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>600R@100MHz</t>
+          <t>2035-25-SM</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>L_0603_1608Metric</t>
+          <t>GDT_Bourns_2035-xx-SM</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>BLM18KG601SN1D</t>
+          <t>2035-25-SM-RPLF</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
+          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>0.03</v>
+        <v>1</v>
       </c>
       <c r="L27" s="20">
         <f>D27*J27</f>
@@ -3028,12 +3028,12 @@
       </c>
       <c r="N27" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O27" s="16" t="inlineStr">
         <is>
-          <t>C85833</t>
+          <t>C3660127</t>
         </is>
       </c>
       <c r="P27" s="16" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>GDT1</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
@@ -3061,34 +3061,34 @@
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>2035-25-SM</t>
+          <t>SM08B-GHS-TB</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>GDT_Bourns_2035-xx-SM</t>
+          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>2035-25-SM-RPLF</t>
+          <t>SM08B-GHS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
+          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="L28" s="20">
         <f>D28*J28</f>
@@ -3100,12 +3100,12 @@
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>C3660127</t>
+          <t>C265111</t>
         </is>
       </c>
       <c r="P28" s="16" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
@@ -3133,34 +3133,34 @@
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>TC2030-IDC-NL</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB(LF)(SN)</t>
+          <t>(PCB 패드만)</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
+          <t>SWD 기록용 패드 — 부품 실장 없음</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="L29" s="20">
         <f>D29*J29</f>
@@ -3172,19 +3172,11 @@
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O29" s="16" t="inlineStr">
-        <is>
-          <t>C265111</t>
-        </is>
-      </c>
-      <c r="P29" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="inlineStr"/>
+      <c r="P29" s="16" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="n">
@@ -3192,12 +3184,12 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
@@ -3205,34 +3197,34 @@
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>TC2030-IDC-NL</t>
+          <t>SM04B-SRSS-TB</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>(PCB 패드만)</t>
+          <t>SM04B-SRSS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>SWD 기록용 패드 — 부품 실장 없음</t>
+          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L30" s="20">
         <f>D30*J30</f>
@@ -3244,11 +3236,19 @@
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O30" s="16" t="inlineStr"/>
-      <c r="P30" s="16" t="inlineStr"/>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr">
+        <is>
+          <t>C160404</t>
+        </is>
+      </c>
+      <c r="P30" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
@@ -3269,34 +3269,34 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>CHASSIS wire</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
+          <t>SolderWire_Chassis_D0.6mm</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB(LF)(SN)</t>
+          <t>PCB 납땜 구멍 (부품 없음)</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
+          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
         </is>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L31" s="20">
         <f>D31*J31</f>
@@ -3308,19 +3308,11 @@
       </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O31" s="16" t="inlineStr">
-        <is>
-          <t>C160404</t>
-        </is>
-      </c>
-      <c r="P31" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr"/>
+      <c r="P31" s="16" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n">
@@ -3328,12 +3320,12 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
@@ -3341,34 +3333,34 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>CHASSIS wire</t>
+          <t>CMC 1mH 0.8A</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>SolderWire_Chassis_D0.6mm</t>
+          <t>L_CommonMode_Wuerth_WE-SL2</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>PCB 납땜 구멍 (부품 없음)</t>
+          <t>SRF0905-102Y</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
+          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="L32" s="20">
         <f>D32*J32</f>
@@ -3378,13 +3370,21 @@
         <f>D32*K32</f>
         <v/>
       </c>
-      <c r="N32" s="16" t="inlineStr">
-        <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O32" s="16" t="inlineStr"/>
-      <c r="P32" s="16" t="inlineStr"/>
+      <c r="N32" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr">
+        <is>
+          <t>C2651138</t>
+        </is>
+      </c>
+      <c r="P32" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="n">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
@@ -3405,34 +3405,34 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>CMC 1mH 0.8A</t>
+          <t>10uH</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>L_CommonMode_Wuerth_WE-SL2</t>
+          <t>L_Taiyo-Yuden_NR-40xx</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>SXN</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>SRF0905-102Y</t>
+          <t>SMNR4020-10UH</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
+          <t>파워 인덕터 10 µH ±20 % 0.62 A 0.95 Ω 4 × 4 × 2 mm (NR-40xx 랜드) — 5 V 벅 (부하 약 60 mA) [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
-        <v>0.5</v>
+        <v>0.05</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>1.2</v>
+        <v>0.12</v>
       </c>
       <c r="L33" s="20">
         <f>D33*J33</f>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>C2651138</t>
+          <t>C135263</t>
         </is>
       </c>
       <c r="P33" s="16" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
@@ -3477,34 +3477,34 @@
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>15uH</t>
+          <t>22uH</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>L_Coilcraft_XAL4040-XXX</t>
+          <t>L_Taiyo-Yuden_NR-40xx</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>Coilcraft</t>
+          <t>(LCSC)</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>XGL4040-153MEC</t>
+          <t>SMNR4020-22UH</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 15 µH 3.6 A, 4 × 4 × 4.0 mm (XAL4040 풋프린트. LCSC — 4030형은 LCSC에 없음)</t>
+          <t>파워 인덕터 22 µH ±20 % 1.05 A 455 mΩ 4 × 4 × 2 mm (NR-40xx 랜드) — VAO 벅 [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
-        <v>0.3</v>
+        <v>0.05</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>0.7</v>
+        <v>0.15</v>
       </c>
       <c r="L34" s="20">
         <f>D34*J34</f>
@@ -3514,14 +3514,14 @@
         <f>D34*K34</f>
         <v/>
       </c>
-      <c r="N34" s="16" t="inlineStr">
-        <is>
-          <t>LCSC</t>
+      <c r="N34" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="O34" s="16" t="inlineStr">
         <is>
-          <t>C3911667</t>
+          <t>C135264</t>
         </is>
       </c>
       <c r="P34" s="16" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D35" s="18" t="n">
@@ -3549,27 +3549,27 @@
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>22uH</t>
+          <t>4.7R 1W pulse</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>L_Taiyo-Yuden_NR-40xx</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>(LCSC)</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>SMNR4020-22UH</t>
+          <t>CRCW25124R70FKEG</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 22 µH ±20 % 1.05 A 455 mΩ 4 × 4 × 2 mm (NR-40xx 랜드) — VAO 벅 [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
+          <t>CRCW 2512 4.7 Ω 1% 1 W (결정 #38: JLC 부품 — 펄스 내성 HP형 대신 일반형, 서지 시험 T1로 확인) [LCSC: 결정 #38: 일반형 (HP 대신)]</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">
@@ -3586,14 +3586,14 @@
         <f>D35*K35</f>
         <v/>
       </c>
-      <c r="N35" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O35" s="16" t="inlineStr">
         <is>
-          <t>C135264</t>
+          <t>C242563</t>
         </is>
       </c>
       <c r="P35" s="16" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
@@ -3621,34 +3621,34 @@
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>4.7R 1W pulse</t>
+          <t>1M HV</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_1206_3216Metric</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>ROHM</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>CRCW25124R70FKEGHP</t>
+          <t>KTR18EZPF1004</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>CRCW-HP 2512 4.7 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (입력 직렬, 1단·2단 서지 분담). MELF → 2512 (결정 #34) [LCSC: 펄스 내성(HP)형은 LCSC에 없음. LCSC 일반형 CRCW25124R70FKEG C242563은 서지 에너지 확인 후에만]</t>
+          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
         </is>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="L36" s="20">
         <f>D36*J36</f>
@@ -3660,13 +3660,17 @@
       </c>
       <c r="N36" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
-        </is>
-      </c>
-      <c r="O36" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O36" s="16" t="inlineStr">
+        <is>
+          <t>C253347</t>
+        </is>
+      </c>
       <c r="P36" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3680,12 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D37" s="18" t="n">
@@ -3689,34 +3693,34 @@
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
-          <t>1M HV</t>
+          <t>866k 1%</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>R_1206_3216Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>ROHM</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>KTR18EZPF1004</t>
+          <t>RCS0603866KFKEA</t>
         </is>
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
+          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
         </is>
       </c>
       <c r="J37" s="19" t="n">
-        <v>0.02</v>
+        <v>0.002</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>0.06</v>
+        <v>0.005</v>
       </c>
       <c r="L37" s="20">
         <f>D37*J37</f>
@@ -3728,12 +3732,12 @@
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>C253347</t>
+          <t>C3954581</t>
         </is>
       </c>
       <c r="P37" s="16" t="inlineStr">
@@ -3753,7 +3757,7 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
@@ -3761,7 +3765,7 @@
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>866k 1%</t>
+          <t>97.6k 1%</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -3771,17 +3775,17 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>RCS0603866KFKEA</t>
+          <t>ERA-3AEB9762V</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
+          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
         </is>
       </c>
       <c r="J38" s="19" t="n">
@@ -3805,7 +3809,7 @@
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>C3954581</t>
+          <t>C2074558</t>
         </is>
       </c>
       <c r="P38" s="16" t="inlineStr">
@@ -3825,7 +3829,7 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="D39" s="18" t="n">
@@ -3833,7 +3837,7 @@
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>97.6k 1%</t>
+          <t>36.5k 1%</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -3843,17 +3847,17 @@
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>CAL-CHIP</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>ERA-3AEB9762V</t>
+          <t>RM06F3652CT</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
+          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
         </is>
       </c>
       <c r="J39" s="19" t="n">
@@ -3877,7 +3881,7 @@
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>C2074558</t>
+          <t>C4027587</t>
         </is>
       </c>
       <c r="P39" s="16" t="inlineStr">
@@ -3897,7 +3901,7 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
@@ -3905,7 +3909,7 @@
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>36.5k 1%</t>
+          <t>80.6k 1%</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
@@ -3915,17 +3919,17 @@
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>CAL-CHIP</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>RM06F3652CT</t>
+          <t>0603WAF8062T5E</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
+          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
         </is>
       </c>
       <c r="J40" s="19" t="n">
@@ -3949,7 +3953,7 @@
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>C4027587</t>
+          <t>C23249</t>
         </is>
       </c>
       <c r="P40" s="16" t="inlineStr">
@@ -3969,7 +3973,7 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D41" s="18" t="n">
@@ -3977,34 +3981,34 @@
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>80.6k 1%</t>
+          <t>118k 1%</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>0603WAF8062T5E</t>
+          <t>AC0402FR-07118KL</t>
         </is>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
-          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
+          <t>저항 118 kΩ 1% 0402 (5 V 벅 FB 상단)</t>
         </is>
       </c>
       <c r="J41" s="19" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="L41" s="20">
         <f>D41*J41</f>
@@ -4016,12 +4020,12 @@
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>C23249</t>
+          <t>C144804</t>
         </is>
       </c>
       <c r="P41" s="16" t="inlineStr">
@@ -4036,12 +4040,12 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>R8 R14</t>
+          <t>R9 R52</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
@@ -4049,7 +4053,7 @@
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>100k 1%</t>
+          <t>22.1k 1%</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
@@ -4064,12 +4068,12 @@
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1003TCE</t>
+          <t>0402WGF2212TCE</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0402 (벅 FB, 전원 감시)</t>
+          <t>저항 22.1 kΩ 1% 0402 (VAO 분압 하단) [LCSC: LCSC 번호 미확인 — JLC 화면에서 22.1 kΩ 1 % 0402 선택]</t>
         </is>
       </c>
       <c r="J42" s="19" t="n">
@@ -4086,19 +4090,15 @@
         <f>D42*K42</f>
         <v/>
       </c>
-      <c r="N42" s="16" t="inlineStr">
-        <is>
-          <t>LCSC</t>
-        </is>
-      </c>
-      <c r="O42" s="16" t="inlineStr">
-        <is>
-          <t>C25741</t>
-        </is>
-      </c>
+      <c r="N42" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="inlineStr"/>
       <c r="P42" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4108,25 +4108,25 @@
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R10 R11 R33 R60</t>
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>24.9k 1%</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G43" s="16" t="inlineStr">
@@ -4136,19 +4136,19 @@
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>0603WAF2492T5E</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>저항 24.9 kΩ 1% 0603 (벅 FB)</t>
+          <t>저항 10 kΩ 1% 0402 (50 V)</t>
         </is>
       </c>
       <c r="J43" s="19" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="K43" s="19" t="n">
-        <v>0.005</v>
+        <v>0.003</v>
       </c>
       <c r="L43" s="20">
         <f>D43*J43</f>
@@ -4160,17 +4160,17 @@
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>C25962</t>
+          <t>C25744</t>
         </is>
       </c>
       <c r="P43" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>R10 R11 R33 R60</t>
+          <t>R12 R13 R31 R41</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
@@ -4208,12 +4208,12 @@
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1002TCE</t>
+          <t>0402WGF1003TCE</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>저항 10 kΩ 1% 0402 (50 V)</t>
+          <t>저항 100 kΩ 1% 0402 (50 V)</t>
         </is>
       </c>
       <c r="J44" s="19" t="n">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C25741</t>
         </is>
       </c>
       <c r="P44" s="16" t="inlineStr">
@@ -4252,20 +4252,20 @@
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>R12 R13 R31 R41</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>100k 1%</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="I45" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0402 (50 V)</t>
+          <t>저항 100 kΩ 1% 0402 (벅 FB, 전원 감시)</t>
         </is>
       </c>
       <c r="J45" s="19" t="n">
@@ -4491,24 +4491,24 @@
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>PLTT0603Z4021</t>
+          <t>ERA-3AEB4021V</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>Pt1000 기준저항 4.02 kΩ 박막 0603, TCR 5 ppm/K (초기 오차는 교정으로 제거) [LCSC: LCSC 최선 ERA-3AEB4021V C491130 (0.1 %·25 ppm)은 Pt1000 정확도 약 5배 나빠 쓰지 않음]</t>
+          <t>Pt1000 기준저항 4.02 kΩ 0.1 % 25 ppm/K 박막 0603 (결정 #38: JLC 부품 — 이전 PLTT 0.02 %·5 ppm. 초기 오차는 교정, 온도 드리프트는 ADS1220 내부 온도로 보정 검토) [LCSC: 결정 #38: 0.1 %·25 ppm (PLTT 0.02 %·5 ppm 대신)]</t>
         </is>
       </c>
       <c r="J48" s="19" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="L48" s="20">
         <f>D48*J48</f>
@@ -4520,13 +4520,17 @@
       </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O48" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O48" s="16" t="inlineStr">
+        <is>
+          <t>C491130</t>
+        </is>
+      </c>
       <c r="P48" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4564,19 +4568,19 @@
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>CRCW251210R0FKEGHP</t>
+          <t>CRCW251210R0FKEG</t>
         </is>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>CRCW-HP 2512 10 Ω 1% 1.5 W 펄스 내성, AEC-Q200 (출력 직렬) [LCSC: LCSC 일반형 CRCW251210R0FKEG C844885는 서지 에너지 확인 후에만]</t>
+          <t>CRCW 2512 10 Ω 1% 1 W (결정 #38: JLC 부품 — 일반형, 서지 시험 T3로 확인) [LCSC: 결정 #38: 일반형 (HP 대신)]</t>
         </is>
       </c>
       <c r="J49" s="19" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L49" s="20">
         <f>D49*J49</f>
@@ -4588,13 +4592,17 @@
       </c>
       <c r="N49" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
-        </is>
-      </c>
-      <c r="O49" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O49" s="16" t="inlineStr">
+        <is>
+          <t>C844885</t>
+        </is>
+      </c>
       <c r="P49" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4771,17 +4779,17 @@
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>0402WGF4223TCE</t>
+          <t>RC0402FR-07422KL</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>저항 422 kΩ 1% 0402 (VAO 분압 상단) [LCSC: LCSC 번호 미확인 — JLC 화면에서 422 kΩ 1 % 0402 선택]</t>
+          <t>저항 422 kΩ 1% 0402 (VAO 분압 상단)</t>
         </is>
       </c>
       <c r="J52" s="19" t="n">
@@ -4798,12 +4806,16 @@
         <f>D52*K52</f>
         <v/>
       </c>
-      <c r="N52" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="O52" s="16" t="inlineStr"/>
+      <c r="N52" s="16" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O52" s="16" t="inlineStr">
+        <is>
+          <t>C477738</t>
+        </is>
+      </c>
       <c r="P52" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -4816,12 +4828,12 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>R52</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -4829,34 +4841,34 @@
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>22.1k 1%</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>0402WGF2212TCE</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>저항 22.1 kΩ 1% 0402 (VAO 분압 하단) [LCSC: LCSC 번호 미확인 — JLC 화면에서 22.1 kΩ 1 % 0402 선택]</t>
+          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
         </is>
       </c>
       <c r="J53" s="19" t="n">
-        <v>0.001</v>
+        <v>1.5</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>0.003</v>
+        <v>3</v>
       </c>
       <c r="L53" s="20">
         <f>D53*J53</f>
@@ -4866,12 +4878,16 @@
         <f>D53*K53</f>
         <v/>
       </c>
-      <c r="N53" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="O53" s="16" t="inlineStr"/>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O53" s="16" t="inlineStr">
+        <is>
+          <t>C544399</t>
+        </is>
+      </c>
       <c r="P53" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -4889,20 +4905,20 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U2 U15</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>LMR51606YFDBVR</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
@@ -4912,19 +4928,19 @@
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>LMR51606YFDBVR</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
+          <t>벅 4–65 V 0.6 A 1.1 MHz FPWM SOT-23-6 — U2 5 V (결정 #38), U15 VAO 16.1 V (결정 #37)</t>
         </is>
       </c>
       <c r="J54" s="19" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>3</v>
+        <v>1.2</v>
       </c>
       <c r="L54" s="20">
         <f>D54*J54</f>
@@ -4936,12 +4952,12 @@
       </c>
       <c r="N54" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
-          <t>C544399</t>
+          <t>C22439294</t>
         </is>
       </c>
       <c r="P54" s="16" t="inlineStr">
@@ -4961,7 +4977,7 @@
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
@@ -4969,12 +4985,12 @@
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>LMR36006BRNXR</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>Texas_RNX0012A_VQFN-HR-12_2x3mm</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
@@ -4984,19 +5000,19 @@
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>LMR36006BRNXR</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
-          <t>벅 60 V 0.6 A → 5 V, 1 MHz 조정형, VQFN-HR 12핀 2×3 mm [LCSC: LCSC에 없음 (차량용 LMR36006FSCQRNXRQ1 C2869760은 다른 품번·재고 16개)]</t>
+          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
         </is>
       </c>
       <c r="J55" s="19" t="n">
-        <v>1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="L55" s="20">
         <f>D55*J55</f>
@@ -5011,10 +5027,14 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="O55" s="16" t="inlineStr"/>
+      <c r="O55" s="16" t="inlineStr">
+        <is>
+          <t>C2862740</t>
+        </is>
+      </c>
       <c r="P55" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -5024,12 +5044,12 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>MCU</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
@@ -5037,34 +5057,34 @@
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>STM32G0B1CCT3</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>LQFP-48_7x7mm_P0.5mm</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>STM32G0B1CCT3</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
+          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이) [LCSC: LCSC엔 85 °C 등급 CCT6 C5270241만 — 몰딩 내부 온도 때문에 125 °C 등급 유지]</t>
         </is>
       </c>
       <c r="J56" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>0.3</v>
+        <v>2.5</v>
       </c>
       <c r="L56" s="20">
         <f>D56*J56</f>
@@ -5079,14 +5099,10 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="O56" s="16" t="inlineStr">
-        <is>
-          <t>C2862740</t>
-        </is>
-      </c>
+      <c r="O56" s="16" t="inlineStr"/>
       <c r="P56" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>글로벌 소싱</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5112,12 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
@@ -5109,34 +5125,34 @@
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>LQFP-48_7x7mm_P0.5mm</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>ScioSense</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
-          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이) [LCSC: LCSC엔 85 °C 등급 CCT6 C5270241만 — 몰딩 내부 온도 때문에 125 °C 등급 유지]</t>
+          <t>정전용량-디지털 변환기 QFN24</t>
         </is>
       </c>
       <c r="J57" s="19" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>2.5</v>
+        <v>7.1</v>
       </c>
       <c r="L57" s="20">
         <f>D57*J57</f>
@@ -5151,10 +5167,14 @@
           <t>확정</t>
         </is>
       </c>
-      <c r="O57" s="16" t="inlineStr"/>
+      <c r="O57" s="16" t="inlineStr">
+        <is>
+          <t>C2829318</t>
+        </is>
+      </c>
       <c r="P57" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -5169,7 +5189,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
@@ -5177,34 +5197,34 @@
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
+          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>ScioSense</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>정전용량-디지털 변환기 QFN24</t>
+          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
         </is>
       </c>
       <c r="J58" s="19" t="n">
-        <v>6.5</v>
+        <v>1.9</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>7.1</v>
+        <v>3.5</v>
       </c>
       <c r="L58" s="20">
         <f>D58*J58</f>
@@ -5221,7 +5241,7 @@
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
-          <t>C2829318</t>
+          <t>C48263</t>
         </is>
       </c>
       <c r="P58" s="16" t="inlineStr">
@@ -5236,25 +5256,25 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U7 U8</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>DAC8760IPWP</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
@@ -5264,19 +5284,19 @@
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>DAC8760IPWPR</t>
         </is>
       </c>
       <c r="I59" s="17" t="inlineStr">
         <is>
-          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
+          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
         </is>
       </c>
       <c r="J59" s="19" t="n">
-        <v>1.9</v>
+        <v>7.8</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>3.5</v>
+        <v>12.4</v>
       </c>
       <c r="L59" s="20">
         <f>D59*J59</f>
@@ -5293,7 +5313,7 @@
       </c>
       <c r="O59" s="16" t="inlineStr">
         <is>
-          <t>C48263</t>
+          <t>C55047</t>
         </is>
       </c>
       <c r="P59" s="16" t="inlineStr">
@@ -5313,7 +5333,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>U7 U8</t>
+          <t>U9 U10</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
@@ -5321,12 +5341,12 @@
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>DAC8760IPWP</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
+          <t>SOT-23-8</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
@@ -5336,19 +5356,19 @@
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>DAC8760IPWPR</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
+          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
         </is>
       </c>
       <c r="J60" s="19" t="n">
-        <v>7.8</v>
+        <v>1.2</v>
       </c>
       <c r="K60" s="19" t="n">
-        <v>12.4</v>
+        <v>2.5</v>
       </c>
       <c r="L60" s="20">
         <f>D60*J60</f>
@@ -5365,7 +5385,7 @@
       </c>
       <c r="O60" s="16" t="inlineStr">
         <is>
-          <t>C55047</t>
+          <t>C3148140</t>
         </is>
       </c>
       <c r="P60" s="16" t="inlineStr">
@@ -5380,25 +5400,25 @@
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>U9 U10</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>THVD2410DGKR</t>
         </is>
       </c>
       <c r="F61" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-8</t>
+          <t>VSSOP-8_3.0x3.0mm_P0.65mm</t>
         </is>
       </c>
       <c r="G61" s="16" t="inlineStr">
@@ -5408,19 +5428,19 @@
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>THVD2410DGKR</t>
         </is>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
-          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
+          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, VSSOP-8 (SOIC와 같은 핀, 외부 검수 H02 TVS 자리 확보) — THVD2450과 같은 핀 (v0.9)</t>
         </is>
       </c>
       <c r="J61" s="19" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L61" s="20">
         <f>D61*J61</f>
@@ -5437,7 +5457,7 @@
       </c>
       <c r="O61" s="16" t="inlineStr">
         <is>
-          <t>C3148140</t>
+          <t>C1858306</t>
         </is>
       </c>
       <c r="P61" s="16" t="inlineStr">
@@ -5452,25 +5472,25 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U12 U13</t>
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>THVD2410DGKR</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="F62" s="16" t="inlineStr">
         <is>
-          <t>VSSOP-8_3.0x3.0mm_P0.65mm</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
@@ -5480,19 +5500,19 @@
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>THVD2410DGKR</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, VSSOP-8 (SOIC와 같은 핀, 외부 검수 H02 TVS 자리 확보) — THVD2450과 같은 핀 (v0.9)</t>
+          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
         </is>
       </c>
       <c r="J62" s="19" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="L62" s="20">
         <f>D62*J62</f>
@@ -5504,12 +5524,12 @@
       </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O62" s="16" t="inlineStr">
         <is>
-          <t>C1858306</t>
+          <t>C221351</t>
         </is>
       </c>
       <c r="P62" s="16" t="inlineStr">
@@ -5529,20 +5549,20 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>U12 U13</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr">
@@ -5552,19 +5572,19 @@
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
-          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
+          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
         </is>
       </c>
       <c r="J63" s="19" t="n">
-        <v>0.6</v>
+        <v>0.08</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="L63" s="20">
         <f>D63*J63</f>
@@ -5581,7 +5601,7 @@
       </c>
       <c r="O63" s="16" t="inlineStr">
         <is>
-          <t>C221351</t>
+          <t>C91874</t>
         </is>
       </c>
       <c r="P63" s="16" t="inlineStr">
@@ -5596,12 +5616,12 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>기판</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D64" s="18" t="n">
@@ -5609,34 +5629,34 @@
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>HMT500(260313A) (E-301)</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
+          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
         </is>
       </c>
       <c r="J64" s="19" t="n">
-        <v>0.08</v>
+        <v>0.8</v>
       </c>
       <c r="K64" s="19" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="L64" s="20">
         <f>D64*J64</f>
@@ -5646,21 +5666,13 @@
         <f>D64*K64</f>
         <v/>
       </c>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O64" s="16" t="inlineStr">
-        <is>
-          <t>C91874</t>
-        </is>
-      </c>
-      <c r="P64" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+      <c r="N64" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O64" s="16" t="inlineStr"/>
+      <c r="P64" s="16" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="16" t="n">
@@ -5668,12 +5680,12 @@
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>U15</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D65" s="18" t="n">
@@ -5681,34 +5693,34 @@
       </c>
       <c r="E65" s="16" t="inlineStr">
         <is>
-          <t>LMR51606YFDBVR</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>LMR51606YFDBVR</t>
+          <t>MK33-W (300 pF, 품번 확인 필요)</t>
         </is>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
-          <t>벅 4–65 V 0.6 A 1.1 MHz FPWM SOT-23-6 — AO 전원 VAO 16.1 V (결정 #37, IVS320 AO rev 1.0과 같음)</t>
+          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
         </is>
       </c>
       <c r="J65" s="19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="K65" s="19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L65" s="20">
         <f>D65*J65</f>
@@ -5718,21 +5730,13 @@
         <f>D65*K65</f>
         <v/>
       </c>
-      <c r="N65" s="16" t="inlineStr">
-        <is>
-          <t>LCSC</t>
-        </is>
-      </c>
-      <c r="O65" s="16" t="inlineStr">
-        <is>
-          <t>C22439294</t>
-        </is>
-      </c>
-      <c r="P65" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+      <c r="N65" s="21" t="inlineStr">
+        <is>
+          <t>사내 단가</t>
+        </is>
+      </c>
+      <c r="O65" s="16" t="inlineStr"/>
+      <c r="P65" s="16" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="16" t="n">
@@ -5740,12 +5744,12 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>기판</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C66" s="17" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D66" s="18" t="n">
@@ -5763,24 +5767,24 @@
       </c>
       <c r="G66" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>HMT500(260313A) (E-301)</t>
+          <t>MiniSens Pt1000 F0.1</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
+          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
         </is>
       </c>
       <c r="J66" s="19" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="K66" s="19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L66" s="20">
         <f>D66*J66</f>
@@ -5804,12 +5808,12 @@
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>P-204</t>
         </is>
       </c>
       <c r="D67" s="18" t="n">
@@ -5827,24 +5831,24 @@
       </c>
       <c r="G67" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>M Connect</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>MK33-W (300 pF, 품번 확인 필요)</t>
+          <t>TBD (두텍 사용품)</t>
         </is>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
-          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
+          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
         </is>
       </c>
       <c r="J67" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K67" s="19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L67" s="20">
         <f>D67*J67</f>
@@ -5854,9 +5858,9 @@
         <f>D67*K67</f>
         <v/>
       </c>
-      <c r="N67" s="21" t="inlineStr">
-        <is>
-          <t>사내 단가</t>
+      <c r="N67" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
       <c r="O67" s="16" t="inlineStr"/>
@@ -5868,12 +5872,12 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>하네스</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="D68" s="18" t="n">
@@ -5891,24 +5895,24 @@
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>MiniSens Pt1000 F0.1</t>
+          <t>GHR-08V-S</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
+          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
         </is>
       </c>
       <c r="J68" s="19" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="K68" s="19" t="n">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="L68" s="20">
         <f>D68*J68</f>
@@ -5918,13 +5922,21 @@
         <f>D68*K68</f>
         <v/>
       </c>
-      <c r="N68" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O68" s="16" t="inlineStr"/>
-      <c r="P68" s="16" t="inlineStr"/>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O68" s="16" t="inlineStr">
+        <is>
+          <t>C485357</t>
+        </is>
+      </c>
+      <c r="P68" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="n">
@@ -5932,16 +5944,16 @@
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>하네스</t>
         </is>
       </c>
       <c r="C69" s="17" t="inlineStr">
         <is>
-          <t>P-204</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="D69" s="18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5955,24 +5967,24 @@
       </c>
       <c r="G69" s="16" t="inlineStr">
         <is>
-          <t>M Connect</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>TBD (두텍 사용품)</t>
+          <t>SSHL-002T-P0.2</t>
         </is>
       </c>
       <c r="I69" s="17" t="inlineStr">
         <is>
-          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
+          <t>GH 크림프 단자 AWG 30–26</t>
         </is>
       </c>
       <c r="J69" s="19" t="n">
-        <v>2</v>
+        <v>0.03</v>
       </c>
       <c r="K69" s="19" t="n">
-        <v>10</v>
+        <v>0.06</v>
       </c>
       <c r="L69" s="20">
         <f>D69*J69</f>
@@ -5982,13 +5994,21 @@
         <f>D69*K69</f>
         <v/>
       </c>
-      <c r="N69" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="O69" s="16" t="inlineStr"/>
-      <c r="P69" s="16" t="inlineStr"/>
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O69" s="16" t="inlineStr">
+        <is>
+          <t>C189897</t>
+        </is>
+      </c>
+      <c r="P69" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="n">
@@ -6019,24 +6039,24 @@
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>GHR-08V-S</t>
+          <t>PTFE AWG28 전선</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
+          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
         </is>
       </c>
       <c r="J70" s="19" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="K70" s="19" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="L70" s="20">
         <f>D70*J70</f>
@@ -6046,21 +6066,13 @@
         <f>D70*K70</f>
         <v/>
       </c>
-      <c r="N70" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O70" s="16" t="inlineStr">
-        <is>
-          <t>C485357</t>
-        </is>
-      </c>
-      <c r="P70" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N70" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O70" s="16" t="inlineStr"/>
+      <c r="P70" s="16" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="16" t="n">
@@ -6073,11 +6085,11 @@
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="D71" s="18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
@@ -6096,19 +6108,19 @@
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>SSHL-002T-P0.2</t>
+          <t>SHR-04V-S</t>
         </is>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
-          <t>GH 크림프 단자 AWG 30–26</t>
+          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
         </is>
       </c>
       <c r="J71" s="19" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="L71" s="20">
         <f>D71*J71</f>
@@ -6125,7 +6137,7 @@
       </c>
       <c r="O71" s="16" t="inlineStr">
         <is>
-          <t>C189897</t>
+          <t>C385125</t>
         </is>
       </c>
       <c r="P71" s="16" t="inlineStr">
@@ -6145,11 +6157,11 @@
       </c>
       <c r="C72" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -6163,24 +6175,24 @@
       </c>
       <c r="G72" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG28 전선</t>
+          <t>SSH-003T-P0.2-H</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+          <t>SH 크림프 단자 AWG 32–28</t>
         </is>
       </c>
       <c r="J72" s="19" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="K72" s="19" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="L72" s="20">
         <f>D72*J72</f>
@@ -6190,13 +6202,21 @@
         <f>D72*K72</f>
         <v/>
       </c>
-      <c r="N72" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O72" s="16" t="inlineStr"/>
-      <c r="P72" s="16" t="inlineStr"/>
+      <c r="N72" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O72" s="16" t="inlineStr">
+        <is>
+          <t>C263995</t>
+        </is>
+      </c>
+      <c r="P72" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="n">
@@ -6227,24 +6247,24 @@
       </c>
       <c r="G73" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>SHR-04V-S</t>
+          <t>PTFE AWG30 전선</t>
         </is>
       </c>
       <c r="I73" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
+          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
         </is>
       </c>
       <c r="J73" s="19" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L73" s="20">
         <f>D73*J73</f>
@@ -6254,21 +6274,13 @@
         <f>D73*K73</f>
         <v/>
       </c>
-      <c r="N73" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O73" s="16" t="inlineStr">
-        <is>
-          <t>C385125</t>
-        </is>
-      </c>
-      <c r="P73" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N73" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O73" s="16" t="inlineStr"/>
+      <c r="P73" s="16" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="16" t="n">
@@ -6276,47 +6288,47 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>조립</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D74" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E74" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F74" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" s="17" t="inlineStr">
+        <is>
+          <t>SMT 양면 실장</t>
+        </is>
+      </c>
+      <c r="I74" s="17" t="inlineStr">
+        <is>
+          <t>1k 기준 조립비</t>
+        </is>
+      </c>
+      <c r="J74" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K74" s="19" t="n">
         <v>4</v>
-      </c>
-      <c r="E74" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G74" s="16" t="inlineStr">
-        <is>
-          <t>JST</t>
-        </is>
-      </c>
-      <c r="H74" s="17" t="inlineStr">
-        <is>
-          <t>SSH-003T-P0.2-H</t>
-        </is>
-      </c>
-      <c r="I74" s="17" t="inlineStr">
-        <is>
-          <t>SH 크림프 단자 AWG 32–28</t>
-        </is>
-      </c>
-      <c r="J74" s="19" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K74" s="19" t="n">
-        <v>0.06</v>
       </c>
       <c r="L74" s="20">
         <f>D74*J74</f>
@@ -6326,162 +6338,26 @@
         <f>D74*K74</f>
         <v/>
       </c>
-      <c r="N74" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O74" s="16" t="inlineStr">
-        <is>
-          <t>C263995</t>
-        </is>
-      </c>
-      <c r="P74" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N74" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O74" s="16" t="inlineStr"/>
+      <c r="P74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="16" t="inlineStr">
-        <is>
-          <t>하네스</t>
-        </is>
-      </c>
-      <c r="C75" s="17" t="inlineStr">
-        <is>
-          <t>W-1</t>
-        </is>
-      </c>
-      <c r="D75" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G75" s="16" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="H75" s="17" t="inlineStr">
-        <is>
-          <t>PTFE AWG30 전선</t>
-        </is>
-      </c>
-      <c r="I75" s="17" t="inlineStr">
-        <is>
-          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
-        </is>
-      </c>
-      <c r="J75" s="19" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K75" s="19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L75" s="20">
-        <f>D75*J75</f>
-        <v/>
-      </c>
-      <c r="M75" s="20">
-        <f>D75*K75</f>
-        <v/>
-      </c>
-      <c r="N75" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O75" s="16" t="inlineStr"/>
-      <c r="P75" s="16" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="16" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>조립</t>
-        </is>
-      </c>
-      <c r="C76" s="17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D76" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F76" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" s="16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" s="17" t="inlineStr">
-        <is>
-          <t>SMT 양면 실장</t>
-        </is>
-      </c>
-      <c r="I76" s="17" t="inlineStr">
-        <is>
-          <t>1k 기준 조립비</t>
-        </is>
-      </c>
-      <c r="J76" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="K76" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="L76" s="20">
-        <f>D76*J76</f>
-        <v/>
-      </c>
-      <c r="M76" s="20">
-        <f>D76*K76</f>
-        <v/>
-      </c>
-      <c r="N76" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O76" s="16" t="inlineStr"/>
-      <c r="P76" s="16" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="I77" s="3" t="inlineStr">
+      <c r="I75" s="3" t="inlineStr">
         <is>
           <t>합계 (1대분)</t>
         </is>
       </c>
-      <c r="L77" s="23">
-        <f>SUM(L2:L76)</f>
-        <v/>
-      </c>
-      <c r="M77" s="23">
-        <f>SUM(M2:M76)</f>
+      <c r="L75" s="23">
+        <f>SUM(L2:L74)</f>
+        <v/>
+      </c>
+      <c r="M75" s="23">
+        <f>SUM(M2:M74)</f>
         <v/>
       </c>
     </row>

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -5057,7 +5057,7 @@
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>STM32G0B1CCT6</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT3</t>
+          <t>STM32G0B1CCT6</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~125 °C (사내 DP2000 G0B1CCT6 동일 다이) [LCSC: LCSC엔 85 °C 등급 CCT6 C5270241만 — 몰딩 내부 온도 때문에 125 °C 등급 유지]</t>
+          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~85 °C — 사내 DP2000과 같은 품번. 샘플 단계 JLC 부품 (결정 #39), 양산은 전자부 온도 사양 확정 후 CCT3(125 °C) 검토 [LCSC: 샘플 단계 (결정 #39). 85 °C 등급 — 양산 전 온도 사양 확인]</t>
         </is>
       </c>
       <c r="J56" s="19" t="n">
@@ -5096,13 +5096,17 @@
       </c>
       <c r="N56" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O56" s="16" t="inlineStr"/>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O56" s="16" t="inlineStr">
+        <is>
+          <t>C5270241</t>
+        </is>
+      </c>
       <c r="P56" s="16" t="inlineStr">
         <is>
-          <t>글로벌 소싱</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -262,8 +262,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P74" headerRowCount="1">
-  <autoFilter ref="A1:P74"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PartsList" displayName="PartsList" ref="A1:P75" headerRowCount="1">
+  <autoFilter ref="A1:P75"/>
   <tableColumns count="16">
     <tableColumn id="1" name="No"/>
     <tableColumn id="2" name="분류"/>
@@ -654,15 +654,15 @@
         </is>
       </c>
       <c r="B7" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A7)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A7)</f>
         <v/>
       </c>
       <c r="C7" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A7)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A7)</f>
         <v/>
       </c>
       <c r="D7" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A7)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A7)</f>
         <v/>
       </c>
       <c r="E7" s="10">
@@ -681,15 +681,15 @@
         </is>
       </c>
       <c r="B8" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A8)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A8)</f>
         <v/>
       </c>
       <c r="C8" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A8)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A8)</f>
         <v/>
       </c>
       <c r="D8" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A8)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A8)</f>
         <v/>
       </c>
       <c r="E8" s="10">
@@ -708,15 +708,15 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A9)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A9)</f>
         <v/>
       </c>
       <c r="C9" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A9)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A9)</f>
         <v/>
       </c>
       <c r="D9" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A9)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A9)</f>
         <v/>
       </c>
       <c r="E9" s="10">
@@ -735,15 +735,15 @@
         </is>
       </c>
       <c r="B10" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A10)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A10)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A10)</f>
         <v/>
       </c>
       <c r="D10" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A10)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A10)</f>
         <v/>
       </c>
       <c r="E10" s="10">
@@ -762,15 +762,15 @@
         </is>
       </c>
       <c r="B11" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A11)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A11)</f>
         <v/>
       </c>
       <c r="C11" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A11)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A11)</f>
         <v/>
       </c>
       <c r="D11" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A11)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A11)</f>
         <v/>
       </c>
       <c r="E11" s="10">
@@ -789,15 +789,15 @@
         </is>
       </c>
       <c r="B12" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A12)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A12)</f>
         <v/>
       </c>
       <c r="C12" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A12)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A12)</f>
         <v/>
       </c>
       <c r="D12" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A12)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A12)</f>
         <v/>
       </c>
       <c r="E12" s="10">
@@ -816,15 +816,15 @@
         </is>
       </c>
       <c r="B13" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A13)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A13)</f>
         <v/>
       </c>
       <c r="C13" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A13)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A13)</f>
         <v/>
       </c>
       <c r="D13" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A13)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A13)</f>
         <v/>
       </c>
       <c r="E13" s="10">
@@ -843,15 +843,15 @@
         </is>
       </c>
       <c r="B14" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A14)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A14)</f>
         <v/>
       </c>
       <c r="C14" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A14)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A14)</f>
         <v/>
       </c>
       <c r="D14" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A14)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A14)</f>
         <v/>
       </c>
       <c r="E14" s="10">
@@ -870,15 +870,15 @@
         </is>
       </c>
       <c r="B15" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A15)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A15)</f>
         <v/>
       </c>
       <c r="C15" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A15)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A15)</f>
         <v/>
       </c>
       <c r="D15" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A15)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A15)</f>
         <v/>
       </c>
       <c r="E15" s="10">
@@ -897,15 +897,15 @@
         </is>
       </c>
       <c r="B16" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A16)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A16)</f>
         <v/>
       </c>
       <c r="C16" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A16)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A16)</f>
         <v/>
       </c>
       <c r="D16" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A16)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A16)</f>
         <v/>
       </c>
       <c r="E16" s="10">
@@ -924,15 +924,15 @@
         </is>
       </c>
       <c r="B17" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A17)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A17)</f>
         <v/>
       </c>
       <c r="C17" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A17)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A17)</f>
         <v/>
       </c>
       <c r="D17" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A17)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A17)</f>
         <v/>
       </c>
       <c r="E17" s="10">
@@ -951,15 +951,15 @@
         </is>
       </c>
       <c r="B18" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A18)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A18)</f>
         <v/>
       </c>
       <c r="C18" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A18)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A18)</f>
         <v/>
       </c>
       <c r="D18" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A18)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A18)</f>
         <v/>
       </c>
       <c r="E18" s="10">
@@ -978,15 +978,15 @@
         </is>
       </c>
       <c r="B19" s="8">
-        <f>COUNTIF('부품리스트'!$B$2:$B$74,A19)</f>
+        <f>COUNTIF('부품리스트'!$B$2:$B$75,A19)</f>
         <v/>
       </c>
       <c r="C19" s="9">
-        <f>SUMIFS('부품리스트'!$L$2:$L$74,'부품리스트'!$B$2:$B$74,A19)</f>
+        <f>SUMIFS('부품리스트'!$L$2:$L$75,'부품리스트'!$B$2:$B$75,A19)</f>
         <v/>
       </c>
       <c r="D19" s="9">
-        <f>SUMIFS('부품리스트'!$M$2:$M$74,'부품리스트'!$B$2:$B$74,A19)</f>
+        <f>SUMIFS('부품리스트'!$M$2:$M$75,'부품리스트'!$B$2:$B$75,A19)</f>
         <v/>
       </c>
       <c r="E19" s="10">
@@ -1071,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P75"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2693,11 +2693,11 @@
       </c>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>D2 D30 D40 D60 D61</t>
+          <t>D2 D60 D61</t>
         </is>
       </c>
       <c r="D23" s="18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="I23" s="17" t="inlineStr">
         <is>
-          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: 재고 적음 (검색 시 약 88개) — v0.9 수량 5개 (D2, D30, D40, D60, D61)]</t>
+          <t>평탄 클램프 TVS 33 V 양방향, 40 V @ 27 A, SON-8 3×3 (아날로그 출력, TPS2661 데이터시트 권장) [LCSC: D2/D60/D61 3개 유지; 재고 확인 필요]</t>
         </is>
       </c>
       <c r="J23" s="19" t="n">
@@ -2832,12 +2832,12 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C25" s="17" t="inlineStr">
         <is>
-          <t>D41 D51</t>
+          <t>D30 D40</t>
         </is>
       </c>
       <c r="D25" s="18" t="n">
@@ -2845,34 +2845,34 @@
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
-          <t>BAS70-04</t>
+          <t>TVS1401DRBR</t>
         </is>
       </c>
       <c r="F25" s="16" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>Texas_DRB0008A_PadFloat</t>
         </is>
       </c>
       <c r="G25" s="16" t="inlineStr">
         <is>
-          <t>Nexperia</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H25" s="17" t="inlineStr">
         <is>
-          <t>BAS70-04,215</t>
+          <t>TVS1401DRBR</t>
         </is>
       </c>
       <c r="I25" s="17" t="inlineStr">
         <is>
-          <t>쇼트키 2개 직렬 70 V SOT-23 — DAC 출력 클램프 (1 A, 2 K, 3 공통)</t>
+          <t>평탄 클램프 TVS 14 V 양방향, 최대 23.55 V @ 30 A/125 C, SON-8 3×3 (AO 전용, 지속 ±28/30 V 오결선 보장 제외) [LCSC: D30/D40; LCSC 품번 확인, JLC 등급/재고 확인 필요]</t>
         </is>
       </c>
       <c r="J25" s="19" t="n">
-        <v>0.02</v>
+        <v>0.35</v>
       </c>
       <c r="K25" s="19" t="n">
-        <v>0.05</v>
+        <v>0.6</v>
       </c>
       <c r="L25" s="20">
         <f>D25*J25</f>
@@ -2884,19 +2884,15 @@
       </c>
       <c r="N25" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>C389351</t>
-        </is>
-      </c>
-      <c r="P25" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+          <t>C1849891</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n">
@@ -2904,47 +2900,47 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>D41 D51</t>
         </is>
       </c>
       <c r="D26" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>600R@100MHz</t>
+          <t>BAS70-04</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
         <is>
-          <t>L_0603_1608Metric</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="G26" s="16" t="inlineStr">
         <is>
-          <t>Murata</t>
+          <t>Nexperia</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>BLM18KG601SN1D</t>
+          <t>BAS70-04,215</t>
         </is>
       </c>
       <c r="I26" s="17" t="inlineStr">
         <is>
-          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
+          <t>쇼트키 2개 직렬 70 V SOT-23 — DAC 출력 클램프 (1 A, 2 K, 3 공통)</t>
         </is>
       </c>
       <c r="J26" s="19" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="K26" s="19" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="L26" s="20">
         <f>D26*J26</f>
@@ -2956,12 +2952,12 @@
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O26" s="16" t="inlineStr">
         <is>
-          <t>C85833</t>
+          <t>C389351</t>
         </is>
       </c>
       <c r="P26" s="16" t="inlineStr">
@@ -2976,12 +2972,12 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C27" s="17" t="inlineStr">
         <is>
-          <t>GDT1</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="D27" s="18" t="n">
@@ -2989,34 +2985,34 @@
       </c>
       <c r="E27" s="16" t="inlineStr">
         <is>
-          <t>2035-25-SM</t>
+          <t>600R@100MHz</t>
         </is>
       </c>
       <c r="F27" s="16" t="inlineStr">
         <is>
-          <t>GDT_Bourns_2035-xx-SM</t>
+          <t>L_0603_1608Metric</t>
         </is>
       </c>
       <c r="G27" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>Murata</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
         <is>
-          <t>2035-25-SM-RPLF</t>
+          <t>BLM18KG601SN1D</t>
         </is>
       </c>
       <c r="I27" s="17" t="inlineStr">
         <is>
-          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
+          <t>페라이트 비드 600 Ω@100 MHz 0603 [LCSC: Basic 비드 C1002는 200 mA라 쓰지 않음]</t>
         </is>
       </c>
       <c r="J27" s="19" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="K27" s="19" t="n">
-        <v>1</v>
+        <v>0.03</v>
       </c>
       <c r="L27" s="20">
         <f>D27*J27</f>
@@ -3028,12 +3024,12 @@
       </c>
       <c r="N27" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O27" s="16" t="inlineStr">
         <is>
-          <t>C3660127</t>
+          <t>C85833</t>
         </is>
       </c>
       <c r="P27" s="16" t="inlineStr">
@@ -3048,12 +3044,12 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>GDT1</t>
         </is>
       </c>
       <c r="D28" s="18" t="n">
@@ -3061,34 +3057,34 @@
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB</t>
+          <t>2035-25-SM</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
         <is>
-          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
+          <t>GDT_Bourns_2035-xx-SM</t>
         </is>
       </c>
       <c r="G28" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H28" s="17" t="inlineStr">
         <is>
-          <t>SM08B-GHS-TB(LF)(SN)</t>
+          <t>2035-25-SM-RPLF</t>
         </is>
       </c>
       <c r="I28" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
+          <t>2전극 SMD GDT 250 V, Ø5 × 4.4 mm (회로 GND–외함. LCSC — 230 V형은 LCSC에 없음)</t>
         </is>
       </c>
       <c r="J28" s="19" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="K28" s="19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="L28" s="20">
         <f>D28*J28</f>
@@ -3100,12 +3096,12 @@
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>C265111</t>
+          <t>C3660127</t>
         </is>
       </c>
       <c r="P28" s="16" t="inlineStr">
@@ -3120,12 +3116,12 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>생산</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C29" s="17" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="D29" s="18" t="n">
@@ -3133,34 +3129,34 @@
       </c>
       <c r="E29" s="16" t="inlineStr">
         <is>
-          <t>TC2030-IDC-NL</t>
+          <t>SM08B-GHS-TB</t>
         </is>
       </c>
       <c r="F29" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
+          <t>JST_GH_SM08B-GHS-TB_1x08-1MP_P1.25mm_Horizontal</t>
         </is>
       </c>
       <c r="G29" s="16" t="inlineStr">
         <is>
-          <t>Tag-Connect</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H29" s="17" t="inlineStr">
         <is>
-          <t>(PCB 패드만)</t>
+          <t>SM08B-GHS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I29" s="17" t="inlineStr">
         <is>
-          <t>SWD 기록용 패드 — 부품 실장 없음</t>
+          <t>GH 1.25 mm 8핀 헤더, 옆 삽입(직각) SMD (M12 하네스 W-2, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J29" s="19" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="K29" s="19" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L29" s="20">
         <f>D29*J29</f>
@@ -3172,11 +3168,19 @@
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O29" s="16" t="inlineStr"/>
-      <c r="P29" s="16" t="inlineStr"/>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O29" s="16" t="inlineStr">
+        <is>
+          <t>C265111</t>
+        </is>
+      </c>
+      <c r="P29" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="n">
@@ -3184,12 +3188,12 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>생산</t>
         </is>
       </c>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="D30" s="18" t="n">
@@ -3197,34 +3201,34 @@
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB</t>
+          <t>TC2030-IDC-NL</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
         <is>
-          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
+          <t>Tag-Connect_TC2030-IDC-NL_2x03_P1.27mm_Vertical</t>
         </is>
       </c>
       <c r="G30" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Tag-Connect</t>
         </is>
       </c>
       <c r="H30" s="17" t="inlineStr">
         <is>
-          <t>SM04B-SRSS-TB(LF)(SN)</t>
+          <t>(PCB 패드만)</t>
         </is>
       </c>
       <c r="I30" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
+          <t>SWD 기록용 패드 — 부품 실장 없음</t>
         </is>
       </c>
       <c r="J30" s="19" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="K30" s="19" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L30" s="20">
         <f>D30*J30</f>
@@ -3236,19 +3240,11 @@
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O30" s="16" t="inlineStr">
-        <is>
-          <t>C160404</t>
-        </is>
-      </c>
-      <c r="P30" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O30" s="16" t="inlineStr"/>
+      <c r="P30" s="16" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="n">
@@ -3261,7 +3257,7 @@
       </c>
       <c r="C31" s="17" t="inlineStr">
         <is>
-          <t>J5</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="D31" s="18" t="n">
@@ -3269,34 +3265,34 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>CHASSIS wire</t>
+          <t>SM04B-SRSS-TB</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
         <is>
-          <t>SolderWire_Chassis_D0.6mm</t>
+          <t>JST_SH_SM04B-SRSS-TB_1x04-1MP_P1.00mm_Horizontal</t>
         </is>
       </c>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H31" s="17" t="inlineStr">
         <is>
-          <t>PCB 납땜 구멍 (부품 없음)</t>
+          <t>SM04B-SRSS-TB(LF)(SN)</t>
         </is>
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
+          <t>SH 1.0 mm 4핀 헤더, 옆 삽입(직각) SMD (센서 하네스 W-1, 정격 −25~+85 °C)</t>
         </is>
       </c>
       <c r="J31" s="19" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K31" s="19" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="L31" s="20">
         <f>D31*J31</f>
@@ -3308,11 +3304,19 @@
       </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
-        </is>
-      </c>
-      <c r="O31" s="16" t="inlineStr"/>
-      <c r="P31" s="16" t="inlineStr"/>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O31" s="16" t="inlineStr">
+        <is>
+          <t>C160404</t>
+        </is>
+      </c>
+      <c r="P31" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n">
@@ -3320,12 +3324,12 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>L1</t>
+          <t>J5</t>
         </is>
       </c>
       <c r="D32" s="18" t="n">
@@ -3333,34 +3337,34 @@
       </c>
       <c r="E32" s="16" t="inlineStr">
         <is>
-          <t>CMC 1mH 0.8A</t>
+          <t>CHASSIS wire</t>
         </is>
       </c>
       <c r="F32" s="16" t="inlineStr">
         <is>
-          <t>L_CommonMode_Wuerth_WE-SL2</t>
+          <t>SolderWire_Chassis_D0.6mm</t>
         </is>
       </c>
       <c r="G32" s="16" t="inlineStr">
         <is>
-          <t>Bourns</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H32" s="17" t="inlineStr">
         <is>
-          <t>SRF0905-102Y</t>
+          <t>PCB 납땜 구멍 (부품 없음)</t>
         </is>
       </c>
       <c r="I32" s="17" t="inlineStr">
         <is>
-          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
+          <t>샤시 선 AWG 28 PTFE 약 25 mm + M2 링 단자 → 홀더 축 나사. 선·단자는 기구 부품표(JLCMC)</t>
         </is>
       </c>
       <c r="J32" s="19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K32" s="19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="L32" s="20">
         <f>D32*J32</f>
@@ -3370,21 +3374,13 @@
         <f>D32*K32</f>
         <v/>
       </c>
-      <c r="N32" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="O32" s="16" t="inlineStr">
-        <is>
-          <t>C2651138</t>
-        </is>
-      </c>
-      <c r="P32" s="16" t="inlineStr">
-        <is>
-          <t>Extended</t>
-        </is>
-      </c>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>확정</t>
+        </is>
+      </c>
+      <c r="O32" s="16" t="inlineStr"/>
+      <c r="P32" s="16" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="n">
@@ -3392,12 +3388,12 @@
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
         <is>
-          <t>L2</t>
+          <t>L1</t>
         </is>
       </c>
       <c r="D33" s="18" t="n">
@@ -3405,34 +3401,34 @@
       </c>
       <c r="E33" s="16" t="inlineStr">
         <is>
-          <t>10uH</t>
+          <t>CMC 1mH 0.8A</t>
         </is>
       </c>
       <c r="F33" s="16" t="inlineStr">
         <is>
-          <t>L_Taiyo-Yuden_NR-40xx</t>
+          <t>L_CommonMode_Wuerth_WE-SL2</t>
         </is>
       </c>
       <c r="G33" s="16" t="inlineStr">
         <is>
-          <t>SXN</t>
+          <t>Bourns</t>
         </is>
       </c>
       <c r="H33" s="17" t="inlineStr">
         <is>
-          <t>SMNR4020-10UH</t>
+          <t>SRF0905-102Y</t>
         </is>
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 10 µH ±20 % 0.62 A 0.95 Ω 4 × 4 × 2 mm (NR-40xx 랜드) — 5 V 벅 (부하 약 60 mA) [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
+          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
       <c r="K33" s="19" t="n">
-        <v>0.12</v>
+        <v>1.2</v>
       </c>
       <c r="L33" s="20">
         <f>D33*J33</f>
@@ -3449,7 +3445,7 @@
       </c>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>C135263</t>
+          <t>C2651138</t>
         </is>
       </c>
       <c r="P33" s="16" t="inlineStr">
@@ -3464,12 +3460,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>L3</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="D34" s="18" t="n">
@@ -3477,7 +3473,7 @@
       </c>
       <c r="E34" s="16" t="inlineStr">
         <is>
-          <t>22uH</t>
+          <t>10uH</t>
         </is>
       </c>
       <c r="F34" s="16" t="inlineStr">
@@ -3487,24 +3483,24 @@
       </c>
       <c r="G34" s="16" t="inlineStr">
         <is>
-          <t>(LCSC)</t>
+          <t>SXN</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
         <is>
-          <t>SMNR4020-22UH</t>
+          <t>SMNR4020-10UH</t>
         </is>
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 22 µH ±20 % 1.05 A 455 mΩ 4 × 4 × 2 mm (NR-40xx 랜드) — VAO 벅 [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
+          <t>파워 인덕터 10 µH ±20 % 0.62 A 0.95 Ω 4 × 4 × 2 mm (NR-40xx 랜드) — 5 V 벅 (부하 약 60 mA) [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
         <v>0.05</v>
       </c>
       <c r="K34" s="19" t="n">
-        <v>0.15</v>
+        <v>0.12</v>
       </c>
       <c r="L34" s="20">
         <f>D34*J34</f>
@@ -3521,7 +3517,7 @@
       </c>
       <c r="O34" s="16" t="inlineStr">
         <is>
-          <t>C135264</t>
+          <t>C135263</t>
         </is>
       </c>
       <c r="P34" s="16" t="inlineStr">
@@ -3536,12 +3532,12 @@
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C35" s="17" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="D35" s="18" t="n">
@@ -3549,27 +3545,27 @@
       </c>
       <c r="E35" s="16" t="inlineStr">
         <is>
-          <t>4.7R 1W pulse</t>
+          <t>22uH</t>
         </is>
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>L_Taiyo-Yuden_NR-40xx</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>(LCSC)</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
         <is>
-          <t>CRCW25124R70FKEG</t>
+          <t>SMNR4020-22UH</t>
         </is>
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>CRCW 2512 4.7 Ω 1% 1 W (결정 #38: JLC 부품 — 펄스 내성 HP형 대신 일반형, 서지 시험 T1로 확인) [LCSC: 결정 #38: 일반형 (HP 대신)]</t>
+          <t>파워 인덕터 22 µH ±20 % 1.05 A 455 mΩ 4 × 4 × 2 mm (NR-40xx 랜드) — VAO 벅 [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">
@@ -3586,14 +3582,14 @@
         <f>D35*K35</f>
         <v/>
       </c>
-      <c r="N35" s="16" t="inlineStr">
-        <is>
-          <t>LCSC</t>
+      <c r="N35" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
         </is>
       </c>
       <c r="O35" s="16" t="inlineStr">
         <is>
-          <t>C242563</t>
+          <t>C135264</t>
         </is>
       </c>
       <c r="P35" s="16" t="inlineStr">
@@ -3613,7 +3609,7 @@
       </c>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D36" s="18" t="n">
@@ -3621,34 +3617,34 @@
       </c>
       <c r="E36" s="16" t="inlineStr">
         <is>
-          <t>1M HV</t>
+          <t>4.7R 1W pulse</t>
         </is>
       </c>
       <c r="F36" s="16" t="inlineStr">
         <is>
-          <t>R_1206_3216Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G36" s="16" t="inlineStr">
         <is>
-          <t>ROHM</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H36" s="17" t="inlineStr">
         <is>
-          <t>KTR18EZPF1004</t>
+          <t>CRCW25124R70FKEG</t>
         </is>
       </c>
       <c r="I36" s="17" t="inlineStr">
         <is>
-          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
+          <t>CRCW 2512 4.7 Ω 1% 1 W (결정 #38: JLC 부품 — 펄스 내성 HP형 대신 일반형, 서지 시험 T1로 확인) [LCSC: 결정 #38: 일반형 (HP 대신)]</t>
         </is>
       </c>
       <c r="J36" s="19" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="K36" s="19" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="L36" s="20">
         <f>D36*J36</f>
@@ -3665,7 +3661,7 @@
       </c>
       <c r="O36" s="16" t="inlineStr">
         <is>
-          <t>C253347</t>
+          <t>C242563</t>
         </is>
       </c>
       <c r="P36" s="16" t="inlineStr">
@@ -3680,12 +3676,12 @@
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C37" s="17" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D37" s="18" t="n">
@@ -3693,34 +3689,34 @@
       </c>
       <c r="E37" s="16" t="inlineStr">
         <is>
-          <t>866k 1%</t>
+          <t>1M HV</t>
         </is>
       </c>
       <c r="F37" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_1206_3216Metric</t>
         </is>
       </c>
       <c r="G37" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>ROHM</t>
         </is>
       </c>
       <c r="H37" s="17" t="inlineStr">
         <is>
-          <t>RCS0603866KFKEA</t>
+          <t>KTR18EZPF1004</t>
         </is>
       </c>
       <c r="I37" s="17" t="inlineStr">
         <is>
-          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
+          <t>서지용 칩 저항 1 MΩ 1% 1206, 최고 사용 전압 500 V (GDT 방전 전 임펄스. LCSC — 1 kV 1206은 LCSC에 없음) [LCSC: 500 V (1 kV 1206은 LCSC에 없음)]</t>
         </is>
       </c>
       <c r="J37" s="19" t="n">
-        <v>0.002</v>
+        <v>0.02</v>
       </c>
       <c r="K37" s="19" t="n">
-        <v>0.005</v>
+        <v>0.06</v>
       </c>
       <c r="L37" s="20">
         <f>D37*J37</f>
@@ -3732,12 +3728,12 @@
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>C3954581</t>
+          <t>C253347</t>
         </is>
       </c>
       <c r="P37" s="16" t="inlineStr">
@@ -3757,7 +3753,7 @@
       </c>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="D38" s="18" t="n">
@@ -3765,7 +3761,7 @@
       </c>
       <c r="E38" s="16" t="inlineStr">
         <is>
-          <t>97.6k 1%</t>
+          <t>866k 1%</t>
         </is>
       </c>
       <c r="F38" s="16" t="inlineStr">
@@ -3775,17 +3771,17 @@
       </c>
       <c r="G38" s="16" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H38" s="17" t="inlineStr">
         <is>
-          <t>ERA-3AEB9762V</t>
+          <t>RCS0603866KFKEA</t>
         </is>
       </c>
       <c r="I38" s="17" t="inlineStr">
         <is>
-          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
+          <t>저항 866 kΩ 1% 0603 (UVLO)</t>
         </is>
       </c>
       <c r="J38" s="19" t="n">
@@ -3809,7 +3805,7 @@
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>C2074558</t>
+          <t>C3954581</t>
         </is>
       </c>
       <c r="P38" s="16" t="inlineStr">
@@ -3829,7 +3825,7 @@
       </c>
       <c r="C39" s="17" t="inlineStr">
         <is>
-          <t>R5</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="D39" s="18" t="n">
@@ -3837,7 +3833,7 @@
       </c>
       <c r="E39" s="16" t="inlineStr">
         <is>
-          <t>36.5k 1%</t>
+          <t>97.6k 1%</t>
         </is>
       </c>
       <c r="F39" s="16" t="inlineStr">
@@ -3847,17 +3843,17 @@
       </c>
       <c r="G39" s="16" t="inlineStr">
         <is>
-          <t>CAL-CHIP</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H39" s="17" t="inlineStr">
         <is>
-          <t>RM06F3652CT</t>
+          <t>ERA-3AEB9762V</t>
         </is>
       </c>
       <c r="I39" s="17" t="inlineStr">
         <is>
-          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
+          <t>저항 97.6 kΩ 1% 0603 (UVLO/OVP) [LCSC: 0.1 % 25 ppm (1 %형 LCSC에 없음, 더 좋음)]</t>
         </is>
       </c>
       <c r="J39" s="19" t="n">
@@ -3881,7 +3877,7 @@
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>C4027587</t>
+          <t>C2074558</t>
         </is>
       </c>
       <c r="P39" s="16" t="inlineStr">
@@ -3901,7 +3897,7 @@
       </c>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>R6</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="D40" s="18" t="n">
@@ -3909,7 +3905,7 @@
       </c>
       <c r="E40" s="16" t="inlineStr">
         <is>
-          <t>80.6k 1%</t>
+          <t>36.5k 1%</t>
         </is>
       </c>
       <c r="F40" s="16" t="inlineStr">
@@ -3919,17 +3915,17 @@
       </c>
       <c r="G40" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>CAL-CHIP</t>
         </is>
       </c>
       <c r="H40" s="17" t="inlineStr">
         <is>
-          <t>0603WAF8062T5E</t>
+          <t>RM06F3652CT</t>
         </is>
       </c>
       <c r="I40" s="17" t="inlineStr">
         <is>
-          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
+          <t>저항 36.5 kΩ 1% 0603 (OVP 32.6 V, 복귀 30.1 V — v0.9)</t>
         </is>
       </c>
       <c r="J40" s="19" t="n">
@@ -3953,7 +3949,7 @@
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>C23249</t>
+          <t>C4027587</t>
         </is>
       </c>
       <c r="P40" s="16" t="inlineStr">
@@ -3973,7 +3969,7 @@
       </c>
       <c r="C41" s="17" t="inlineStr">
         <is>
-          <t>R8</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="D41" s="18" t="n">
@@ -3981,34 +3977,34 @@
       </c>
       <c r="E41" s="16" t="inlineStr">
         <is>
-          <t>118k 1%</t>
+          <t>80.6k 1%</t>
         </is>
       </c>
       <c r="F41" s="16" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H41" s="17" t="inlineStr">
         <is>
-          <t>AC0402FR-07118KL</t>
+          <t>0603WAF8062T5E</t>
         </is>
       </c>
       <c r="I41" s="17" t="inlineStr">
         <is>
-          <t>저항 118 kΩ 1% 0402 (5 V 벅 FB 상단)</t>
+          <t>저항 80.6 kΩ 1% 0603 (TPS2660 전류제한 149 mA = 12/R)</t>
         </is>
       </c>
       <c r="J41" s="19" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="K41" s="19" t="n">
-        <v>0.003</v>
+        <v>0.005</v>
       </c>
       <c r="L41" s="20">
         <f>D41*J41</f>
@@ -4020,12 +4016,12 @@
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>C144804</t>
+          <t>C23249</t>
         </is>
       </c>
       <c r="P41" s="16" t="inlineStr">
@@ -4040,20 +4036,20 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>R9 R52</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="D42" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="16" t="inlineStr">
         <is>
-          <t>22.1k 1%</t>
+          <t>118k 1%</t>
         </is>
       </c>
       <c r="F42" s="16" t="inlineStr">
@@ -4063,17 +4059,17 @@
       </c>
       <c r="G42" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H42" s="17" t="inlineStr">
         <is>
-          <t>0402WGF2212TCE</t>
+          <t>AC0402FR-07118KL</t>
         </is>
       </c>
       <c r="I42" s="17" t="inlineStr">
         <is>
-          <t>저항 22.1 kΩ 1% 0402 (VAO 분압 하단) [LCSC: LCSC 번호 미확인 — JLC 화면에서 22.1 kΩ 1 % 0402 선택]</t>
+          <t>저항 118 kΩ 1% 0402 (5 V 벅 FB 상단)</t>
         </is>
       </c>
       <c r="J42" s="19" t="n">
@@ -4090,12 +4086,16 @@
         <f>D42*K42</f>
         <v/>
       </c>
-      <c r="N42" s="21" t="inlineStr">
-        <is>
-          <t>확인 필요</t>
-        </is>
-      </c>
-      <c r="O42" s="16" t="inlineStr"/>
+      <c r="N42" s="16" t="inlineStr">
+        <is>
+          <t>LCSC</t>
+        </is>
+      </c>
+      <c r="O42" s="16" t="inlineStr">
+        <is>
+          <t>C144804</t>
+        </is>
+      </c>
       <c r="P42" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -4108,20 +4108,20 @@
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C43" s="17" t="inlineStr">
         <is>
-          <t>R10 R11 R33 R60</t>
+          <t>R9 R52</t>
         </is>
       </c>
       <c r="D43" s="18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E43" s="16" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>22.1k 1%</t>
         </is>
       </c>
       <c r="F43" s="16" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="H43" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1002TCE</t>
+          <t>0402WGF2212TCE</t>
         </is>
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>저항 10 kΩ 1% 0402 (50 V)</t>
+          <t>저항 22.1 kΩ 1% 0402 (VAO 분압 하단) [LCSC: LCSC 번호 미확인 — JLC 화면에서 22.1 kΩ 1 % 0402 선택]</t>
         </is>
       </c>
       <c r="J43" s="19" t="n">
@@ -4158,19 +4158,15 @@
         <f>D43*K43</f>
         <v/>
       </c>
-      <c r="N43" s="16" t="inlineStr">
-        <is>
-          <t>LCSC</t>
-        </is>
-      </c>
-      <c r="O43" s="16" t="inlineStr">
-        <is>
-          <t>C25744</t>
-        </is>
-      </c>
+      <c r="N43" s="21" t="inlineStr">
+        <is>
+          <t>확인 필요</t>
+        </is>
+      </c>
+      <c r="O43" s="16" t="inlineStr"/>
       <c r="P43" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4185,7 +4181,7 @@
       </c>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>R12 R13 R31 R41</t>
+          <t>R10 R11 R33 R60</t>
         </is>
       </c>
       <c r="D44" s="18" t="n">
@@ -4193,7 +4189,7 @@
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>100k</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
@@ -4208,12 +4204,12 @@
       </c>
       <c r="H44" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1003TCE</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
       <c r="I44" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0402 (50 V)</t>
+          <t>저항 10 kΩ 1% 0402 (50 V)</t>
         </is>
       </c>
       <c r="J44" s="19" t="n">
@@ -4237,7 +4233,7 @@
       </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
-          <t>C25741</t>
+          <t>C25744</t>
         </is>
       </c>
       <c r="P44" s="16" t="inlineStr">
@@ -4252,20 +4248,20 @@
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C45" s="17" t="inlineStr">
         <is>
-          <t>R14</t>
+          <t>R12 R13 R31 R41</t>
         </is>
       </c>
       <c r="D45" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E45" s="16" t="inlineStr">
         <is>
-          <t>100k 1%</t>
+          <t>100k</t>
         </is>
       </c>
       <c r="F45" s="16" t="inlineStr">
@@ -4285,7 +4281,7 @@
       </c>
       <c r="I45" s="17" t="inlineStr">
         <is>
-          <t>저항 100 kΩ 1% 0402 (벅 FB, 전원 감시)</t>
+          <t>저항 100 kΩ 1% 0402 (50 V)</t>
         </is>
       </c>
       <c r="J45" s="19" t="n">
@@ -4324,12 +4320,12 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>수동</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>R15</t>
+          <t>R14</t>
         </is>
       </c>
       <c r="D46" s="18" t="n">
@@ -4337,7 +4333,7 @@
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>10k 1%</t>
+          <t>100k 1%</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
@@ -4352,12 +4348,12 @@
       </c>
       <c r="H46" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1002TCE</t>
+          <t>0402WGF1003TCE</t>
         </is>
       </c>
       <c r="I46" s="17" t="inlineStr">
         <is>
-          <t>저항 10 kΩ 1% 0402 (전원 감시 분압)</t>
+          <t>저항 100 kΩ 1% 0402 (벅 FB, 전원 감시)</t>
         </is>
       </c>
       <c r="J46" s="19" t="n">
@@ -4381,7 +4377,7 @@
       </c>
       <c r="O46" s="16" t="inlineStr">
         <is>
-          <t>C25744</t>
+          <t>C25741</t>
         </is>
       </c>
       <c r="P46" s="16" t="inlineStr">
@@ -4401,15 +4397,15 @@
       </c>
       <c r="C47" s="17" t="inlineStr">
         <is>
-          <t>R17 R18 R20</t>
+          <t>R15</t>
         </is>
       </c>
       <c r="D47" s="18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" s="16" t="inlineStr">
         <is>
-          <t>1k</t>
+          <t>10k 1%</t>
         </is>
       </c>
       <c r="F47" s="16" t="inlineStr">
@@ -4424,12 +4420,12 @@
       </c>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>0402WGF1001TCE</t>
+          <t>0402WGF1002TCE</t>
         </is>
       </c>
       <c r="I47" s="17" t="inlineStr">
         <is>
-          <t>저항 1 kΩ 1% 0402</t>
+          <t>저항 10 kΩ 1% 0402 (전원 감시 분압)</t>
         </is>
       </c>
       <c r="J47" s="19" t="n">
@@ -4453,7 +4449,7 @@
       </c>
       <c r="O47" s="16" t="inlineStr">
         <is>
-          <t>C11702</t>
+          <t>C25744</t>
         </is>
       </c>
       <c r="P47" s="16" t="inlineStr">
@@ -4468,47 +4464,47 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>수동</t>
         </is>
       </c>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>R19</t>
+          <t>R17 R18 R20</t>
         </is>
       </c>
       <c r="D48" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>4.02k 0.02% 5ppm</t>
+          <t>1k</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G48" s="16" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H48" s="17" t="inlineStr">
         <is>
-          <t>ERA-3AEB4021V</t>
+          <t>0402WGF1001TCE</t>
         </is>
       </c>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>Pt1000 기준저항 4.02 kΩ 0.1 % 25 ppm/K 박막 0603 (결정 #38: JLC 부품 — 이전 PLTT 0.02 %·5 ppm. 초기 오차는 교정, 온도 드리프트는 ADS1220 내부 온도로 보정 검토) [LCSC: 결정 #38: 0.1 %·25 ppm (PLTT 0.02 %·5 ppm 대신)]</t>
+          <t>저항 1 kΩ 1% 0402</t>
         </is>
       </c>
       <c r="J48" s="19" t="n">
-        <v>0.1</v>
+        <v>0.001</v>
       </c>
       <c r="K48" s="19" t="n">
-        <v>0.3</v>
+        <v>0.003</v>
       </c>
       <c r="L48" s="20">
         <f>D48*J48</f>
@@ -4525,12 +4521,12 @@
       </c>
       <c r="O48" s="16" t="inlineStr">
         <is>
-          <t>C491130</t>
+          <t>C11702</t>
         </is>
       </c>
       <c r="P48" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4540,47 +4536,47 @@
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C49" s="17" t="inlineStr">
         <is>
-          <t>R30 R40</t>
+          <t>R19</t>
         </is>
       </c>
       <c r="D49" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>10R pulse</t>
+          <t>4.02k 0.02% 5ppm</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
         <is>
-          <t>R_2512_6332Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G49" s="16" t="inlineStr">
         <is>
-          <t>Vishay</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>CRCW251210R0FKEG</t>
+          <t>ERA-3AEB4021V</t>
         </is>
       </c>
       <c r="I49" s="17" t="inlineStr">
         <is>
-          <t>CRCW 2512 10 Ω 1% 1 W (결정 #38: JLC 부품 — 일반형, 서지 시험 T3로 확인) [LCSC: 결정 #38: 일반형 (HP 대신)]</t>
+          <t>Pt1000 기준저항 4.02 kΩ 0.1 % 25 ppm/K 박막 0603 (결정 #38: JLC 부품 — 이전 PLTT 0.02 %·5 ppm. 초기 오차는 교정, 온도 드리프트는 ADS1220 내부 온도로 보정 검토) [LCSC: 결정 #38: 0.1 %·25 ppm (PLTT 0.02 %·5 ppm 대신)]</t>
         </is>
       </c>
       <c r="J49" s="19" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="K49" s="19" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L49" s="20">
         <f>D49*J49</f>
@@ -4597,7 +4593,7 @@
       </c>
       <c r="O49" s="16" t="inlineStr">
         <is>
-          <t>C844885</t>
+          <t>C491130</t>
         </is>
       </c>
       <c r="P49" s="16" t="inlineStr">
@@ -4612,12 +4608,12 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>R32 R42</t>
+          <t>R30 R40</t>
         </is>
       </c>
       <c r="D50" s="18" t="n">
@@ -4625,34 +4621,34 @@
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>15k 0.1% 25ppm</t>
+          <t>10R pulse</t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
         <is>
-          <t>R_0603_1608Metric</t>
+          <t>R_2512_6332Metric</t>
         </is>
       </c>
       <c r="G50" s="16" t="inlineStr">
         <is>
-          <t>Panasonic</t>
+          <t>Vishay</t>
         </is>
       </c>
       <c r="H50" s="17" t="inlineStr">
         <is>
-          <t>ERA-3AEB153V</t>
+          <t>CRCW251210R0FKEG</t>
         </is>
       </c>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>저항 15 kΩ 0.1% 25 ppm/K 0603 (DAC8760 외부 ISET-R)</t>
+          <t>CRCW 2512 10 Ω 1% 1 W (결정 #38: JLC 부품 — 일반형, 서지 시험 T3로 확인) [LCSC: 결정 #38: 일반형 (HP 대신)]</t>
         </is>
       </c>
       <c r="J50" s="19" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="K50" s="19" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="L50" s="20">
         <f>D50*J50</f>
@@ -4664,12 +4660,12 @@
       </c>
       <c r="N50" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O50" s="16" t="inlineStr">
         <is>
-          <t>C473244</t>
+          <t>C844885</t>
         </is>
       </c>
       <c r="P50" s="16" t="inlineStr">
@@ -4689,7 +4685,7 @@
       </c>
       <c r="C51" s="17" t="inlineStr">
         <is>
-          <t>R34 R44</t>
+          <t>R32 R42</t>
         </is>
       </c>
       <c r="D51" s="18" t="n">
@@ -4697,34 +4693,34 @@
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>10R</t>
+          <t>15k 0.1% 25ppm</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
         <is>
-          <t>R_0402_1005Metric</t>
+          <t>R_0603_1608Metric</t>
         </is>
       </c>
       <c r="G51" s="16" t="inlineStr">
         <is>
-          <t>UNI-ROYAL</t>
+          <t>Panasonic</t>
         </is>
       </c>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>0402WGF100JTCE</t>
+          <t>ERA-3AEB153V</t>
         </is>
       </c>
       <c r="I51" s="17" t="inlineStr">
         <is>
-          <t>저항 10 Ω 1% 0402 (DAC8760 AVDD 직렬, 약 8 mW)</t>
+          <t>저항 15 kΩ 0.1% 25 ppm/K 0603 (DAC8760 외부 ISET-R)</t>
         </is>
       </c>
       <c r="J51" s="19" t="n">
-        <v>0.001</v>
+        <v>0.02</v>
       </c>
       <c r="K51" s="19" t="n">
-        <v>0.003</v>
+        <v>0.06</v>
       </c>
       <c r="L51" s="20">
         <f>D51*J51</f>
@@ -4736,17 +4732,17 @@
       </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>제안</t>
         </is>
       </c>
       <c r="O51" s="16" t="inlineStr">
         <is>
-          <t>C25077</t>
+          <t>C473244</t>
         </is>
       </c>
       <c r="P51" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>Extended</t>
         </is>
       </c>
     </row>
@@ -4761,15 +4757,15 @@
       </c>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>R51</t>
+          <t>R34 R44</t>
         </is>
       </c>
       <c r="D52" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="16" t="inlineStr">
         <is>
-          <t>422k 1%</t>
+          <t>10R</t>
         </is>
       </c>
       <c r="F52" s="16" t="inlineStr">
@@ -4779,17 +4775,17 @@
       </c>
       <c r="G52" s="16" t="inlineStr">
         <is>
-          <t>YAGEO</t>
+          <t>UNI-ROYAL</t>
         </is>
       </c>
       <c r="H52" s="17" t="inlineStr">
         <is>
-          <t>RC0402FR-07422KL</t>
+          <t>0402WGF100JTCE</t>
         </is>
       </c>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>저항 422 kΩ 1% 0402 (VAO 분압 상단)</t>
+          <t>저항 10 Ω 1% 0402 (DAC8760 AVDD 직렬, 약 8 mW)</t>
         </is>
       </c>
       <c r="J52" s="19" t="n">
@@ -4813,12 +4809,12 @@
       </c>
       <c r="O52" s="16" t="inlineStr">
         <is>
-          <t>C477738</t>
+          <t>C25077</t>
         </is>
       </c>
       <c r="P52" s="16" t="inlineStr">
         <is>
-          <t>Extended</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -4828,12 +4824,12 @@
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>전원</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C53" s="17" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>R51</t>
         </is>
       </c>
       <c r="D53" s="18" t="n">
@@ -4841,34 +4837,34 @@
       </c>
       <c r="E53" s="16" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>422k 1%</t>
         </is>
       </c>
       <c r="F53" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
+          <t>R_0402_1005Metric</t>
         </is>
       </c>
       <c r="G53" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>TPS26600PWPR</t>
+          <t>RC0402FR-07422KL</t>
         </is>
       </c>
       <c r="I53" s="17" t="inlineStr">
         <is>
-          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
+          <t>저항 422 kΩ 1% 0402 (VAO 분압 상단)</t>
         </is>
       </c>
       <c r="J53" s="19" t="n">
-        <v>1.5</v>
+        <v>0.001</v>
       </c>
       <c r="K53" s="19" t="n">
-        <v>3</v>
+        <v>0.003</v>
       </c>
       <c r="L53" s="20">
         <f>D53*J53</f>
@@ -4880,12 +4876,12 @@
       </c>
       <c r="N53" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O53" s="16" t="inlineStr">
         <is>
-          <t>C544399</t>
+          <t>C477738</t>
         </is>
       </c>
       <c r="P53" s="16" t="inlineStr">
@@ -4905,20 +4901,20 @@
       </c>
       <c r="C54" s="17" t="inlineStr">
         <is>
-          <t>U2 U15</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="D54" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E54" s="16" t="inlineStr">
         <is>
-          <t>LMR51606YFDBVR</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="F54" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-6</t>
+          <t>HTSSOP-16-1EP_4.4x5mm_P0.65mm_EP3.4x5mm_Mask2.46x2.31mm_ThermalVias</t>
         </is>
       </c>
       <c r="G54" s="16" t="inlineStr">
@@ -4928,19 +4924,19 @@
       </c>
       <c r="H54" s="17" t="inlineStr">
         <is>
-          <t>LMR51606YFDBVR</t>
+          <t>TPS26600PWPR</t>
         </is>
       </c>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>벅 4–65 V 0.6 A 1.1 MHz FPWM SOT-23-6 — U2 5 V (결정 #38), U15 VAO 16.1 V (결정 #37)</t>
+          <t>eFuse 60 V 2 A, 역극성·OVP·UVLO, HTSSOP-16</t>
         </is>
       </c>
       <c r="J54" s="19" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="K54" s="19" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="L54" s="20">
         <f>D54*J54</f>
@@ -4952,12 +4948,12 @@
       </c>
       <c r="N54" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
-          <t>C22439294</t>
+          <t>C544399</t>
         </is>
       </c>
       <c r="P54" s="16" t="inlineStr">
@@ -4977,20 +4973,20 @@
       </c>
       <c r="C55" s="17" t="inlineStr">
         <is>
-          <t>U3</t>
+          <t>U2 U15</t>
         </is>
       </c>
       <c r="D55" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" s="16" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>LMR51606YFDBVR</t>
         </is>
       </c>
       <c r="F55" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>SOT-23-6</t>
         </is>
       </c>
       <c r="G55" s="16" t="inlineStr">
@@ -5000,19 +4996,19 @@
       </c>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>TPS7A2033PDBVR</t>
+          <t>LMR51606YFDBVR</t>
         </is>
       </c>
       <c r="I55" s="17" t="inlineStr">
         <is>
-          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
+          <t>벅 4–65 V 0.6 A 1.1 MHz FPWM SOT-23-6 — U2 5 V (결정 #38), U15 VAO 16.1 V (결정 #37)</t>
         </is>
       </c>
       <c r="J55" s="19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="K55" s="19" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
       <c r="L55" s="20">
         <f>D55*J55</f>
@@ -5024,12 +5020,12 @@
       </c>
       <c r="N55" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O55" s="16" t="inlineStr">
         <is>
-          <t>C2862740</t>
+          <t>C22439294</t>
         </is>
       </c>
       <c r="P55" s="16" t="inlineStr">
@@ -5044,12 +5040,12 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>MCU</t>
+          <t>전원</t>
         </is>
       </c>
       <c r="C56" s="17" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U3</t>
         </is>
       </c>
       <c r="D56" s="18" t="n">
@@ -5057,34 +5053,34 @@
       </c>
       <c r="E56" s="16" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT6</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="F56" s="16" t="inlineStr">
         <is>
-          <t>LQFP-48_7x7mm_P0.5mm</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G56" s="16" t="inlineStr">
         <is>
-          <t>ST</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H56" s="17" t="inlineStr">
         <is>
-          <t>STM32G0B1CCT6</t>
+          <t>TPS7A2033PDBVR</t>
         </is>
       </c>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~85 °C — 사내 DP2000과 같은 품번. 샘플 단계 JLC 부품 (결정 #39), 양산은 전자부 온도 사양 확정 후 CCT3(125 °C) 검토 [LCSC: 샘플 단계 (결정 #39). 85 °C 등급 — 양산 전 온도 사양 확인]</t>
+          <t>LDO 3.3 V 300 mA 저잡음 SOT-23-5 [LCSC: TECHPUBLIC 복제품 C49452001 아님]</t>
         </is>
       </c>
       <c r="J56" s="19" t="n">
-        <v>1.5</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K56" s="19" t="n">
-        <v>2.5</v>
+        <v>0.3</v>
       </c>
       <c r="L56" s="20">
         <f>D56*J56</f>
@@ -5096,12 +5092,12 @@
       </c>
       <c r="N56" s="16" t="inlineStr">
         <is>
-          <t>LCSC</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="O56" s="16" t="inlineStr">
         <is>
-          <t>C5270241</t>
+          <t>C2862740</t>
         </is>
       </c>
       <c r="P56" s="16" t="inlineStr">
@@ -5116,12 +5112,12 @@
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>측정</t>
+          <t>MCU</t>
         </is>
       </c>
       <c r="C57" s="17" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="D57" s="18" t="n">
@@ -5129,34 +5125,34 @@
       </c>
       <c r="E57" s="16" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>STM32G0B1CCT6</t>
         </is>
       </c>
       <c r="F57" s="16" t="inlineStr">
         <is>
-          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
+          <t>LQFP-48_7x7mm_P0.5mm</t>
         </is>
       </c>
       <c r="G57" s="16" t="inlineStr">
         <is>
-          <t>ScioSense</t>
+          <t>ST</t>
         </is>
       </c>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>PCAP04-AQFM-24</t>
+          <t>STM32G0B1CCT6</t>
         </is>
       </c>
       <c r="I57" s="17" t="inlineStr">
         <is>
-          <t>정전용량-디지털 변환기 QFN24</t>
+          <t>MCU Cortex-M0+ 64 MHz 256 KB, LQFP48, −40~85 °C — 사내 DP2000과 같은 품번. 샘플 단계 JLC 부품 (결정 #39), 양산은 전자부 온도 사양 확정 후 CCT3(125 °C) 검토 [LCSC: 샘플 단계 (결정 #39). 85 °C 등급 — 양산 전 온도 사양 확인]</t>
         </is>
       </c>
       <c r="J57" s="19" t="n">
-        <v>6.5</v>
+        <v>1.5</v>
       </c>
       <c r="K57" s="19" t="n">
-        <v>7.1</v>
+        <v>2.5</v>
       </c>
       <c r="L57" s="20">
         <f>D57*J57</f>
@@ -5168,12 +5164,12 @@
       </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
-          <t>확정</t>
+          <t>LCSC</t>
         </is>
       </c>
       <c r="O57" s="16" t="inlineStr">
         <is>
-          <t>C2829318</t>
+          <t>C5270241</t>
         </is>
       </c>
       <c r="P57" s="16" t="inlineStr">
@@ -5193,7 +5189,7 @@
       </c>
       <c r="C58" s="17" t="inlineStr">
         <is>
-          <t>U6</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="D58" s="18" t="n">
@@ -5201,34 +5197,34 @@
       </c>
       <c r="E58" s="16" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="F58" s="16" t="inlineStr">
         <is>
-          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>QFN-24-1EP_4x4mm_P0.5mm_EP2.6x2.6mm</t>
         </is>
       </c>
       <c r="G58" s="16" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>ScioSense</t>
         </is>
       </c>
       <c r="H58" s="17" t="inlineStr">
         <is>
-          <t>ADS1220IPWR</t>
+          <t>PCAP04-AQFM-24</t>
         </is>
       </c>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
+          <t>정전용량-디지털 변환기 QFN24</t>
         </is>
       </c>
       <c r="J58" s="19" t="n">
-        <v>1.9</v>
+        <v>6.5</v>
       </c>
       <c r="K58" s="19" t="n">
-        <v>3.5</v>
+        <v>7.1</v>
       </c>
       <c r="L58" s="20">
         <f>D58*J58</f>
@@ -5245,7 +5241,7 @@
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
-          <t>C48263</t>
+          <t>C2829318</t>
         </is>
       </c>
       <c r="P58" s="16" t="inlineStr">
@@ -5260,25 +5256,25 @@
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>측정</t>
         </is>
       </c>
       <c r="C59" s="17" t="inlineStr">
         <is>
-          <t>U7 U8</t>
+          <t>U6</t>
         </is>
       </c>
       <c r="D59" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="16" t="inlineStr">
         <is>
-          <t>DAC8760IPWP</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="F59" s="16" t="inlineStr">
         <is>
-          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
+          <t>TSSOP-16_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="G59" s="16" t="inlineStr">
@@ -5288,19 +5284,19 @@
       </c>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>DAC8760IPWPR</t>
+          <t>ADS1220IPWR</t>
         </is>
       </c>
       <c r="I59" s="17" t="inlineStr">
         <is>
-          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
+          <t>24-bit ADC, Pt1000 2선 (J3 패드에서 켈빈 분기), TSSOP-16</t>
         </is>
       </c>
       <c r="J59" s="19" t="n">
-        <v>7.8</v>
+        <v>1.9</v>
       </c>
       <c r="K59" s="19" t="n">
-        <v>12.4</v>
+        <v>3.5</v>
       </c>
       <c r="L59" s="20">
         <f>D59*J59</f>
@@ -5317,7 +5313,7 @@
       </c>
       <c r="O59" s="16" t="inlineStr">
         <is>
-          <t>C55047</t>
+          <t>C48263</t>
         </is>
       </c>
       <c r="P59" s="16" t="inlineStr">
@@ -5337,7 +5333,7 @@
       </c>
       <c r="C60" s="17" t="inlineStr">
         <is>
-          <t>U9 U10</t>
+          <t>U7 U8</t>
         </is>
       </c>
       <c r="D60" s="18" t="n">
@@ -5345,12 +5341,12 @@
       </c>
       <c r="E60" s="16" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>DAC8760IPWP</t>
         </is>
       </c>
       <c r="F60" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-8</t>
+          <t>HTSSOP-24-1EP_4.4x7.8mm_P0.65mm_EP3.2x5mm</t>
         </is>
       </c>
       <c r="G60" s="16" t="inlineStr">
@@ -5360,19 +5356,19 @@
       </c>
       <c r="H60" s="17" t="inlineStr">
         <is>
-          <t>TPS26611DDFR</t>
+          <t>DAC8760IPWPR</t>
         </is>
       </c>
       <c r="I60" s="17" t="inlineStr">
         <is>
-          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
+          <t>16-bit 전압/전류 출력 DAC, HTSSOP-24. 사양 확정 후 같은 핀 대체: DAC7760(12-bit V/I), DAC8750(16-bit 전류), DAC7750(12-bit 전류)</t>
         </is>
       </c>
       <c r="J60" s="19" t="n">
-        <v>1.2</v>
+        <v>7.8</v>
       </c>
       <c r="K60" s="19" t="n">
-        <v>2.5</v>
+        <v>12.4</v>
       </c>
       <c r="L60" s="20">
         <f>D60*J60</f>
@@ -5389,7 +5385,7 @@
       </c>
       <c r="O60" s="16" t="inlineStr">
         <is>
-          <t>C3148140</t>
+          <t>C55047</t>
         </is>
       </c>
       <c r="P60" s="16" t="inlineStr">
@@ -5404,25 +5400,25 @@
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>통신</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C61" s="17" t="inlineStr">
         <is>
-          <t>U11</t>
+          <t>U9 U10</t>
         </is>
       </c>
       <c r="D61" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" s="16" t="inlineStr">
         <is>
-          <t>THVD2410DGKR</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="F61" s="16" t="inlineStr">
         <is>
-          <t>VSSOP-8_3.0x3.0mm_P0.65mm</t>
+          <t>SOT-23-8</t>
         </is>
       </c>
       <c r="G61" s="16" t="inlineStr">
@@ -5432,19 +5428,19 @@
       </c>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>THVD2410DGKR</t>
+          <t>TPS26611DDFR</t>
         </is>
       </c>
       <c r="I61" s="17" t="inlineStr">
         <is>
-          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, VSSOP-8 (SOIC와 같은 핀, 외부 검수 H02 TVS 자리 확보) — THVD2450과 같은 핀 (v0.9)</t>
+          <t>±50 V 아날로그 출력 오결선 보호, 32 mA 제한, SOT-23-8</t>
         </is>
       </c>
       <c r="J61" s="19" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K61" s="19" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L61" s="20">
         <f>D61*J61</f>
@@ -5461,7 +5457,7 @@
       </c>
       <c r="O61" s="16" t="inlineStr">
         <is>
-          <t>C1858306</t>
+          <t>C3148140</t>
         </is>
       </c>
       <c r="P61" s="16" t="inlineStr">
@@ -5476,25 +5472,25 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>출력</t>
+          <t>통신</t>
         </is>
       </c>
       <c r="C62" s="17" t="inlineStr">
         <is>
-          <t>U12 U13</t>
+          <t>U11</t>
         </is>
       </c>
       <c r="D62" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" s="16" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>THVD2410DGKR</t>
         </is>
       </c>
       <c r="F62" s="16" t="inlineStr">
         <is>
-          <t>SOT-23-5</t>
+          <t>VSSOP-8_3.0x3.0mm_P0.65mm</t>
         </is>
       </c>
       <c r="G62" s="16" t="inlineStr">
@@ -5504,19 +5500,19 @@
       </c>
       <c r="H62" s="17" t="inlineStr">
         <is>
-          <t>OPA197IDBVR</t>
+          <t>THVD2410DGKR</t>
         </is>
       </c>
       <c r="I62" s="17" t="inlineStr">
         <is>
-          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
+          <t>RS-485 트랜시버 500 kbps (느린 에지), 버스 ±70 V 내성, VSSOP-8 (SOIC와 같은 핀, 외부 검수 H02 TVS 자리 확보) — THVD2450과 같은 핀 (v0.9)</t>
         </is>
       </c>
       <c r="J62" s="19" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="K62" s="19" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="L62" s="20">
         <f>D62*J62</f>
@@ -5528,12 +5524,12 @@
       </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
-          <t>제안</t>
+          <t>확정</t>
         </is>
       </c>
       <c r="O62" s="16" t="inlineStr">
         <is>
-          <t>C221351</t>
+          <t>C1858306</t>
         </is>
       </c>
       <c r="P62" s="16" t="inlineStr">
@@ -5553,20 +5549,20 @@
       </c>
       <c r="C63" s="17" t="inlineStr">
         <is>
-          <t>U14</t>
+          <t>U12 U13</t>
         </is>
       </c>
       <c r="D63" s="18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" s="16" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="F63" s="16" t="inlineStr">
         <is>
-          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
+          <t>SOT-23-5</t>
         </is>
       </c>
       <c r="G63" s="16" t="inlineStr">
@@ -5576,19 +5572,19 @@
       </c>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>SN74LVC2G32DCUR</t>
+          <t>OPA197IDBVR</t>
         </is>
       </c>
       <c r="I63" s="17" t="inlineStr">
         <is>
-          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
+          <t>36 V 레일투레일 연산증폭기 SOT-23-5 — DAC8760 +VSENSE 버퍼 (이득 1)</t>
         </is>
       </c>
       <c r="J63" s="19" t="n">
-        <v>0.08</v>
+        <v>0.6</v>
       </c>
       <c r="K63" s="19" t="n">
-        <v>0.2</v>
+        <v>1.1</v>
       </c>
       <c r="L63" s="20">
         <f>D63*J63</f>
@@ -5605,7 +5601,7 @@
       </c>
       <c r="O63" s="16" t="inlineStr">
         <is>
-          <t>C91874</t>
+          <t>C221351</t>
         </is>
       </c>
       <c r="P63" s="16" t="inlineStr">
@@ -5620,12 +5616,12 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>기판</t>
+          <t>출력</t>
         </is>
       </c>
       <c r="C64" s="17" t="inlineStr">
         <is>
-          <t>PCB</t>
+          <t>U14</t>
         </is>
       </c>
       <c r="D64" s="18" t="n">
@@ -5633,34 +5629,34 @@
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>VSSOP-8_2.3x2mm_P0.5mm</t>
         </is>
       </c>
       <c r="G64" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TI</t>
         </is>
       </c>
       <c r="H64" s="17" t="inlineStr">
         <is>
-          <t>HMT500(260313A) (E-301)</t>
+          <t>SN74LVC2G32DCUR</t>
         </is>
       </c>
       <c r="I64" s="17" t="inlineStr">
         <is>
-          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
+          <t>OR 게이트 2회로 VSSOP-8 — DAC별 SCLK 게이트 (DAC8760 8.5.1.5)</t>
         </is>
       </c>
       <c r="J64" s="19" t="n">
-        <v>0.8</v>
+        <v>0.08</v>
       </c>
       <c r="K64" s="19" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="L64" s="20">
         <f>D64*J64</f>
@@ -5670,13 +5666,21 @@
         <f>D64*K64</f>
         <v/>
       </c>
-      <c r="N64" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O64" s="16" t="inlineStr"/>
-      <c r="P64" s="16" t="inlineStr"/>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O64" s="16" t="inlineStr">
+        <is>
+          <t>C91874</t>
+        </is>
+      </c>
+      <c r="P64" s="16" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="n">
@@ -5684,12 +5688,12 @@
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>센서</t>
+          <t>기판</t>
         </is>
       </c>
       <c r="C65" s="17" t="inlineStr">
         <is>
-          <t>센서 헤드</t>
+          <t>PCB</t>
         </is>
       </c>
       <c r="D65" s="18" t="n">
@@ -5707,24 +5711,24 @@
       </c>
       <c r="G65" s="16" t="inlineStr">
         <is>
-          <t>IST</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H65" s="17" t="inlineStr">
         <is>
-          <t>MK33-W (300 pF, 품번 확인 필요)</t>
+          <t>HMT500(260313A) (E-301)</t>
         </is>
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
-          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
+          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
         </is>
       </c>
       <c r="J65" s="19" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="K65" s="19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="20">
         <f>D65*J65</f>
@@ -5736,7 +5740,7 @@
       </c>
       <c r="N65" s="21" t="inlineStr">
         <is>
-          <t>사내 단가</t>
+          <t>추정</t>
         </is>
       </c>
       <c r="O65" s="16" t="inlineStr"/>
@@ -5776,19 +5780,19 @@
       </c>
       <c r="H66" s="17" t="inlineStr">
         <is>
-          <t>MiniSens Pt1000 F0.1</t>
+          <t>MK33-W (300 pF, 품번 확인 필요)</t>
         </is>
       </c>
       <c r="I66" s="17" t="inlineStr">
         <is>
-          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
+          <t>정전용량 습도 소자 300 pF (센서 프로브 P-202에 실장, 결정 #33)</t>
         </is>
       </c>
       <c r="J66" s="19" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="K66" s="19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L66" s="20">
         <f>D66*J66</f>
@@ -5800,7 +5804,7 @@
       </c>
       <c r="N66" s="21" t="inlineStr">
         <is>
-          <t>추정</t>
+          <t>사내 단가</t>
         </is>
       </c>
       <c r="O66" s="16" t="inlineStr"/>
@@ -5812,12 +5816,12 @@
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>커넥터</t>
+          <t>센서</t>
         </is>
       </c>
       <c r="C67" s="17" t="inlineStr">
         <is>
-          <t>P-204</t>
+          <t>센서 헤드</t>
         </is>
       </c>
       <c r="D67" s="18" t="n">
@@ -5835,24 +5839,24 @@
       </c>
       <c r="G67" s="16" t="inlineStr">
         <is>
-          <t>M Connect</t>
+          <t>IST</t>
         </is>
       </c>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>TBD (두텍 사용품)</t>
+          <t>MiniSens Pt1000 F0.1</t>
         </is>
       </c>
       <c r="I67" s="17" t="inlineStr">
         <is>
-          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
+          <t>온도 소자 1.6×1.2 mm (센서 프로브 P-202에 실장)</t>
         </is>
       </c>
       <c r="J67" s="19" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="K67" s="19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L67" s="20">
         <f>D67*J67</f>
@@ -5862,9 +5866,9 @@
         <f>D67*K67</f>
         <v/>
       </c>
-      <c r="N67" s="22" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="N67" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
         </is>
       </c>
       <c r="O67" s="16" t="inlineStr"/>
@@ -5876,12 +5880,12 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>하네스</t>
+          <t>커넥터</t>
         </is>
       </c>
       <c r="C68" s="17" t="inlineStr">
         <is>
-          <t>W-2</t>
+          <t>P-204</t>
         </is>
       </c>
       <c r="D68" s="18" t="n">
@@ -5899,24 +5903,24 @@
       </c>
       <c r="G68" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>M Connect</t>
         </is>
       </c>
       <c r="H68" s="17" t="inlineStr">
         <is>
-          <t>GHR-08V-S</t>
+          <t>TBD (두텍 사용품)</t>
         </is>
       </c>
       <c r="I68" s="17" t="inlineStr">
         <is>
-          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
+          <t>M12 8핀 수컷 전면 장착형 M16×1.5, 리드선형 (W-2 납땜)</t>
         </is>
       </c>
       <c r="J68" s="19" t="n">
-        <v>0.06</v>
+        <v>2</v>
       </c>
       <c r="K68" s="19" t="n">
-        <v>0.15</v>
+        <v>10</v>
       </c>
       <c r="L68" s="20">
         <f>D68*J68</f>
@@ -5926,21 +5930,13 @@
         <f>D68*K68</f>
         <v/>
       </c>
-      <c r="N68" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O68" s="16" t="inlineStr">
-        <is>
-          <t>C485357</t>
-        </is>
-      </c>
-      <c r="P68" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N68" s="22" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="O68" s="16" t="inlineStr"/>
+      <c r="P68" s="16" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="16" t="n">
@@ -5957,7 +5953,7 @@
         </is>
       </c>
       <c r="D69" s="18" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E69" s="16" t="inlineStr">
         <is>
@@ -5976,19 +5972,19 @@
       </c>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>SSHL-002T-P0.2</t>
+          <t>GHR-08V-S</t>
         </is>
       </c>
       <c r="I69" s="17" t="inlineStr">
         <is>
-          <t>GH 크림프 단자 AWG 30–26</t>
+          <t>GH 1.25 mm 8핀 소켓 하우징 (M12 하네스 W-2)</t>
         </is>
       </c>
       <c r="J69" s="19" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="K69" s="19" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="L69" s="20">
         <f>D69*J69</f>
@@ -6005,7 +6001,7 @@
       </c>
       <c r="O69" s="16" t="inlineStr">
         <is>
-          <t>C189897</t>
+          <t>C485357</t>
         </is>
       </c>
       <c r="P69" s="16" t="inlineStr">
@@ -6029,7 +6025,7 @@
         </is>
       </c>
       <c r="D70" s="18" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
@@ -6043,24 +6039,24 @@
       </c>
       <c r="G70" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H70" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG28 전선</t>
+          <t>SSHL-002T-P0.2</t>
         </is>
       </c>
       <c r="I70" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+          <t>GH 크림프 단자 AWG 30–26</t>
         </is>
       </c>
       <c r="J70" s="19" t="n">
-        <v>0.15</v>
+        <v>0.03</v>
       </c>
       <c r="K70" s="19" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="L70" s="20">
         <f>D70*J70</f>
@@ -6070,13 +6066,21 @@
         <f>D70*K70</f>
         <v/>
       </c>
-      <c r="N70" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O70" s="16" t="inlineStr"/>
-      <c r="P70" s="16" t="inlineStr"/>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O70" s="16" t="inlineStr">
+        <is>
+          <t>C189897</t>
+        </is>
+      </c>
+      <c r="P70" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="n">
@@ -6089,7 +6093,7 @@
       </c>
       <c r="C71" s="17" t="inlineStr">
         <is>
-          <t>W-1</t>
+          <t>W-2</t>
         </is>
       </c>
       <c r="D71" s="18" t="n">
@@ -6107,24 +6111,24 @@
       </c>
       <c r="G71" s="16" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>SHR-04V-S</t>
+          <t>PTFE AWG28 전선</t>
         </is>
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
-          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
+          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
         </is>
       </c>
       <c r="J71" s="19" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="K71" s="19" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="L71" s="20">
         <f>D71*J71</f>
@@ -6134,21 +6138,13 @@
         <f>D71*K71</f>
         <v/>
       </c>
-      <c r="N71" s="16" t="inlineStr">
-        <is>
-          <t>제안</t>
-        </is>
-      </c>
-      <c r="O71" s="16" t="inlineStr">
-        <is>
-          <t>C385125</t>
-        </is>
-      </c>
-      <c r="P71" s="16" t="inlineStr">
-        <is>
-          <t>LCSC 주문</t>
-        </is>
-      </c>
+      <c r="N71" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O71" s="16" t="inlineStr"/>
+      <c r="P71" s="16" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="16" t="n">
@@ -6165,7 +6161,7 @@
         </is>
       </c>
       <c r="D72" s="18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E72" s="16" t="inlineStr">
         <is>
@@ -6184,19 +6180,19 @@
       </c>
       <c r="H72" s="17" t="inlineStr">
         <is>
-          <t>SSH-003T-P0.2-H</t>
+          <t>SHR-04V-S</t>
         </is>
       </c>
       <c r="I72" s="17" t="inlineStr">
         <is>
-          <t>SH 크림프 단자 AWG 32–28</t>
+          <t>SH 1.0 mm 4핀 소켓 하우징 (센서 하네스 W-1)</t>
         </is>
       </c>
       <c r="J72" s="19" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="K72" s="19" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="L72" s="20">
         <f>D72*J72</f>
@@ -6213,7 +6209,7 @@
       </c>
       <c r="O72" s="16" t="inlineStr">
         <is>
-          <t>C263995</t>
+          <t>C385125</t>
         </is>
       </c>
       <c r="P72" s="16" t="inlineStr">
@@ -6237,7 +6233,7 @@
         </is>
       </c>
       <c r="D73" s="18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E73" s="16" t="inlineStr">
         <is>
@@ -6251,24 +6247,24 @@
       </c>
       <c r="G73" s="16" t="inlineStr">
         <is>
-          <t>TBD</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>PTFE AWG30 전선</t>
+          <t>SSH-003T-P0.2-H</t>
         </is>
       </c>
       <c r="I73" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+          <t>SH 크림프 단자 AWG 32–28</t>
         </is>
       </c>
       <c r="J73" s="19" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="K73" s="19" t="n">
-        <v>0.3</v>
+        <v>0.06</v>
       </c>
       <c r="L73" s="20">
         <f>D73*J73</f>
@@ -6278,13 +6274,21 @@
         <f>D73*K73</f>
         <v/>
       </c>
-      <c r="N73" s="21" t="inlineStr">
-        <is>
-          <t>추정</t>
-        </is>
-      </c>
-      <c r="O73" s="16" t="inlineStr"/>
-      <c r="P73" s="16" t="inlineStr"/>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>제안</t>
+        </is>
+      </c>
+      <c r="O73" s="16" t="inlineStr">
+        <is>
+          <t>C263995</t>
+        </is>
+      </c>
+      <c r="P73" s="16" t="inlineStr">
+        <is>
+          <t>LCSC 주문</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="n">
@@ -6292,12 +6296,12 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>조립</t>
+          <t>하네스</t>
         </is>
       </c>
       <c r="C74" s="17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>W-1</t>
         </is>
       </c>
       <c r="D74" s="18" t="n">
@@ -6315,24 +6319,24 @@
       </c>
       <c r="G74" s="16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TBD</t>
         </is>
       </c>
       <c r="H74" s="17" t="inlineStr">
         <is>
-          <t>SMT 양면 실장</t>
+          <t>PTFE AWG30 전선</t>
         </is>
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>1k 기준 조립비</t>
+          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
         </is>
       </c>
       <c r="J74" s="19" t="n">
-        <v>2</v>
+        <v>0.1</v>
       </c>
       <c r="K74" s="19" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="L74" s="20">
         <f>D74*J74</f>
@@ -6351,17 +6355,81 @@
       <c r="P74" s="16" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="I75" s="3" t="inlineStr">
+      <c r="A75" s="16" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>조립</t>
+        </is>
+      </c>
+      <c r="C75" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E75" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" s="17" t="inlineStr">
+        <is>
+          <t>SMT 양면 실장</t>
+        </is>
+      </c>
+      <c r="I75" s="17" t="inlineStr">
+        <is>
+          <t>1k 기준 조립비</t>
+        </is>
+      </c>
+      <c r="J75" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="K75" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="L75" s="20">
+        <f>D75*J75</f>
+        <v/>
+      </c>
+      <c r="M75" s="20">
+        <f>D75*K75</f>
+        <v/>
+      </c>
+      <c r="N75" s="21" t="inlineStr">
+        <is>
+          <t>추정</t>
+        </is>
+      </c>
+      <c r="O75" s="16" t="inlineStr"/>
+      <c r="P75" s="16" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="I76" s="3" t="inlineStr">
         <is>
           <t>합계 (1대분)</t>
         </is>
       </c>
-      <c r="L75" s="23">
-        <f>SUM(L2:L74)</f>
-        <v/>
-      </c>
-      <c r="M75" s="23">
-        <f>SUM(M2:M74)</f>
+      <c r="L76" s="23">
+        <f>SUM(L2:L75)</f>
+        <v/>
+      </c>
+      <c r="M76" s="23">
+        <f>SUM(M2:M75)</f>
         <v/>
       </c>
     </row>

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -3421,7 +3421,7 @@
       </c>
       <c r="I33" s="17" t="inlineStr">
         <is>
-          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 풋프린트 사용 — 랜드·권선 핀 배정은 Bourns 데이터시트로 확인 필요 [LCSC: 재고 적음 (약 810개). 풋프린트 대조 필요]</t>
+          <t>공통모드 초크 2 × 1 mH, 0.8 A, 0.31 Ω, 9.2 × 6 × 5.3 mm (LCSC, Würth 744222 동등). WE-SL2 랜드 일치: 패드 2×1.2, 중심 ±3.75/±1.27 mm; SRF0905 원문 권선 1–4/2–3 대조 완료 [LCSC: SRF0905 권장 랜드와 WE-SL2 패드 치수·핀 배정 대조 완료 (2026-10-01); 주문 시 재고 확인]</t>
         </is>
       </c>
       <c r="J33" s="19" t="n">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>L_Taiyo-Yuden_NR-40xx</t>
+          <t>L_SXN_SMNR4020</t>
         </is>
       </c>
       <c r="G34" s="16" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="I34" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 10 µH ±20 % 0.62 A 0.95 Ω 4 × 4 × 2 mm (NR-40xx 랜드) — 5 V 벅 (부하 약 60 mA) [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
+          <t>파워 인덕터 10 µH ±20 %, 원문 정격 DC 1.60 A, DCR 0.165 Ω ±30 %, 4 × 4 × 2.2 mm max (전용 랜드; 포화 기준 확인 필요) — 5 V 벅 (부하 약 60 mA) [LCSC: SXN 원문 F=.95/G=2.1/H=3.3 mm 전용 랜드 반영; Isat 정의 확인 필요]</t>
         </is>
       </c>
       <c r="J34" s="19" t="n">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="F35" s="16" t="inlineStr">
         <is>
-          <t>L_Taiyo-Yuden_NR-40xx</t>
+          <t>L_SXN_SMNR4020</t>
         </is>
       </c>
       <c r="G35" s="16" t="inlineStr">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="I35" s="17" t="inlineStr">
         <is>
-          <t>파워 인덕터 22 µH ±20 % 1.05 A 455 mΩ 4 × 4 × 2 mm (NR-40xx 랜드) — VAO 벅 [LCSC: 랜드 패턴을 NR-40xx와 대조 필요]</t>
+          <t>파워 인덕터 22 µH ±20 %, 원문 정격 DC 1.05 A, DCR 0.350 Ω ±30 %, 4 × 4 × 2.2 mm max (전용 랜드; 포화 기준 확인 필요) — VAO 벅 [LCSC: SXN 원문 F=.95/G=2.1/H=3.3 mm 전용 랜드 반영; Isat 정의 확인 필요]</t>
         </is>
       </c>
       <c r="J35" s="19" t="n">

--- a/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
+++ b/hardware/kicad/HMT500(260313A)/HMT500(260313A)_parts_list.xlsx
@@ -1429,7 +1429,7 @@
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
-          <t>MLCC 22 nF 16 V X7R 0402 (eFuse dV/dt, RTN 기준 저전압)</t>
+          <t>MLCC 22 nF 16 V X7R 0402 (eFuse dV/dt, RTN 기준 저전압) [LCSC: 2026-10-03 LCSC 품번 대조: C1532는 FH 제품이므로 정정; JLC 등급/재고 확인 필요]</t>
         </is>
       </c>
       <c r="J5" s="19" t="n">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="O5" s="16" t="inlineStr">
         <is>
-          <t>C1532</t>
+          <t>C318579</t>
         </is>
       </c>
       <c r="P5" s="16" t="inlineStr">
         <is>
-          <t>Basic</t>
+          <t>확인 필요</t>
         </is>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="E13" s="16" t="inlineStr">
         <is>
-          <t>330p C0G 1%</t>
+          <t>330p C0G 2%</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>MLCC 330 pF 50 V C0G ±1% 0603 (PCAP04 기준 C, 센서 MK33-W 300 pF) [LCSC: ±2 % (LCSC에 ±1 % 없음) — 기준 C 절대값은 교정으로 제거, C0G라 온도 안정]</t>
+          <t>MLCC 330 pF 50 V C0G ±2% 0603 (결정 #34, PCAP04 기준 C) [LCSC: ±2 % (LCSC에 ±1 % 없음) — 기준 C 절대값은 교정으로 제거, C0G라 온도 안정]</t>
         </is>
       </c>
       <c r="J13" s="19" t="n">
@@ -2571,24 +2571,24 @@
       </c>
       <c r="G21" s="16" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>YAGEO</t>
         </is>
       </c>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>CL21B225KBFNNNE</t>
+          <t>CC0805KKX7R9BB225</t>
         </is>
       </c>
       <c r="I21" s="17" t="inlineStr">
         <is>
-          <t>MLCC 2.2 uF 50 V X7R 0805 (VAO 벅 입력) [LCSC: LCSC 번호는 JLC 화면에서 같은 품번 선택 (검색에서 C 번호 미확인)]</t>
+          <t>MLCC 2.2 uF 50 V X7R ±10% 0805, 최대 높이 1.45 mm (VAO 벅 입력) [LCSC: 결정 #53: 2.2 µF 50 V X7R ±10% 0805; 최대 높이 1.45 mm; DC 바이어스 실효 용량 확인 필요]</t>
         </is>
       </c>
       <c r="J21" s="19" t="n">
         <v>0.02</v>
       </c>
       <c r="K21" s="19" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="L21" s="20">
         <f>D21*J21</f>
@@ -2603,7 +2603,11 @@
           <t>LCSC</t>
         </is>
       </c>
-      <c r="O21" s="16" t="inlineStr"/>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>C125847</t>
+        </is>
+      </c>
       <c r="P21" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -3555,7 +3559,7 @@
       </c>
       <c r="G35" s="16" t="inlineStr">
         <is>
-          <t>(LCSC)</t>
+          <t>SXN</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
@@ -4141,7 +4145,7 @@
       </c>
       <c r="I43" s="17" t="inlineStr">
         <is>
-          <t>저항 22.1 kΩ 1% 0402 (VAO 분압 하단) [LCSC: LCSC 번호 미확인 — JLC 화면에서 22.1 kΩ 1 % 0402 선택]</t>
+          <t>저항 22.1 kΩ 1% 0402 (VAO 분압 하단) [LCSC: 2026-10-03 LCSC/JLC 품번·22.1 kΩ ±1%·0402 대조]</t>
         </is>
       </c>
       <c r="J43" s="19" t="n">
@@ -4163,7 +4167,11 @@
           <t>확인 필요</t>
         </is>
       </c>
-      <c r="O43" s="16" t="inlineStr"/>
+      <c r="O43" s="16" t="inlineStr">
+        <is>
+          <t>C43473</t>
+        </is>
+      </c>
       <c r="P43" s="16" t="inlineStr">
         <is>
           <t>Extended</t>
@@ -4549,7 +4557,7 @@
       </c>
       <c r="E49" s="16" t="inlineStr">
         <is>
-          <t>4.02k 0.02% 5ppm</t>
+          <t>4.02k 0.1% 25ppm</t>
         </is>
       </c>
       <c r="F49" s="16" t="inlineStr">
@@ -5721,7 +5729,7 @@
       </c>
       <c r="I65" s="17" t="inlineStr">
         <is>
-          <t>PCB 4층 57×23 mm, FR-4 1.6 t, ENIG (기구 Rev C 외곽)</t>
+          <t>PCB 6층 57×23 mm, FR-4 nominal 1.6 t, ENIG (A5-R1, 기구 Rev I 외곽)</t>
         </is>
       </c>
       <c r="J65" s="19" t="n">
@@ -6121,7 +6129,7 @@
       </c>
       <c r="I71" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 8심 × 60 mm + 수축튜브 (M12 핀 납땜)</t>
+          <t>UL1213 계열 200 °C, 8심 × 40±2 mm 설계값(절단/완성 길이 확인 필요) + 수축튜브 (M12 핀 납땜)</t>
         </is>
       </c>
       <c r="J71" s="19" t="n">
@@ -6329,7 +6337,7 @@
       </c>
       <c r="I74" s="17" t="inlineStr">
         <is>
-          <t>UL1213 계열 200 °C, 4심 × 60 mm (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
+          <t>UL1213 계열 200 °C, 4심 × 40±2 mm 설계값(절단/완성 길이 확인 필요) (HTX99R 뒤 핀 납땜 + 수축튜브)</t>
         </is>
       </c>
       <c r="J74" s="19" t="n">
